--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="F14" t="n">
-        <v>8.27</v>
+        <v>8.59</v>
       </c>
       <c r="G14" t="n">
-        <v>291.6</v>
+        <v>313.7</v>
       </c>
       <c r="H14" t="n">
-        <v>82.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.28</v>
+        <v>-66.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.58</v>
+        <v>19.09</v>
       </c>
       <c r="L14" t="n">
-        <v>21.64</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:13:51</t>
+          <t>06:15:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="F15" t="n">
-        <v>8.140000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="G15" t="n">
-        <v>294.4</v>
+        <v>286.9</v>
       </c>
       <c r="H15" t="n">
-        <v>70.5</v>
+        <v>81.3</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>11.29</v>
+        <v>28.43</v>
       </c>
       <c r="K15" t="n">
-        <v>-28.02</v>
+        <v>122.62</v>
       </c>
       <c r="L15" t="n">
-        <v>30.21</v>
+        <v>125.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:14:47</t>
+          <t>06:16:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="F16" t="n">
-        <v>8.119999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="G16" t="n">
-        <v>284.5</v>
+        <v>305.7</v>
       </c>
       <c r="H16" t="n">
-        <v>77.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-47.36</v>
+        <v>94.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-85.65000000000001</v>
+        <v>48.74</v>
       </c>
       <c r="L16" t="n">
-        <v>97.87</v>
+        <v>105.94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:18:06</t>
+          <t>06:20:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="F17" t="n">
-        <v>8.210000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="G17" t="n">
-        <v>301.7</v>
+        <v>307.3</v>
       </c>
       <c r="H17" t="n">
-        <v>84.2</v>
+        <v>80</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>155.64</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-32.63</v>
+        <v>84.95</v>
       </c>
       <c r="L17" t="n">
-        <v>159.02</v>
+        <v>113.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:20:01</t>
+          <t>06:21:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="F18" t="n">
-        <v>8.31</v>
+        <v>8.41</v>
       </c>
       <c r="G18" t="n">
-        <v>310</v>
+        <v>304.1</v>
       </c>
       <c r="H18" t="n">
-        <v>86</v>
+        <v>85.2</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>57.09</v>
+        <v>-27.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-83.56999999999999</v>
+        <v>-125.31</v>
       </c>
       <c r="L18" t="n">
-        <v>101.2</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:20:53</t>
+          <t>06:22:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="F19" t="n">
-        <v>8.039999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>292.3</v>
+        <v>297.9</v>
       </c>
       <c r="H19" t="n">
-        <v>78.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>68.22</v>
+        <v>-24.22</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.84</v>
+        <v>58.51</v>
       </c>
       <c r="L19" t="n">
-        <v>68.56</v>
+        <v>63.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:25:07</t>
+          <t>06:27:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="F20" t="n">
-        <v>8.710000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>290.4</v>
+        <v>288.7</v>
       </c>
       <c r="H20" t="n">
-        <v>80</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-185.02</v>
+        <v>-37.98</v>
       </c>
       <c r="K20" t="n">
-        <v>-109.08</v>
+        <v>77.73</v>
       </c>
       <c r="L20" t="n">
-        <v>214.78</v>
+        <v>86.51000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:26:00</t>
+          <t>06:29:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="F21" t="n">
-        <v>9.68</v>
+        <v>8.73</v>
       </c>
       <c r="G21" t="n">
-        <v>297</v>
+        <v>293.2</v>
       </c>
       <c r="H21" t="n">
-        <v>82.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-293.35</v>
+        <v>-34.49</v>
       </c>
       <c r="K21" t="n">
-        <v>26.25</v>
+        <v>73.66</v>
       </c>
       <c r="L21" t="n">
-        <v>294.52</v>
+        <v>81.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:28:00</t>
+          <t>06:31:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="F22" t="n">
-        <v>8.880000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="G22" t="n">
-        <v>295</v>
+        <v>298.3</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>80.7</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-116.91</v>
+        <v>-0.24</v>
       </c>
       <c r="K22" t="n">
-        <v>63.49</v>
+        <v>-53.44</v>
       </c>
       <c r="L22" t="n">
-        <v>133.04</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:34:10</t>
+          <t>06:35:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.37</v>
+        <v>1.59</v>
       </c>
       <c r="F23" t="n">
-        <v>8.51</v>
+        <v>7.68</v>
       </c>
       <c r="G23" t="n">
         <v>287.6</v>
       </c>
       <c r="H23" t="n">
-        <v>75.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-276.15</v>
+        <v>249.6</v>
       </c>
       <c r="K23" t="n">
-        <v>-241.73</v>
+        <v>-28.03</v>
       </c>
       <c r="L23" t="n">
-        <v>367</v>
+        <v>251.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:35:05</t>
+          <t>06:37:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="F24" t="n">
-        <v>8.33</v>
+        <v>8.68</v>
       </c>
       <c r="G24" t="n">
-        <v>303.1</v>
+        <v>287.5</v>
       </c>
       <c r="H24" t="n">
-        <v>85.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-283.36</v>
+        <v>172.5</v>
       </c>
       <c r="K24" t="n">
-        <v>-138.74</v>
+        <v>-174.26</v>
       </c>
       <c r="L24" t="n">
-        <v>315.51</v>
+        <v>245.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:36:10</t>
+          <t>06:38:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="F25" t="n">
-        <v>8.33</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>307.8</v>
+        <v>296.1</v>
       </c>
       <c r="H25" t="n">
-        <v>77.8</v>
+        <v>82.5</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>106.34</v>
+        <v>176.43</v>
       </c>
       <c r="K25" t="n">
-        <v>85.09</v>
+        <v>-130.88</v>
       </c>
       <c r="L25" t="n">
-        <v>136.2</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:40:13</t>
+          <t>06:43:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="F26" t="n">
-        <v>8.630000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="G26" t="n">
-        <v>306.2</v>
+        <v>306.5</v>
       </c>
       <c r="H26" t="n">
-        <v>89.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-248.31</v>
+        <v>-116.08</v>
       </c>
       <c r="K26" t="n">
-        <v>96.72</v>
+        <v>-50.58</v>
       </c>
       <c r="L26" t="n">
-        <v>266.48</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:41:33</t>
+          <t>06:43:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="F27" t="n">
-        <v>8.52</v>
+        <v>7.8</v>
       </c>
       <c r="G27" t="n">
-        <v>282.3</v>
+        <v>299.1</v>
       </c>
       <c r="H27" t="n">
-        <v>77.7</v>
+        <v>83.8</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>19.36</v>
+        <v>341.27</v>
       </c>
       <c r="K27" t="n">
-        <v>223.3</v>
+        <v>457.38</v>
       </c>
       <c r="L27" t="n">
-        <v>224.14</v>
+        <v>570.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:43:02</t>
+          <t>06:45:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="F28" t="n">
-        <v>8.52</v>
+        <v>8.59</v>
       </c>
       <c r="G28" t="n">
-        <v>300.6</v>
+        <v>305</v>
       </c>
       <c r="H28" t="n">
-        <v>81</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>395.49</v>
+        <v>120.27</v>
       </c>
       <c r="K28" t="n">
-        <v>180.39</v>
+        <v>-4.15</v>
       </c>
       <c r="L28" t="n">
-        <v>434.68</v>
+        <v>120.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:51:22</t>
+          <t>06:58:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.51</v>
+        <v>1.91</v>
       </c>
       <c r="F29" t="n">
-        <v>7.82</v>
+        <v>7.76</v>
       </c>
       <c r="G29" t="n">
-        <v>324.4</v>
+        <v>302.7</v>
       </c>
       <c r="H29" t="n">
-        <v>83.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>150.54</v>
+        <v>125.64</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.44</v>
+        <v>5.29</v>
       </c>
       <c r="L29" t="n">
-        <v>158.45</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:52:17</t>
+          <t>07:01:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="F30" t="n">
-        <v>8.859999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>290.5</v>
+        <v>290</v>
       </c>
       <c r="H30" t="n">
-        <v>83.7</v>
+        <v>89</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>17.4</v>
+        <v>-44.42</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.64</v>
+        <v>-3.51</v>
       </c>
       <c r="L30" t="n">
-        <v>18.01</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:54:11</t>
+          <t>07:02:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="F31" t="n">
-        <v>7.88</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>291.4</v>
+        <v>318.1</v>
       </c>
       <c r="H31" t="n">
-        <v>76.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>19.18</v>
+        <v>-150.76</v>
       </c>
       <c r="K31" t="n">
-        <v>42.63</v>
+        <v>118.91</v>
       </c>
       <c r="L31" t="n">
-        <v>46.75</v>
+        <v>192.01</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:59:04</t>
+          <t>07:07:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="F32" t="n">
-        <v>8.49</v>
+        <v>8.33</v>
       </c>
       <c r="G32" t="n">
-        <v>294.7</v>
+        <v>309.9</v>
       </c>
       <c r="H32" t="n">
-        <v>79.8</v>
+        <v>75.3</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-182.04</v>
+        <v>-173.35</v>
       </c>
       <c r="K32" t="n">
-        <v>119.48</v>
+        <v>154.32</v>
       </c>
       <c r="L32" t="n">
-        <v>217.74</v>
+        <v>232.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:01:05</t>
+          <t>07:09:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="F33" t="n">
-        <v>8.65</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>294.5</v>
+        <v>293.6</v>
       </c>
       <c r="H33" t="n">
-        <v>85.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>28.77</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>101.8</v>
+        <v>-167.45</v>
       </c>
       <c r="L33" t="n">
-        <v>105.78</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:02:17</t>
+          <t>07:10:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="F34" t="n">
-        <v>9.039999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G34" t="n">
-        <v>301.4</v>
+        <v>301</v>
       </c>
       <c r="H34" t="n">
-        <v>76.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-23.23</v>
+        <v>-70.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-30.17</v>
+        <v>-93.76000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>38.08</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:06:36</t>
+          <t>07:14:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="F35" t="n">
-        <v>8.140000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>294.5</v>
+        <v>290.8</v>
       </c>
       <c r="H35" t="n">
-        <v>84.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-25.14</v>
+        <v>94.87</v>
       </c>
       <c r="K35" t="n">
-        <v>56.87</v>
+        <v>171</v>
       </c>
       <c r="L35" t="n">
-        <v>62.18</v>
+        <v>195.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:07:48</t>
+          <t>07:16:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="F36" t="n">
-        <v>8.33</v>
+        <v>8.19</v>
       </c>
       <c r="G36" t="n">
-        <v>308.5</v>
+        <v>287.9</v>
       </c>
       <c r="H36" t="n">
-        <v>77.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>210.44</v>
+        <v>23.7</v>
       </c>
       <c r="K36" t="n">
-        <v>-27.76</v>
+        <v>-164.42</v>
       </c>
       <c r="L36" t="n">
-        <v>212.26</v>
+        <v>166.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:10:23</t>
+          <t>07:18:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="F37" t="n">
-        <v>8.300000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="G37" t="n">
-        <v>298.3</v>
+        <v>296</v>
       </c>
       <c r="H37" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-274.65</v>
+        <v>-56.84</v>
       </c>
       <c r="K37" t="n">
-        <v>41.58</v>
+        <v>182.9</v>
       </c>
       <c r="L37" t="n">
-        <v>277.78</v>
+        <v>191.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:16:02</t>
+          <t>07:22:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="F38" t="n">
-        <v>8.289999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="G38" t="n">
-        <v>300.2</v>
+        <v>305</v>
       </c>
       <c r="H38" t="n">
-        <v>82.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-209.78</v>
+        <v>66.31</v>
       </c>
       <c r="K38" t="n">
-        <v>684.04</v>
+        <v>-43.91</v>
       </c>
       <c r="L38" t="n">
-        <v>715.49</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:17:47</t>
+          <t>07:24:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="F39" t="n">
-        <v>8.119999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>290.7</v>
+        <v>301.4</v>
       </c>
       <c r="H39" t="n">
-        <v>81.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-387.64</v>
+        <v>-55.8</v>
       </c>
       <c r="K39" t="n">
-        <v>413.38</v>
+        <v>-339.46</v>
       </c>
       <c r="L39" t="n">
-        <v>566.7</v>
+        <v>344.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:19:11</t>
+          <t>07:26:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="F40" t="n">
-        <v>7.96</v>
+        <v>8.5</v>
       </c>
       <c r="G40" t="n">
-        <v>302.8</v>
+        <v>299.3</v>
       </c>
       <c r="H40" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-63.55</v>
+        <v>93.52</v>
       </c>
       <c r="K40" t="n">
-        <v>-469.82</v>
+        <v>-355.28</v>
       </c>
       <c r="L40" t="n">
-        <v>474.1</v>
+        <v>367.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:24:04</t>
+          <t>07:30:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="F41" t="n">
-        <v>7.94</v>
+        <v>8.33</v>
       </c>
       <c r="G41" t="n">
-        <v>301.1</v>
+        <v>292.7</v>
       </c>
       <c r="H41" t="n">
-        <v>78.7</v>
+        <v>83.3</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-60.41</v>
+        <v>146.62</v>
       </c>
       <c r="K41" t="n">
-        <v>-372.37</v>
+        <v>52.03</v>
       </c>
       <c r="L41" t="n">
-        <v>377.24</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:25:39</t>
+          <t>07:31:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="F42" t="n">
-        <v>8.640000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>292.2</v>
+        <v>288.5</v>
       </c>
       <c r="H42" t="n">
-        <v>76.8</v>
+        <v>82</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>102.31</v>
+        <v>348.81</v>
       </c>
       <c r="K42" t="n">
-        <v>136.76</v>
+        <v>208.28</v>
       </c>
       <c r="L42" t="n">
-        <v>170.79</v>
+        <v>406.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:27:56</t>
+          <t>07:32:31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="F43" t="n">
-        <v>8.23</v>
+        <v>8.02</v>
       </c>
       <c r="G43" t="n">
-        <v>301.8</v>
+        <v>291.9</v>
       </c>
       <c r="H43" t="n">
-        <v>84.8</v>
+        <v>86</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-151.82</v>
+        <v>-301.17</v>
       </c>
       <c r="K43" t="n">
-        <v>-331.3</v>
+        <v>-308.7</v>
       </c>
       <c r="L43" t="n">
-        <v>364.43</v>
+        <v>431.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:39:45</t>
+          <t>07:40:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="F44" t="n">
-        <v>8.25</v>
+        <v>8.51</v>
       </c>
       <c r="G44" t="n">
-        <v>286.1</v>
+        <v>292</v>
       </c>
       <c r="H44" t="n">
-        <v>72.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>17.43</v>
+        <v>-18.09</v>
       </c>
       <c r="K44" t="n">
-        <v>40.87</v>
+        <v>56.43</v>
       </c>
       <c r="L44" t="n">
-        <v>44.43</v>
+        <v>59.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:42:17</t>
+          <t>07:42:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="F45" t="n">
-        <v>7.65</v>
+        <v>8.33</v>
       </c>
       <c r="G45" t="n">
-        <v>303.1</v>
+        <v>297</v>
       </c>
       <c r="H45" t="n">
-        <v>79.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-67.52</v>
+        <v>-67.92</v>
       </c>
       <c r="K45" t="n">
-        <v>-54.26</v>
+        <v>60.28</v>
       </c>
       <c r="L45" t="n">
-        <v>86.62</v>
+        <v>90.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:43:26</t>
+          <t>07:45:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="F46" t="n">
-        <v>7.89</v>
+        <v>8.58</v>
       </c>
       <c r="G46" t="n">
-        <v>294.5</v>
+        <v>298.6</v>
       </c>
       <c r="H46" t="n">
-        <v>81.2</v>
+        <v>82</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-46.6</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>103.02</v>
+        <v>-7.55</v>
       </c>
       <c r="L46" t="n">
-        <v>113.07</v>
+        <v>73.43000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:47:41</t>
+          <t>07:49:31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="F47" t="n">
-        <v>7.62</v>
+        <v>8.01</v>
       </c>
       <c r="G47" t="n">
-        <v>297.8</v>
+        <v>300.2</v>
       </c>
       <c r="H47" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-67.56999999999999</v>
+        <v>272.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-11.22</v>
+        <v>-34.76</v>
       </c>
       <c r="L47" t="n">
-        <v>68.48999999999999</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>07:50:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="F48" t="n">
-        <v>8.84</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>301.1</v>
+        <v>310.6</v>
       </c>
       <c r="H48" t="n">
-        <v>82.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.79</v>
+        <v>-154.55</v>
       </c>
       <c r="K48" t="n">
-        <v>-94.12</v>
+        <v>-71.12</v>
       </c>
       <c r="L48" t="n">
-        <v>110.44</v>
+        <v>170.12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:51:43</t>
+          <t>07:51:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="F49" t="n">
-        <v>8.279999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="G49" t="n">
-        <v>286.2</v>
+        <v>284.9</v>
       </c>
       <c r="H49" t="n">
-        <v>80.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>192.22</v>
+        <v>112.59</v>
       </c>
       <c r="K49" t="n">
-        <v>86.3</v>
+        <v>-24.35</v>
       </c>
       <c r="L49" t="n">
-        <v>210.71</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:57:33</t>
+          <t>07:57:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="F50" t="n">
-        <v>8.43</v>
+        <v>8.1</v>
       </c>
       <c r="G50" t="n">
-        <v>290.5</v>
+        <v>296.4</v>
       </c>
       <c r="H50" t="n">
-        <v>75.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>14.93</v>
+        <v>-25.62</v>
       </c>
       <c r="K50" t="n">
-        <v>-173.71</v>
+        <v>-168.87</v>
       </c>
       <c r="L50" t="n">
-        <v>174.35</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:00:01</t>
+          <t>07:59:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.44</v>
+        <v>2.31</v>
       </c>
       <c r="F51" t="n">
-        <v>7.76</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>296.2</v>
+        <v>300.6</v>
       </c>
       <c r="H51" t="n">
-        <v>77.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-130.28</v>
+        <v>179.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-31.29</v>
+        <v>153.13</v>
       </c>
       <c r="L51" t="n">
-        <v>133.98</v>
+        <v>236.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:02:28</t>
+          <t>08:00:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="F52" t="n">
-        <v>8.73</v>
+        <v>7.76</v>
       </c>
       <c r="G52" t="n">
-        <v>297.8</v>
+        <v>294.7</v>
       </c>
       <c r="H52" t="n">
-        <v>82.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>5.54</v>
+        <v>79.33</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.43</v>
+        <v>178.86</v>
       </c>
       <c r="L52" t="n">
-        <v>45.77</v>
+        <v>195.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:06:37</t>
+          <t>08:05:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.86</v>
+        <v>1.97</v>
       </c>
       <c r="F53" t="n">
-        <v>8.65</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>312.5</v>
+        <v>283.1</v>
       </c>
       <c r="H53" t="n">
-        <v>77.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-132.27</v>
+        <v>-182.88</v>
       </c>
       <c r="K53" t="n">
-        <v>207.31</v>
+        <v>246.24</v>
       </c>
       <c r="L53" t="n">
-        <v>245.91</v>
+        <v>306.72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:07:45</t>
+          <t>08:05:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="F54" t="n">
-        <v>8.390000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="G54" t="n">
-        <v>301.6</v>
+        <v>298.5</v>
       </c>
       <c r="H54" t="n">
-        <v>80.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-291.07</v>
+        <v>-119.88</v>
       </c>
       <c r="K54" t="n">
-        <v>137.85</v>
+        <v>339.01</v>
       </c>
       <c r="L54" t="n">
-        <v>322.06</v>
+        <v>359.58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:09:00</t>
+          <t>08:07:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="F55" t="n">
-        <v>8.43</v>
+        <v>7.88</v>
       </c>
       <c r="G55" t="n">
-        <v>290.4</v>
+        <v>284.9</v>
       </c>
       <c r="H55" t="n">
-        <v>78</v>
+        <v>80.2</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>45.44</v>
+        <v>-28.79</v>
       </c>
       <c r="K55" t="n">
-        <v>-129.03</v>
+        <v>-68.55</v>
       </c>
       <c r="L55" t="n">
-        <v>136.8</v>
+        <v>74.34999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:13:34</t>
+          <t>08:11:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="F56" t="n">
-        <v>8.02</v>
+        <v>7.25</v>
       </c>
       <c r="G56" t="n">
-        <v>304.6</v>
+        <v>306.1</v>
       </c>
       <c r="H56" t="n">
-        <v>75.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-253.2</v>
+        <v>54.48</v>
       </c>
       <c r="K56" t="n">
-        <v>159.83</v>
+        <v>-27.8</v>
       </c>
       <c r="L56" t="n">
-        <v>299.43</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:15:29</t>
+          <t>08:12:19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="F57" t="n">
-        <v>8.68</v>
+        <v>8.76</v>
       </c>
       <c r="G57" t="n">
-        <v>298.9</v>
+        <v>296.2</v>
       </c>
       <c r="H57" t="n">
-        <v>77.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-552.17</v>
+        <v>-63.8</v>
       </c>
       <c r="K57" t="n">
-        <v>-337.57</v>
+        <v>89.92</v>
       </c>
       <c r="L57" t="n">
-        <v>647.1799999999999</v>
+        <v>110.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:16:25</t>
+          <t>08:14:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.32</v>
+        <v>2.65</v>
       </c>
       <c r="F58" t="n">
-        <v>7.83</v>
+        <v>8.27</v>
       </c>
       <c r="G58" t="n">
-        <v>306.5</v>
+        <v>308.1</v>
       </c>
       <c r="H58" t="n">
-        <v>81.2</v>
+        <v>84.7</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>470.43</v>
+        <v>-152.1</v>
       </c>
       <c r="K58" t="n">
-        <v>286.14</v>
+        <v>-61.77</v>
       </c>
       <c r="L58" t="n">
-        <v>550.62</v>
+        <v>164.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:27:18</t>
+          <t>08:25:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="F59" t="n">
-        <v>7.93</v>
+        <v>9.16</v>
       </c>
       <c r="G59" t="n">
-        <v>301.1</v>
+        <v>290.5</v>
       </c>
       <c r="H59" t="n">
-        <v>80.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>79.31999999999999</v>
+        <v>-66.64</v>
       </c>
       <c r="K59" t="n">
-        <v>24.39</v>
+        <v>120.96</v>
       </c>
       <c r="L59" t="n">
-        <v>82.98</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:28:59</t>
+          <t>08:27:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="F60" t="n">
-        <v>7.22</v>
+        <v>8.23</v>
       </c>
       <c r="G60" t="n">
-        <v>298.4</v>
+        <v>295.7</v>
       </c>
       <c r="H60" t="n">
-        <v>83.2</v>
+        <v>80.3</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>75.31999999999999</v>
+        <v>-12.05</v>
       </c>
       <c r="K60" t="n">
-        <v>-54.03</v>
+        <v>35.37</v>
       </c>
       <c r="L60" t="n">
-        <v>92.69</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:30:28</t>
+          <t>08:29:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="F61" t="n">
-        <v>8.48</v>
+        <v>8.65</v>
       </c>
       <c r="G61" t="n">
-        <v>301.1</v>
+        <v>320.1</v>
       </c>
       <c r="H61" t="n">
-        <v>87.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-61.72</v>
+        <v>60.51</v>
       </c>
       <c r="K61" t="n">
-        <v>27.18</v>
+        <v>-76.04000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>67.44</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:34:59</t>
+          <t>08:33:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="F62" t="n">
-        <v>8.369999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="G62" t="n">
-        <v>273.6</v>
+        <v>283.2</v>
       </c>
       <c r="H62" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>168.97</v>
+        <v>-47.51</v>
       </c>
       <c r="K62" t="n">
-        <v>31.14</v>
+        <v>44.11</v>
       </c>
       <c r="L62" t="n">
-        <v>171.82</v>
+        <v>64.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:36:34</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="F63" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="G63" t="n">
-        <v>278.7</v>
+        <v>284.5</v>
       </c>
       <c r="H63" t="n">
-        <v>77.3</v>
+        <v>87.5</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>12.46</v>
+        <v>144.38</v>
       </c>
       <c r="K63" t="n">
-        <v>128.66</v>
+        <v>28.25</v>
       </c>
       <c r="L63" t="n">
-        <v>129.27</v>
+        <v>147.12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:37:18</t>
+          <t>08:35:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="F64" t="n">
-        <v>7.62</v>
+        <v>7.82</v>
       </c>
       <c r="G64" t="n">
-        <v>310.2</v>
+        <v>294.3</v>
       </c>
       <c r="H64" t="n">
-        <v>82.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>140.91</v>
+        <v>39.21</v>
       </c>
       <c r="K64" t="n">
-        <v>26.07</v>
+        <v>-116.29</v>
       </c>
       <c r="L64" t="n">
-        <v>143.3</v>
+        <v>122.73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:42:10</t>
+          <t>08:41:25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="F65" t="n">
-        <v>8.16</v>
+        <v>8.43</v>
       </c>
       <c r="G65" t="n">
-        <v>305.1</v>
+        <v>309.5</v>
       </c>
       <c r="H65" t="n">
-        <v>83.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>126.03</v>
+        <v>-132.75</v>
       </c>
       <c r="K65" t="n">
-        <v>22.12</v>
+        <v>15.46</v>
       </c>
       <c r="L65" t="n">
-        <v>127.96</v>
+        <v>133.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:43:00</t>
+          <t>08:42:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="F66" t="n">
-        <v>7.88</v>
+        <v>7.81</v>
       </c>
       <c r="G66" t="n">
-        <v>299.7</v>
+        <v>292.4</v>
       </c>
       <c r="H66" t="n">
-        <v>80.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>5.58</v>
+        <v>-338.74</v>
       </c>
       <c r="K66" t="n">
-        <v>290.01</v>
+        <v>-147.27</v>
       </c>
       <c r="L66" t="n">
-        <v>290.07</v>
+        <v>369.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:44:33</t>
+          <t>08:45:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="F67" t="n">
-        <v>7.9</v>
+        <v>8.43</v>
       </c>
       <c r="G67" t="n">
-        <v>275.7</v>
+        <v>293.1</v>
       </c>
       <c r="H67" t="n">
-        <v>87.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.44</v>
+        <v>104.39</v>
       </c>
       <c r="K67" t="n">
-        <v>2.02</v>
+        <v>-257.78</v>
       </c>
       <c r="L67" t="n">
-        <v>3.17</v>
+        <v>278.12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:49:57</t>
+          <t>08:49:47</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="F68" t="n">
-        <v>8.609999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="G68" t="n">
-        <v>293.9</v>
+        <v>285.4</v>
       </c>
       <c r="H68" t="n">
-        <v>82.5</v>
+        <v>90.7</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-393.13</v>
+        <v>-275.02</v>
       </c>
       <c r="K68" t="n">
-        <v>-238.64</v>
+        <v>239.81</v>
       </c>
       <c r="L68" t="n">
-        <v>459.89</v>
+        <v>364.89</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:51:09</t>
+          <t>08:51:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.99</v>
+        <v>2.95</v>
       </c>
       <c r="F69" t="n">
-        <v>8.109999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="G69" t="n">
-        <v>289.8</v>
+        <v>296.2</v>
       </c>
       <c r="H69" t="n">
-        <v>68.3</v>
+        <v>72</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>244.25</v>
+        <v>36.16</v>
       </c>
       <c r="K69" t="n">
-        <v>-12.5</v>
+        <v>129.64</v>
       </c>
       <c r="L69" t="n">
-        <v>244.57</v>
+        <v>134.58</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:52:45</t>
+          <t>08:54:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="F70" t="n">
-        <v>8.369999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="G70" t="n">
-        <v>292.1</v>
+        <v>303.5</v>
       </c>
       <c r="H70" t="n">
-        <v>80.7</v>
+        <v>76.5</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>98.97</v>
+        <v>153.31</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.3</v>
+        <v>-293.79</v>
       </c>
       <c r="L70" t="n">
-        <v>143.78</v>
+        <v>331.38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:57:29</t>
+          <t>08:59:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="F71" t="n">
-        <v>7.65</v>
+        <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>290.6</v>
+        <v>301</v>
       </c>
       <c r="H71" t="n">
-        <v>78.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>904.49</v>
+        <v>35.38</v>
       </c>
       <c r="K71" t="n">
-        <v>302.8</v>
+        <v>348.49</v>
       </c>
       <c r="L71" t="n">
-        <v>953.83</v>
+        <v>350.28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:59:38</t>
+          <t>09:01:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="F72" t="n">
-        <v>7.28</v>
+        <v>8.18</v>
       </c>
       <c r="G72" t="n">
-        <v>291.9</v>
+        <v>299.1</v>
       </c>
       <c r="H72" t="n">
-        <v>88.3</v>
+        <v>86.8</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>111.17</v>
+        <v>31.24</v>
       </c>
       <c r="K72" t="n">
-        <v>491.53</v>
+        <v>257.73</v>
       </c>
       <c r="L72" t="n">
-        <v>503.94</v>
+        <v>259.61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:01:02</t>
+          <t>09:03:11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="F73" t="n">
-        <v>8.34</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>311.1</v>
+        <v>297.8</v>
       </c>
       <c r="H73" t="n">
-        <v>76.5</v>
+        <v>73</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-230.31</v>
+        <v>741.34</v>
       </c>
       <c r="K73" t="n">
-        <v>-407.51</v>
+        <v>-1.75</v>
       </c>
       <c r="L73" t="n">
-        <v>468.09</v>
+        <v>741.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:12:41</t>
+          <t>09:15:12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="F74" t="n">
-        <v>8.42</v>
+        <v>8</v>
       </c>
       <c r="G74" t="n">
-        <v>307.1</v>
+        <v>282.2</v>
       </c>
       <c r="H74" t="n">
-        <v>78.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>23.91</v>
+        <v>-50.24</v>
       </c>
       <c r="K74" t="n">
-        <v>52.7</v>
+        <v>-64.27</v>
       </c>
       <c r="L74" t="n">
-        <v>57.87</v>
+        <v>81.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:13:52</t>
+          <t>09:17:03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="F75" t="n">
-        <v>7.57</v>
+        <v>7.98</v>
       </c>
       <c r="G75" t="n">
-        <v>294.3</v>
+        <v>296.3</v>
       </c>
       <c r="H75" t="n">
-        <v>84.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>31.03</v>
+        <v>-106.68</v>
       </c>
       <c r="K75" t="n">
-        <v>-21.68</v>
+        <v>-61.18</v>
       </c>
       <c r="L75" t="n">
-        <v>37.85</v>
+        <v>122.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:16:01</t>
+          <t>09:18:01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="F76" t="n">
-        <v>8.74</v>
+        <v>8.98</v>
       </c>
       <c r="G76" t="n">
-        <v>293.7</v>
+        <v>300.1</v>
       </c>
       <c r="H76" t="n">
-        <v>82.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>59.85</v>
+        <v>26.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-19.68</v>
+        <v>30.31</v>
       </c>
       <c r="L76" t="n">
-        <v>63</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:21:48</t>
+          <t>09:22:06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="F77" t="n">
-        <v>8.4</v>
+        <v>8.16</v>
       </c>
       <c r="G77" t="n">
-        <v>295.3</v>
+        <v>296.2</v>
       </c>
       <c r="H77" t="n">
-        <v>80.7</v>
+        <v>82.2</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>32.12</v>
+        <v>-80</v>
       </c>
       <c r="K77" t="n">
-        <v>-39.67</v>
+        <v>-58.67</v>
       </c>
       <c r="L77" t="n">
-        <v>51.04</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:23:54</t>
+          <t>09:24:06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="F78" t="n">
-        <v>8.140000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="G78" t="n">
-        <v>280.3</v>
+        <v>290.9</v>
       </c>
       <c r="H78" t="n">
-        <v>89.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>84.56</v>
+        <v>-35.58</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.26</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>84.56</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:26:17</t>
+          <t>09:25:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="F79" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="G79" t="n">
-        <v>296.7</v>
+        <v>293</v>
       </c>
       <c r="H79" t="n">
-        <v>80.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-163.15</v>
+        <v>98.14</v>
       </c>
       <c r="K79" t="n">
-        <v>73.37</v>
+        <v>32.32</v>
       </c>
       <c r="L79" t="n">
-        <v>178.89</v>
+        <v>103.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:31:15</t>
+          <t>09:29:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="F80" t="n">
-        <v>8.06</v>
+        <v>8.49</v>
       </c>
       <c r="G80" t="n">
-        <v>312.5</v>
+        <v>295.7</v>
       </c>
       <c r="H80" t="n">
-        <v>75.2</v>
+        <v>79.7</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-82.98999999999999</v>
+        <v>215.89</v>
       </c>
       <c r="K80" t="n">
-        <v>21.63</v>
+        <v>77.12</v>
       </c>
       <c r="L80" t="n">
-        <v>85.77</v>
+        <v>229.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:33:34</t>
+          <t>09:32:09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.13</v>
+        <v>2.44</v>
       </c>
       <c r="F81" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="G81" t="n">
-        <v>301.1</v>
+        <v>297.3</v>
       </c>
       <c r="H81" t="n">
-        <v>85.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>21.34</v>
+        <v>-81.13</v>
       </c>
       <c r="K81" t="n">
-        <v>-449.16</v>
+        <v>7.09</v>
       </c>
       <c r="L81" t="n">
-        <v>449.67</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:35:18</t>
+          <t>09:33:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="F82" t="n">
-        <v>7.96</v>
+        <v>7.95</v>
       </c>
       <c r="G82" t="n">
-        <v>303.9</v>
+        <v>285.9</v>
       </c>
       <c r="H82" t="n">
-        <v>80</v>
+        <v>75.5</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-52.84</v>
+        <v>-107.82</v>
       </c>
       <c r="K82" t="n">
-        <v>183.42</v>
+        <v>100.09</v>
       </c>
       <c r="L82" t="n">
-        <v>190.88</v>
+        <v>147.11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:39:48</t>
+          <t>09:39:15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="F83" t="n">
-        <v>8.300000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>287.6</v>
+        <v>302.9</v>
       </c>
       <c r="H83" t="n">
-        <v>74.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-647.4299999999999</v>
+        <v>17.1</v>
       </c>
       <c r="K83" t="n">
-        <v>135.95</v>
+        <v>430.92</v>
       </c>
       <c r="L83" t="n">
-        <v>661.55</v>
+        <v>431.26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:41:53</t>
+          <t>09:41:54</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="F84" t="n">
-        <v>8.640000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="G84" t="n">
-        <v>301</v>
+        <v>298.9</v>
       </c>
       <c r="H84" t="n">
-        <v>77.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>115.99</v>
+        <v>-269.86</v>
       </c>
       <c r="K84" t="n">
-        <v>-2.56</v>
+        <v>-163.32</v>
       </c>
       <c r="L84" t="n">
-        <v>116.01</v>
+        <v>315.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:43:52</t>
+          <t>09:44:31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="F85" t="n">
-        <v>8.07</v>
+        <v>8.66</v>
       </c>
       <c r="G85" t="n">
-        <v>293.4</v>
+        <v>298.7</v>
       </c>
       <c r="H85" t="n">
-        <v>88.8</v>
+        <v>80.2</v>
       </c>
       <c r="I85" t="n">
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.27</v>
+        <v>78.17</v>
       </c>
       <c r="K85" t="n">
-        <v>-14.56</v>
+        <v>-120.99</v>
       </c>
       <c r="L85" t="n">
-        <v>15.18</v>
+        <v>144.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:48:02</t>
+          <t>09:50:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="F86" t="n">
-        <v>8.529999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>297</v>
+        <v>303.9</v>
       </c>
       <c r="H86" t="n">
-        <v>88.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>499.45</v>
+        <v>53.69</v>
       </c>
       <c r="K86" t="n">
-        <v>-213.86</v>
+        <v>432.43</v>
       </c>
       <c r="L86" t="n">
-        <v>543.3099999999999</v>
+        <v>435.75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:49:43</t>
+          <t>09:51:17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="F87" t="n">
-        <v>7.54</v>
+        <v>8.27</v>
       </c>
       <c r="G87" t="n">
-        <v>308.5</v>
+        <v>291.6</v>
       </c>
       <c r="H87" t="n">
-        <v>79.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-311</v>
+        <v>-598.3099999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-568.86</v>
+        <v>-46.26</v>
       </c>
       <c r="L87" t="n">
-        <v>648.3200000000001</v>
+        <v>600.09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:50:46</t>
+          <t>09:53:23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="F88" t="n">
-        <v>8.460000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="G88" t="n">
-        <v>307.8</v>
+        <v>288.5</v>
       </c>
       <c r="H88" t="n">
-        <v>76.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-351.3</v>
+        <v>-187.6</v>
       </c>
       <c r="K88" t="n">
-        <v>-34.84</v>
+        <v>-113.87</v>
       </c>
       <c r="L88" t="n">
-        <v>353.03</v>
+        <v>219.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-66.38</v>
+        <v>-54.76</v>
       </c>
       <c r="K14" t="n">
-        <v>19.09</v>
+        <v>15.74</v>
       </c>
       <c r="L14" t="n">
-        <v>69.06999999999999</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>28.43</v>
+        <v>18.65</v>
       </c>
       <c r="K15" t="n">
-        <v>122.62</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>125.87</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>94.06</v>
+        <v>71.84</v>
       </c>
       <c r="K16" t="n">
-        <v>48.74</v>
+        <v>37.23</v>
       </c>
       <c r="L16" t="n">
-        <v>105.94</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>75.18000000000001</v>
+        <v>62.36</v>
       </c>
       <c r="K17" t="n">
-        <v>84.95</v>
+        <v>70.47</v>
       </c>
       <c r="L17" t="n">
-        <v>113.44</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-27.34</v>
+        <v>-22.28</v>
       </c>
       <c r="K18" t="n">
-        <v>-125.31</v>
+        <v>-102.13</v>
       </c>
       <c r="L18" t="n">
-        <v>128.25</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-24.22</v>
+        <v>-24.51</v>
       </c>
       <c r="K19" t="n">
-        <v>58.51</v>
+        <v>59.22</v>
       </c>
       <c r="L19" t="n">
-        <v>63.32</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-37.98</v>
+        <v>-47.31</v>
       </c>
       <c r="K20" t="n">
-        <v>77.73</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>86.51000000000001</v>
+        <v>107.76</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-34.49</v>
+        <v>-46.77</v>
       </c>
       <c r="K21" t="n">
-        <v>73.66</v>
+        <v>99.87</v>
       </c>
       <c r="L21" t="n">
-        <v>81.34</v>
+        <v>110.28</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-53.44</v>
+        <v>-76.62</v>
       </c>
       <c r="L22" t="n">
-        <v>53.44</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>249.6</v>
+        <v>269.21</v>
       </c>
       <c r="K23" t="n">
-        <v>-28.03</v>
+        <v>-30.23</v>
       </c>
       <c r="L23" t="n">
-        <v>251.17</v>
+        <v>270.9</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>172.5</v>
+        <v>185.89</v>
       </c>
       <c r="K24" t="n">
-        <v>-174.26</v>
+        <v>-187.79</v>
       </c>
       <c r="L24" t="n">
-        <v>245.2</v>
+        <v>264.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>176.43</v>
+        <v>157.03</v>
       </c>
       <c r="K25" t="n">
-        <v>-130.88</v>
+        <v>-116.49</v>
       </c>
       <c r="L25" t="n">
-        <v>219.68</v>
+        <v>195.52</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-116.08</v>
+        <v>-172.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-50.58</v>
+        <v>-75.06</v>
       </c>
       <c r="L26" t="n">
-        <v>126.63</v>
+        <v>187.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>341.27</v>
+        <v>295.55</v>
       </c>
       <c r="K27" t="n">
-        <v>457.38</v>
+        <v>396.1</v>
       </c>
       <c r="L27" t="n">
-        <v>570.67</v>
+        <v>494.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>120.27</v>
+        <v>236.71</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.15</v>
+        <v>-8.18</v>
       </c>
       <c r="L28" t="n">
-        <v>120.34</v>
+        <v>236.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>125.64</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>5.29</v>
+        <v>3.15</v>
       </c>
       <c r="L29" t="n">
-        <v>125.75</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.42</v>
+        <v>-38.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.51</v>
+        <v>-3.02</v>
       </c>
       <c r="L30" t="n">
-        <v>44.55</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-150.76</v>
+        <v>-104.29</v>
       </c>
       <c r="K31" t="n">
-        <v>118.91</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>192.01</v>
+        <v>132.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-173.35</v>
+        <v>-132.19</v>
       </c>
       <c r="K32" t="n">
-        <v>154.32</v>
+        <v>117.68</v>
       </c>
       <c r="L32" t="n">
-        <v>232.09</v>
+        <v>176.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>9.720000000000001</v>
+        <v>6.58</v>
       </c>
       <c r="K33" t="n">
-        <v>-167.45</v>
+        <v>-113.36</v>
       </c>
       <c r="L33" t="n">
-        <v>167.73</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-70.37</v>
+        <v>-63.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-93.76000000000001</v>
+        <v>-84.61</v>
       </c>
       <c r="L34" t="n">
-        <v>117.23</v>
+        <v>105.79</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>94.87</v>
+        <v>76.33</v>
       </c>
       <c r="K35" t="n">
-        <v>171</v>
+        <v>137.57</v>
       </c>
       <c r="L35" t="n">
-        <v>195.55</v>
+        <v>157.33</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>23.7</v>
+        <v>18.53</v>
       </c>
       <c r="K36" t="n">
-        <v>-164.42</v>
+        <v>-128.55</v>
       </c>
       <c r="L36" t="n">
-        <v>166.12</v>
+        <v>129.88</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-56.84</v>
+        <v>-54.29</v>
       </c>
       <c r="K37" t="n">
-        <v>182.9</v>
+        <v>174.7</v>
       </c>
       <c r="L37" t="n">
-        <v>191.53</v>
+        <v>182.94</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>66.31</v>
+        <v>95.28</v>
       </c>
       <c r="K38" t="n">
-        <v>-43.91</v>
+        <v>-63.09</v>
       </c>
       <c r="L38" t="n">
-        <v>79.53</v>
+        <v>114.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-55.8</v>
+        <v>-57.62</v>
       </c>
       <c r="K39" t="n">
-        <v>-339.46</v>
+        <v>-350.51</v>
       </c>
       <c r="L39" t="n">
-        <v>344.01</v>
+        <v>355.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>93.52</v>
+        <v>81.7</v>
       </c>
       <c r="K40" t="n">
-        <v>-355.28</v>
+        <v>-310.37</v>
       </c>
       <c r="L40" t="n">
-        <v>367.39</v>
+        <v>320.95</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>146.62</v>
+        <v>228.32</v>
       </c>
       <c r="K41" t="n">
-        <v>52.03</v>
+        <v>81.03</v>
       </c>
       <c r="L41" t="n">
-        <v>155.58</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>348.81</v>
+        <v>370.43</v>
       </c>
       <c r="K42" t="n">
-        <v>208.28</v>
+        <v>221.19</v>
       </c>
       <c r="L42" t="n">
-        <v>406.26</v>
+        <v>431.44</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-301.17</v>
+        <v>-279.59</v>
       </c>
       <c r="K43" t="n">
-        <v>-308.7</v>
+        <v>-286.57</v>
       </c>
       <c r="L43" t="n">
-        <v>431.28</v>
+        <v>400.37</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.09</v>
+        <v>-17.65</v>
       </c>
       <c r="K44" t="n">
-        <v>56.43</v>
+        <v>55.07</v>
       </c>
       <c r="L44" t="n">
-        <v>59.26</v>
+        <v>57.83</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-67.92</v>
+        <v>-48.81</v>
       </c>
       <c r="K45" t="n">
-        <v>60.28</v>
+        <v>43.32</v>
       </c>
       <c r="L45" t="n">
-        <v>90.81</v>
+        <v>65.26000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>73.04000000000001</v>
+        <v>57.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.55</v>
+        <v>-5.94</v>
       </c>
       <c r="L46" t="n">
-        <v>73.43000000000001</v>
+        <v>57.77</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>272.89</v>
+        <v>183.25</v>
       </c>
       <c r="K47" t="n">
-        <v>-34.76</v>
+        <v>-23.34</v>
       </c>
       <c r="L47" t="n">
-        <v>275.09</v>
+        <v>184.74</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-154.55</v>
+        <v>-114.2</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.12</v>
+        <v>-52.55</v>
       </c>
       <c r="L48" t="n">
-        <v>170.12</v>
+        <v>125.72</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>112.59</v>
+        <v>95.69</v>
       </c>
       <c r="K49" t="n">
-        <v>-24.35</v>
+        <v>-20.69</v>
       </c>
       <c r="L49" t="n">
-        <v>115.19</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-25.62</v>
+        <v>-21.56</v>
       </c>
       <c r="K50" t="n">
-        <v>-168.87</v>
+        <v>-142.13</v>
       </c>
       <c r="L50" t="n">
-        <v>170.8</v>
+        <v>143.76</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>179.97</v>
+        <v>167.28</v>
       </c>
       <c r="K51" t="n">
-        <v>153.13</v>
+        <v>142.33</v>
       </c>
       <c r="L51" t="n">
-        <v>236.3</v>
+        <v>219.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>79.33</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>178.86</v>
+        <v>172.16</v>
       </c>
       <c r="L52" t="n">
-        <v>195.66</v>
+        <v>188.33</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-182.88</v>
+        <v>-172.07</v>
       </c>
       <c r="K53" t="n">
-        <v>246.24</v>
+        <v>231.68</v>
       </c>
       <c r="L53" t="n">
-        <v>306.72</v>
+        <v>288.59</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-119.88</v>
+        <v>-115.96</v>
       </c>
       <c r="K54" t="n">
-        <v>339.01</v>
+        <v>327.9</v>
       </c>
       <c r="L54" t="n">
-        <v>359.58</v>
+        <v>347.8</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-28.79</v>
+        <v>-40.46</v>
       </c>
       <c r="K55" t="n">
-        <v>-68.55</v>
+        <v>-96.36</v>
       </c>
       <c r="L55" t="n">
-        <v>74.34999999999999</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>54.48</v>
+        <v>148.28</v>
       </c>
       <c r="K56" t="n">
-        <v>-27.8</v>
+        <v>-75.67</v>
       </c>
       <c r="L56" t="n">
-        <v>61.16</v>
+        <v>166.47</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-63.8</v>
+        <v>-112.2</v>
       </c>
       <c r="K57" t="n">
-        <v>89.92</v>
+        <v>158.14</v>
       </c>
       <c r="L57" t="n">
-        <v>110.26</v>
+        <v>193.9</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-152.1</v>
+        <v>-229.89</v>
       </c>
       <c r="K58" t="n">
-        <v>-61.77</v>
+        <v>-93.36</v>
       </c>
       <c r="L58" t="n">
-        <v>164.17</v>
+        <v>248.12</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-66.64</v>
+        <v>-46.02</v>
       </c>
       <c r="K59" t="n">
-        <v>120.96</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>138.1</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.05</v>
+        <v>-15.23</v>
       </c>
       <c r="K60" t="n">
-        <v>35.37</v>
+        <v>44.7</v>
       </c>
       <c r="L60" t="n">
-        <v>37.37</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>60.51</v>
+        <v>57.18</v>
       </c>
       <c r="K61" t="n">
-        <v>-76.04000000000001</v>
+        <v>-71.86</v>
       </c>
       <c r="L61" t="n">
-        <v>97.18000000000001</v>
+        <v>91.84</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-47.51</v>
+        <v>-52</v>
       </c>
       <c r="K62" t="n">
-        <v>44.11</v>
+        <v>48.27</v>
       </c>
       <c r="L62" t="n">
-        <v>64.83</v>
+        <v>70.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>144.38</v>
+        <v>100.85</v>
       </c>
       <c r="K63" t="n">
-        <v>28.25</v>
+        <v>19.73</v>
       </c>
       <c r="L63" t="n">
-        <v>147.12</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>39.21</v>
+        <v>31.97</v>
       </c>
       <c r="K64" t="n">
-        <v>-116.29</v>
+        <v>-94.81</v>
       </c>
       <c r="L64" t="n">
-        <v>122.73</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-132.75</v>
+        <v>-135.87</v>
       </c>
       <c r="K65" t="n">
-        <v>15.46</v>
+        <v>15.82</v>
       </c>
       <c r="L65" t="n">
-        <v>133.65</v>
+        <v>136.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-338.74</v>
+        <v>-256.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-147.27</v>
+        <v>-111.31</v>
       </c>
       <c r="L66" t="n">
-        <v>369.37</v>
+        <v>279.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>104.39</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-257.78</v>
+        <v>-239.98</v>
       </c>
       <c r="L67" t="n">
-        <v>278.12</v>
+        <v>258.91</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-275.02</v>
+        <v>-206.92</v>
       </c>
       <c r="K68" t="n">
-        <v>239.81</v>
+        <v>180.42</v>
       </c>
       <c r="L68" t="n">
-        <v>364.89</v>
+        <v>274.53</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>36.16</v>
+        <v>56.82</v>
       </c>
       <c r="K69" t="n">
-        <v>129.64</v>
+        <v>203.69</v>
       </c>
       <c r="L69" t="n">
-        <v>134.58</v>
+        <v>211.47</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>153.31</v>
+        <v>150.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-293.79</v>
+        <v>-288.03</v>
       </c>
       <c r="L70" t="n">
-        <v>331.38</v>
+        <v>324.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>35.38</v>
+        <v>38.54</v>
       </c>
       <c r="K71" t="n">
-        <v>348.49</v>
+        <v>379.62</v>
       </c>
       <c r="L71" t="n">
-        <v>350.28</v>
+        <v>381.58</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>31.24</v>
+        <v>41.24</v>
       </c>
       <c r="K72" t="n">
-        <v>257.73</v>
+        <v>340.14</v>
       </c>
       <c r="L72" t="n">
-        <v>259.61</v>
+        <v>342.63</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>741.34</v>
+        <v>762.4</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.75</v>
+        <v>-1.8</v>
       </c>
       <c r="L73" t="n">
-        <v>741.34</v>
+        <v>762.4</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.24</v>
+        <v>-36.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-64.27</v>
+        <v>-47.12</v>
       </c>
       <c r="L74" t="n">
-        <v>81.58</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-106.68</v>
+        <v>-96.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-61.18</v>
+        <v>-55.42</v>
       </c>
       <c r="L75" t="n">
-        <v>122.98</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>26.76</v>
+        <v>29.15</v>
       </c>
       <c r="K76" t="n">
-        <v>30.31</v>
+        <v>33.01</v>
       </c>
       <c r="L76" t="n">
-        <v>40.43</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-80</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-58.67</v>
+        <v>-47.13</v>
       </c>
       <c r="L77" t="n">
-        <v>99.20999999999999</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.58</v>
+        <v>-35.94</v>
       </c>
       <c r="K78" t="n">
-        <v>-73.76000000000001</v>
+        <v>-74.52</v>
       </c>
       <c r="L78" t="n">
-        <v>81.89</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>98.14</v>
+        <v>95.33</v>
       </c>
       <c r="K79" t="n">
-        <v>32.32</v>
+        <v>31.4</v>
       </c>
       <c r="L79" t="n">
-        <v>103.33</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>215.89</v>
+        <v>244.27</v>
       </c>
       <c r="K80" t="n">
-        <v>77.12</v>
+        <v>87.27</v>
       </c>
       <c r="L80" t="n">
-        <v>229.25</v>
+        <v>259.39</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-81.13</v>
+        <v>-127.75</v>
       </c>
       <c r="K81" t="n">
-        <v>7.09</v>
+        <v>11.17</v>
       </c>
       <c r="L81" t="n">
-        <v>81.44</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-107.82</v>
+        <v>-102.58</v>
       </c>
       <c r="K82" t="n">
-        <v>100.09</v>
+        <v>95.23</v>
       </c>
       <c r="L82" t="n">
-        <v>147.11</v>
+        <v>139.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>17.1</v>
+        <v>14.82</v>
       </c>
       <c r="K83" t="n">
-        <v>430.92</v>
+        <v>373.53</v>
       </c>
       <c r="L83" t="n">
-        <v>431.26</v>
+        <v>373.82</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-269.86</v>
+        <v>-219.7</v>
       </c>
       <c r="K84" t="n">
-        <v>-163.32</v>
+        <v>-132.97</v>
       </c>
       <c r="L84" t="n">
-        <v>315.43</v>
+        <v>256.8</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>78.17</v>
+        <v>108.74</v>
       </c>
       <c r="K85" t="n">
-        <v>-120.99</v>
+        <v>-168.31</v>
       </c>
       <c r="L85" t="n">
-        <v>144.04</v>
+        <v>200.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>53.69</v>
+        <v>58.83</v>
       </c>
       <c r="K86" t="n">
-        <v>432.43</v>
+        <v>473.82</v>
       </c>
       <c r="L86" t="n">
-        <v>435.75</v>
+        <v>477.46</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-598.3099999999999</v>
+        <v>-521.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-46.26</v>
+        <v>-40.29</v>
       </c>
       <c r="L87" t="n">
-        <v>600.09</v>
+        <v>522.6900000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.6</v>
+        <v>-248.93</v>
       </c>
       <c r="K88" t="n">
-        <v>-113.87</v>
+        <v>-151.09</v>
       </c>
       <c r="L88" t="n">
-        <v>219.46</v>
+        <v>291.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-54.76</v>
+        <v>-51.45</v>
       </c>
       <c r="K14" t="n">
-        <v>15.74</v>
+        <v>14.79</v>
       </c>
       <c r="L14" t="n">
-        <v>56.98</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>18.65</v>
+        <v>18.06</v>
       </c>
       <c r="K15" t="n">
-        <v>80.43000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="L15" t="n">
-        <v>82.56</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>71.84</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>37.23</v>
+        <v>36.37</v>
       </c>
       <c r="L16" t="n">
-        <v>80.91</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>62.36</v>
+        <v>54.58</v>
       </c>
       <c r="K17" t="n">
-        <v>70.47</v>
+        <v>61.68</v>
       </c>
       <c r="L17" t="n">
-        <v>94.09999999999999</v>
+        <v>82.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-22.28</v>
+        <v>-20.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-102.13</v>
+        <v>-95.34999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>104.53</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-24.51</v>
+        <v>-22.26</v>
       </c>
       <c r="K19" t="n">
-        <v>59.22</v>
+        <v>53.78</v>
       </c>
       <c r="L19" t="n">
-        <v>64.09999999999999</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-47.31</v>
+        <v>-34.67</v>
       </c>
       <c r="K20" t="n">
-        <v>96.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="L20" t="n">
-        <v>107.76</v>
+        <v>78.95999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-46.77</v>
+        <v>-34.84</v>
       </c>
       <c r="K21" t="n">
-        <v>99.87</v>
+        <v>74.39</v>
       </c>
       <c r="L21" t="n">
-        <v>110.28</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="K22" t="n">
-        <v>-76.62</v>
+        <v>-63.43</v>
       </c>
       <c r="L22" t="n">
-        <v>76.62</v>
+        <v>63.43</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>269.21</v>
+        <v>158.85</v>
       </c>
       <c r="K23" t="n">
-        <v>-30.23</v>
+        <v>-17.84</v>
       </c>
       <c r="L23" t="n">
-        <v>270.9</v>
+        <v>159.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>185.89</v>
+        <v>117.76</v>
       </c>
       <c r="K24" t="n">
-        <v>-187.79</v>
+        <v>-118.97</v>
       </c>
       <c r="L24" t="n">
-        <v>264.23</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>157.03</v>
+        <v>118.55</v>
       </c>
       <c r="K25" t="n">
-        <v>-116.49</v>
+        <v>-87.94</v>
       </c>
       <c r="L25" t="n">
-        <v>195.52</v>
+        <v>147.61</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-172.28</v>
+        <v>-122.14</v>
       </c>
       <c r="K26" t="n">
-        <v>-75.06</v>
+        <v>-53.22</v>
       </c>
       <c r="L26" t="n">
-        <v>187.92</v>
+        <v>133.23</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>295.55</v>
+        <v>191.61</v>
       </c>
       <c r="K27" t="n">
-        <v>396.1</v>
+        <v>256.8</v>
       </c>
       <c r="L27" t="n">
-        <v>494.21</v>
+        <v>320.41</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>236.71</v>
+        <v>135.44</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.18</v>
+        <v>-4.68</v>
       </c>
       <c r="L28" t="n">
-        <v>236.85</v>
+        <v>135.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>74.76000000000001</v>
+        <v>78.56</v>
       </c>
       <c r="K29" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="L29" t="n">
-        <v>74.83</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.2</v>
+        <v>-43.61</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.02</v>
+        <v>-3.45</v>
       </c>
       <c r="L30" t="n">
-        <v>38.32</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-104.29</v>
+        <v>-96.05</v>
       </c>
       <c r="K31" t="n">
-        <v>82.26000000000001</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>132.83</v>
+        <v>122.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-132.19</v>
+        <v>-109.57</v>
       </c>
       <c r="K32" t="n">
-        <v>117.68</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>176.98</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>6.58</v>
+        <v>6.77</v>
       </c>
       <c r="K33" t="n">
-        <v>-113.36</v>
+        <v>-116.64</v>
       </c>
       <c r="L33" t="n">
-        <v>113.55</v>
+        <v>116.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-63.51</v>
+        <v>-54.79</v>
       </c>
       <c r="K34" t="n">
-        <v>-84.61</v>
+        <v>-73</v>
       </c>
       <c r="L34" t="n">
-        <v>105.79</v>
+        <v>91.27</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>76.33</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>137.57</v>
+        <v>121.85</v>
       </c>
       <c r="L35" t="n">
-        <v>157.33</v>
+        <v>139.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>18.53</v>
+        <v>16.2</v>
       </c>
       <c r="K36" t="n">
-        <v>-128.55</v>
+        <v>-112.39</v>
       </c>
       <c r="L36" t="n">
-        <v>129.88</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-54.29</v>
+        <v>-36.36</v>
       </c>
       <c r="K37" t="n">
-        <v>174.7</v>
+        <v>117.01</v>
       </c>
       <c r="L37" t="n">
-        <v>182.94</v>
+        <v>122.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>95.28</v>
+        <v>73.09</v>
       </c>
       <c r="K38" t="n">
-        <v>-63.09</v>
+        <v>-48.4</v>
       </c>
       <c r="L38" t="n">
-        <v>114.27</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-57.62</v>
+        <v>-35.42</v>
       </c>
       <c r="K39" t="n">
-        <v>-350.51</v>
+        <v>-215.49</v>
       </c>
       <c r="L39" t="n">
-        <v>355.22</v>
+        <v>218.38</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>81.7</v>
+        <v>53.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-310.37</v>
+        <v>-202.94</v>
       </c>
       <c r="L40" t="n">
-        <v>320.95</v>
+        <v>209.85</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>228.32</v>
+        <v>128.81</v>
       </c>
       <c r="K41" t="n">
-        <v>81.03</v>
+        <v>45.71</v>
       </c>
       <c r="L41" t="n">
-        <v>242.27</v>
+        <v>136.68</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>370.43</v>
+        <v>209.44</v>
       </c>
       <c r="K42" t="n">
-        <v>221.19</v>
+        <v>125.06</v>
       </c>
       <c r="L42" t="n">
-        <v>431.44</v>
+        <v>243.93</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-279.59</v>
+        <v>-181.56</v>
       </c>
       <c r="K43" t="n">
-        <v>-286.57</v>
+        <v>-186.1</v>
       </c>
       <c r="L43" t="n">
-        <v>400.37</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-17.65</v>
+        <v>-16.16</v>
       </c>
       <c r="K44" t="n">
-        <v>55.07</v>
+        <v>50.41</v>
       </c>
       <c r="L44" t="n">
-        <v>57.83</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-48.81</v>
+        <v>-50.1</v>
       </c>
       <c r="K45" t="n">
-        <v>43.32</v>
+        <v>44.47</v>
       </c>
       <c r="L45" t="n">
-        <v>65.26000000000001</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>57.46</v>
+        <v>61.75</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.94</v>
+        <v>-6.38</v>
       </c>
       <c r="L46" t="n">
-        <v>57.77</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>183.25</v>
+        <v>174.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.34</v>
+        <v>-22.21</v>
       </c>
       <c r="L47" t="n">
-        <v>184.74</v>
+        <v>175.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-114.2</v>
+        <v>-104.11</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.55</v>
+        <v>-47.91</v>
       </c>
       <c r="L48" t="n">
-        <v>125.72</v>
+        <v>114.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>95.69</v>
+        <v>80.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-20.69</v>
+        <v>-17.34</v>
       </c>
       <c r="L49" t="n">
-        <v>97.90000000000001</v>
+        <v>82.04000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.56</v>
+        <v>-17.64</v>
       </c>
       <c r="K50" t="n">
-        <v>-142.13</v>
+        <v>-116.3</v>
       </c>
       <c r="L50" t="n">
-        <v>143.76</v>
+        <v>117.63</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>167.28</v>
+        <v>117.27</v>
       </c>
       <c r="K51" t="n">
-        <v>142.33</v>
+        <v>99.78</v>
       </c>
       <c r="L51" t="n">
-        <v>219.63</v>
+        <v>153.97</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>76.34999999999999</v>
+        <v>55.29</v>
       </c>
       <c r="K52" t="n">
-        <v>172.16</v>
+        <v>124.67</v>
       </c>
       <c r="L52" t="n">
-        <v>188.33</v>
+        <v>136.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-172.07</v>
+        <v>-106.4</v>
       </c>
       <c r="K53" t="n">
-        <v>231.68</v>
+        <v>143.26</v>
       </c>
       <c r="L53" t="n">
-        <v>288.59</v>
+        <v>178.45</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-115.96</v>
+        <v>-76.31</v>
       </c>
       <c r="K54" t="n">
-        <v>327.9</v>
+        <v>215.79</v>
       </c>
       <c r="L54" t="n">
-        <v>347.8</v>
+        <v>228.89</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-40.46</v>
+        <v>-32.66</v>
       </c>
       <c r="K55" t="n">
-        <v>-96.36</v>
+        <v>-77.79000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>104.51</v>
+        <v>84.37</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>148.28</v>
+        <v>90.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-75.67</v>
+        <v>-46.21</v>
       </c>
       <c r="L56" t="n">
-        <v>166.47</v>
+        <v>101.67</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-112.2</v>
+        <v>-74.7</v>
       </c>
       <c r="K57" t="n">
-        <v>158.14</v>
+        <v>105.29</v>
       </c>
       <c r="L57" t="n">
-        <v>193.9</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-229.89</v>
+        <v>-149.41</v>
       </c>
       <c r="K58" t="n">
-        <v>-93.36</v>
+        <v>-60.68</v>
       </c>
       <c r="L58" t="n">
-        <v>248.12</v>
+        <v>161.26</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-46.02</v>
+        <v>-47.59</v>
       </c>
       <c r="K59" t="n">
-        <v>83.54000000000001</v>
+        <v>86.39</v>
       </c>
       <c r="L59" t="n">
-        <v>95.38</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.23</v>
+        <v>-14.88</v>
       </c>
       <c r="K60" t="n">
-        <v>44.7</v>
+        <v>43.67</v>
       </c>
       <c r="L60" t="n">
-        <v>47.23</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>57.18</v>
+        <v>52.02</v>
       </c>
       <c r="K61" t="n">
-        <v>-71.86</v>
+        <v>-65.37</v>
       </c>
       <c r="L61" t="n">
-        <v>91.84</v>
+        <v>83.54000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-52</v>
+        <v>-43.98</v>
       </c>
       <c r="K62" t="n">
-        <v>48.27</v>
+        <v>40.83</v>
       </c>
       <c r="L62" t="n">
-        <v>70.95</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>100.85</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>19.73</v>
+        <v>19.09</v>
       </c>
       <c r="L63" t="n">
-        <v>102.76</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>31.97</v>
+        <v>30.87</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.81</v>
+        <v>-91.55</v>
       </c>
       <c r="L64" t="n">
-        <v>100.06</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-135.87</v>
+        <v>-109.78</v>
       </c>
       <c r="K65" t="n">
-        <v>15.82</v>
+        <v>12.79</v>
       </c>
       <c r="L65" t="n">
-        <v>136.79</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-256.02</v>
+        <v>-186.45</v>
       </c>
       <c r="K66" t="n">
-        <v>-111.31</v>
+        <v>-81.06</v>
       </c>
       <c r="L66" t="n">
-        <v>279.17</v>
+        <v>203.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>97.18000000000001</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-239.98</v>
+        <v>-164.86</v>
       </c>
       <c r="L67" t="n">
-        <v>258.91</v>
+        <v>177.86</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-206.92</v>
+        <v>-164.23</v>
       </c>
       <c r="K68" t="n">
-        <v>180.42</v>
+        <v>143.2</v>
       </c>
       <c r="L68" t="n">
-        <v>274.53</v>
+        <v>217.9</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>56.82</v>
+        <v>36.59</v>
       </c>
       <c r="K69" t="n">
-        <v>203.69</v>
+        <v>131.17</v>
       </c>
       <c r="L69" t="n">
-        <v>211.47</v>
+        <v>136.18</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>150.3</v>
+        <v>94.87</v>
       </c>
       <c r="K70" t="n">
-        <v>-288.03</v>
+        <v>-181.81</v>
       </c>
       <c r="L70" t="n">
-        <v>324.89</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>38.54</v>
+        <v>22.18</v>
       </c>
       <c r="K71" t="n">
-        <v>379.62</v>
+        <v>218.53</v>
       </c>
       <c r="L71" t="n">
-        <v>381.58</v>
+        <v>219.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>41.24</v>
+        <v>24.01</v>
       </c>
       <c r="K72" t="n">
-        <v>340.14</v>
+        <v>198.02</v>
       </c>
       <c r="L72" t="n">
-        <v>342.63</v>
+        <v>199.47</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>762.4</v>
+        <v>407.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.8</v>
+        <v>-0.96</v>
       </c>
       <c r="L73" t="n">
-        <v>762.4</v>
+        <v>407.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-36.83</v>
+        <v>-40.04</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.12</v>
+        <v>-51.23</v>
       </c>
       <c r="L74" t="n">
-        <v>59.81</v>
+        <v>65.03</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-96.64</v>
+        <v>-82.13</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.42</v>
+        <v>-47.1</v>
       </c>
       <c r="L75" t="n">
-        <v>111.4</v>
+        <v>94.68000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>29.15</v>
+        <v>28.12</v>
       </c>
       <c r="K76" t="n">
-        <v>33.01</v>
+        <v>31.84</v>
       </c>
       <c r="L76" t="n">
-        <v>44.03</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-64.26000000000001</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.13</v>
+        <v>-48.55</v>
       </c>
       <c r="L77" t="n">
-        <v>79.69</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.94</v>
+        <v>-30.36</v>
       </c>
       <c r="K78" t="n">
-        <v>-74.52</v>
+        <v>-62.94</v>
       </c>
       <c r="L78" t="n">
-        <v>82.73</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>95.33</v>
+        <v>83.48</v>
       </c>
       <c r="K79" t="n">
-        <v>31.4</v>
+        <v>27.49</v>
       </c>
       <c r="L79" t="n">
-        <v>100.37</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>244.27</v>
+        <v>159.35</v>
       </c>
       <c r="K80" t="n">
-        <v>87.27</v>
+        <v>56.93</v>
       </c>
       <c r="L80" t="n">
-        <v>259.39</v>
+        <v>169.21</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-127.75</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>11.17</v>
+        <v>7.69</v>
       </c>
       <c r="L81" t="n">
-        <v>128.24</v>
+        <v>88.31999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-102.58</v>
+        <v>-85.98999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>95.23</v>
+        <v>79.83</v>
       </c>
       <c r="L82" t="n">
-        <v>139.97</v>
+        <v>117.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>14.82</v>
+        <v>9.76</v>
       </c>
       <c r="K83" t="n">
-        <v>373.53</v>
+        <v>245.98</v>
       </c>
       <c r="L83" t="n">
-        <v>373.82</v>
+        <v>246.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-219.7</v>
+        <v>-171.24</v>
       </c>
       <c r="K84" t="n">
-        <v>-132.97</v>
+        <v>-103.64</v>
       </c>
       <c r="L84" t="n">
-        <v>256.8</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>108.74</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-168.31</v>
+        <v>-103.2</v>
       </c>
       <c r="L85" t="n">
-        <v>200.38</v>
+        <v>122.87</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>58.83</v>
+        <v>35.33</v>
       </c>
       <c r="K86" t="n">
-        <v>473.82</v>
+        <v>284.53</v>
       </c>
       <c r="L86" t="n">
-        <v>477.46</v>
+        <v>286.72</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-521.14</v>
+        <v>-335.01</v>
       </c>
       <c r="K87" t="n">
-        <v>-40.29</v>
+        <v>-25.9</v>
       </c>
       <c r="L87" t="n">
-        <v>522.6900000000001</v>
+        <v>336.01</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-248.93</v>
+        <v>-151.76</v>
       </c>
       <c r="K88" t="n">
-        <v>-151.09</v>
+        <v>-92.12</v>
       </c>
       <c r="L88" t="n">
-        <v>291.2</v>
+        <v>177.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.45</v>
+        <v>-52.52</v>
       </c>
       <c r="K14" t="n">
-        <v>14.79</v>
+        <v>15.1</v>
       </c>
       <c r="L14" t="n">
-        <v>53.54</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>18.06</v>
+        <v>18.05</v>
       </c>
       <c r="K15" t="n">
-        <v>77.92</v>
+        <v>77.84</v>
       </c>
       <c r="L15" t="n">
-        <v>79.98</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>70.18000000000001</v>
+        <v>71.91</v>
       </c>
       <c r="K16" t="n">
-        <v>36.37</v>
+        <v>37.26</v>
       </c>
       <c r="L16" t="n">
-        <v>79.05</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>54.58</v>
+        <v>56.4</v>
       </c>
       <c r="K17" t="n">
-        <v>61.68</v>
+        <v>63.73</v>
       </c>
       <c r="L17" t="n">
-        <v>82.36</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.8</v>
+        <v>-21.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-95.34999999999999</v>
+        <v>-100.06</v>
       </c>
       <c r="L18" t="n">
-        <v>97.59999999999999</v>
+        <v>102.41</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-22.26</v>
+        <v>-23.1</v>
       </c>
       <c r="K19" t="n">
-        <v>53.78</v>
+        <v>55.82</v>
       </c>
       <c r="L19" t="n">
-        <v>58.2</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-34.67</v>
+        <v>-38.28</v>
       </c>
       <c r="K20" t="n">
-        <v>70.95</v>
+        <v>78.33</v>
       </c>
       <c r="L20" t="n">
-        <v>78.95999999999999</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-34.84</v>
+        <v>-38.24</v>
       </c>
       <c r="K21" t="n">
-        <v>74.39</v>
+        <v>81.67</v>
       </c>
       <c r="L21" t="n">
-        <v>82.15000000000001</v>
+        <v>90.18000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="K22" t="n">
-        <v>-63.43</v>
+        <v>-68.64</v>
       </c>
       <c r="L22" t="n">
-        <v>63.43</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>158.85</v>
+        <v>182.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-17.84</v>
+        <v>-20.51</v>
       </c>
       <c r="L23" t="n">
-        <v>159.85</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>117.76</v>
+        <v>134.31</v>
       </c>
       <c r="K24" t="n">
-        <v>-118.97</v>
+        <v>-135.69</v>
       </c>
       <c r="L24" t="n">
-        <v>167.4</v>
+        <v>190.92</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>118.55</v>
+        <v>132.86</v>
       </c>
       <c r="K25" t="n">
-        <v>-87.94</v>
+        <v>-98.56</v>
       </c>
       <c r="L25" t="n">
-        <v>147.61</v>
+        <v>165.42</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-122.14</v>
+        <v>-136.13</v>
       </c>
       <c r="K26" t="n">
-        <v>-53.22</v>
+        <v>-59.32</v>
       </c>
       <c r="L26" t="n">
-        <v>133.23</v>
+        <v>148.49</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>191.61</v>
+        <v>218.36</v>
       </c>
       <c r="K27" t="n">
-        <v>256.8</v>
+        <v>292.65</v>
       </c>
       <c r="L27" t="n">
-        <v>320.41</v>
+        <v>365.13</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>135.44</v>
+        <v>156.45</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.68</v>
+        <v>-5.4</v>
       </c>
       <c r="L28" t="n">
-        <v>135.52</v>
+        <v>156.55</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>78.56</v>
+        <v>78.61</v>
       </c>
       <c r="K29" t="n">
         <v>3.31</v>
       </c>
       <c r="L29" t="n">
-        <v>78.63</v>
+        <v>78.68000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.61</v>
+        <v>-44.07</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.45</v>
+        <v>-3.49</v>
       </c>
       <c r="L30" t="n">
-        <v>43.75</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-96.05</v>
+        <v>-98</v>
       </c>
       <c r="K31" t="n">
-        <v>75.76000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>122.34</v>
+        <v>124.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-109.57</v>
+        <v>-115.33</v>
       </c>
       <c r="K32" t="n">
-        <v>97.54000000000001</v>
+        <v>102.66</v>
       </c>
       <c r="L32" t="n">
-        <v>146.7</v>
+        <v>154.4</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>6.77</v>
+        <v>6.95</v>
       </c>
       <c r="K33" t="n">
-        <v>-116.64</v>
+        <v>-119.73</v>
       </c>
       <c r="L33" t="n">
-        <v>116.83</v>
+        <v>119.93</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-54.79</v>
+        <v>-57.56</v>
       </c>
       <c r="K34" t="n">
-        <v>-73</v>
+        <v>-76.68000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>91.27</v>
+        <v>95.88</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>67.59999999999999</v>
+        <v>72.77</v>
       </c>
       <c r="K35" t="n">
-        <v>121.85</v>
+        <v>131.16</v>
       </c>
       <c r="L35" t="n">
-        <v>139.35</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>16.2</v>
+        <v>17.42</v>
       </c>
       <c r="K36" t="n">
-        <v>-112.39</v>
+        <v>-120.84</v>
       </c>
       <c r="L36" t="n">
-        <v>113.55</v>
+        <v>122.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-36.36</v>
+        <v>-40.28</v>
       </c>
       <c r="K37" t="n">
-        <v>117.01</v>
+        <v>129.6</v>
       </c>
       <c r="L37" t="n">
-        <v>122.53</v>
+        <v>135.71</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>73.09</v>
+        <v>81.75</v>
       </c>
       <c r="K38" t="n">
-        <v>-48.4</v>
+        <v>-54.13</v>
       </c>
       <c r="L38" t="n">
-        <v>87.66</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-35.42</v>
+        <v>-40.17</v>
       </c>
       <c r="K39" t="n">
-        <v>-215.49</v>
+        <v>-244.37</v>
       </c>
       <c r="L39" t="n">
-        <v>218.38</v>
+        <v>247.65</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>53.42</v>
+        <v>60.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-202.94</v>
+        <v>-229.53</v>
       </c>
       <c r="L40" t="n">
-        <v>209.85</v>
+        <v>237.35</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>128.81</v>
+        <v>148.92</v>
       </c>
       <c r="K41" t="n">
-        <v>45.71</v>
+        <v>52.85</v>
       </c>
       <c r="L41" t="n">
-        <v>136.68</v>
+        <v>158.01</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>209.44</v>
+        <v>242.26</v>
       </c>
       <c r="K42" t="n">
-        <v>125.06</v>
+        <v>144.66</v>
       </c>
       <c r="L42" t="n">
-        <v>243.93</v>
+        <v>282.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-181.56</v>
+        <v>-207.56</v>
       </c>
       <c r="K43" t="n">
-        <v>-186.1</v>
+        <v>-212.75</v>
       </c>
       <c r="L43" t="n">
-        <v>260</v>
+        <v>297.23</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.16</v>
+        <v>-16.62</v>
       </c>
       <c r="K44" t="n">
-        <v>50.41</v>
+        <v>51.85</v>
       </c>
       <c r="L44" t="n">
-        <v>52.94</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-50.1</v>
+        <v>-51.13</v>
       </c>
       <c r="K45" t="n">
-        <v>44.47</v>
+        <v>45.38</v>
       </c>
       <c r="L45" t="n">
-        <v>66.98999999999999</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>61.75</v>
+        <v>62.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.38</v>
+        <v>-6.43</v>
       </c>
       <c r="L46" t="n">
-        <v>62.08</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>174.37</v>
+        <v>181.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.21</v>
+        <v>-23.17</v>
       </c>
       <c r="L47" t="n">
-        <v>175.78</v>
+        <v>183.38</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-104.11</v>
+        <v>-108.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-47.91</v>
+        <v>-49.99</v>
       </c>
       <c r="L48" t="n">
-        <v>114.61</v>
+        <v>119.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>80.19</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-17.34</v>
+        <v>-18.02</v>
       </c>
       <c r="L49" t="n">
-        <v>82.04000000000001</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-17.64</v>
+        <v>-19.28</v>
       </c>
       <c r="K50" t="n">
-        <v>-116.3</v>
+        <v>-127.11</v>
       </c>
       <c r="L50" t="n">
-        <v>117.63</v>
+        <v>128.57</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>117.27</v>
+        <v>130.86</v>
       </c>
       <c r="K51" t="n">
-        <v>99.78</v>
+        <v>111.34</v>
       </c>
       <c r="L51" t="n">
-        <v>153.97</v>
+        <v>171.82</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>55.29</v>
+        <v>61.4</v>
       </c>
       <c r="K52" t="n">
-        <v>124.67</v>
+        <v>138.44</v>
       </c>
       <c r="L52" t="n">
-        <v>136.39</v>
+        <v>151.45</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-106.4</v>
+        <v>-121.74</v>
       </c>
       <c r="K53" t="n">
-        <v>143.26</v>
+        <v>163.92</v>
       </c>
       <c r="L53" t="n">
-        <v>178.45</v>
+        <v>204.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-76.31</v>
+        <v>-85.42</v>
       </c>
       <c r="K54" t="n">
-        <v>215.79</v>
+        <v>241.56</v>
       </c>
       <c r="L54" t="n">
-        <v>228.89</v>
+        <v>256.21</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-32.66</v>
+        <v>-36.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-77.79000000000001</v>
+        <v>-86.33</v>
       </c>
       <c r="L55" t="n">
-        <v>84.37</v>
+        <v>93.63</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>90.56</v>
+        <v>103.68</v>
       </c>
       <c r="K56" t="n">
-        <v>-46.21</v>
+        <v>-52.91</v>
       </c>
       <c r="L56" t="n">
-        <v>101.67</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-74.7</v>
+        <v>-83.90000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>105.29</v>
+        <v>118.24</v>
       </c>
       <c r="L57" t="n">
-        <v>129.1</v>
+        <v>144.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-149.41</v>
+        <v>-168.59</v>
       </c>
       <c r="K58" t="n">
-        <v>-60.68</v>
+        <v>-68.47</v>
       </c>
       <c r="L58" t="n">
-        <v>161.26</v>
+        <v>181.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.59</v>
+        <v>-47.57</v>
       </c>
       <c r="K59" t="n">
-        <v>86.39</v>
+        <v>86.36</v>
       </c>
       <c r="L59" t="n">
-        <v>98.63</v>
+        <v>98.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.88</v>
+        <v>-15.12</v>
       </c>
       <c r="K60" t="n">
-        <v>43.67</v>
+        <v>44.38</v>
       </c>
       <c r="L60" t="n">
-        <v>46.14</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>52.02</v>
+        <v>52.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-65.37</v>
+        <v>-66.44</v>
       </c>
       <c r="L61" t="n">
-        <v>83.54000000000001</v>
+        <v>84.91</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-43.98</v>
+        <v>-45.95</v>
       </c>
       <c r="K62" t="n">
-        <v>40.83</v>
+        <v>42.66</v>
       </c>
       <c r="L62" t="n">
-        <v>60.01</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>97.59999999999999</v>
+        <v>101.24</v>
       </c>
       <c r="K63" t="n">
-        <v>19.09</v>
+        <v>19.81</v>
       </c>
       <c r="L63" t="n">
-        <v>99.45</v>
+        <v>103.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>30.87</v>
+        <v>31.91</v>
       </c>
       <c r="K64" t="n">
-        <v>-91.55</v>
+        <v>-94.63</v>
       </c>
       <c r="L64" t="n">
-        <v>96.62</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-109.78</v>
+        <v>-119.19</v>
       </c>
       <c r="K65" t="n">
-        <v>12.79</v>
+        <v>13.88</v>
       </c>
       <c r="L65" t="n">
-        <v>110.52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-186.45</v>
+        <v>-205.95</v>
       </c>
       <c r="K66" t="n">
-        <v>-81.06</v>
+        <v>-89.54000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>203.31</v>
+        <v>224.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>66.76000000000001</v>
+        <v>74.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-164.86</v>
+        <v>-185</v>
       </c>
       <c r="L67" t="n">
-        <v>177.86</v>
+        <v>199.59</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-164.23</v>
+        <v>-184.47</v>
       </c>
       <c r="K68" t="n">
-        <v>143.2</v>
+        <v>160.85</v>
       </c>
       <c r="L68" t="n">
-        <v>217.9</v>
+        <v>244.75</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>36.59</v>
+        <v>40.44</v>
       </c>
       <c r="K69" t="n">
-        <v>131.17</v>
+        <v>144.98</v>
       </c>
       <c r="L69" t="n">
-        <v>136.18</v>
+        <v>150.52</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>94.87</v>
+        <v>107.26</v>
       </c>
       <c r="K70" t="n">
-        <v>-181.81</v>
+        <v>-205.54</v>
       </c>
       <c r="L70" t="n">
-        <v>205.08</v>
+        <v>231.84</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>22.18</v>
+        <v>25.62</v>
       </c>
       <c r="K71" t="n">
-        <v>218.53</v>
+        <v>252.4</v>
       </c>
       <c r="L71" t="n">
-        <v>219.65</v>
+        <v>253.7</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>24.01</v>
+        <v>27.67</v>
       </c>
       <c r="K72" t="n">
-        <v>198.02</v>
+        <v>228.22</v>
       </c>
       <c r="L72" t="n">
-        <v>199.47</v>
+        <v>229.89</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>407.63</v>
+        <v>464.96</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.96</v>
+        <v>-1.1</v>
       </c>
       <c r="L73" t="n">
-        <v>407.63</v>
+        <v>464.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-40.04</v>
+        <v>-40.48</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.23</v>
+        <v>-51.8</v>
       </c>
       <c r="L74" t="n">
-        <v>65.03</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-82.13</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-47.1</v>
+        <v>-48.28</v>
       </c>
       <c r="L75" t="n">
-        <v>94.68000000000001</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>28.12</v>
+        <v>28.78</v>
       </c>
       <c r="K76" t="n">
-        <v>31.84</v>
+        <v>32.59</v>
       </c>
       <c r="L76" t="n">
-        <v>42.48</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.20999999999999</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-48.55</v>
+        <v>-50.12</v>
       </c>
       <c r="L77" t="n">
-        <v>82.09999999999999</v>
+        <v>84.76000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-30.36</v>
+        <v>-32.19</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.94</v>
+        <v>-66.73999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>69.88</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>83.48</v>
+        <v>87.77</v>
       </c>
       <c r="K79" t="n">
-        <v>27.49</v>
+        <v>28.91</v>
       </c>
       <c r="L79" t="n">
-        <v>87.89</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>159.35</v>
+        <v>176.83</v>
       </c>
       <c r="K80" t="n">
-        <v>56.93</v>
+        <v>63.17</v>
       </c>
       <c r="L80" t="n">
-        <v>169.21</v>
+        <v>187.77</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-87.98999999999999</v>
+        <v>-97.89</v>
       </c>
       <c r="K81" t="n">
-        <v>7.69</v>
+        <v>8.56</v>
       </c>
       <c r="L81" t="n">
-        <v>88.31999999999999</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.98999999999999</v>
+        <v>-92.41</v>
       </c>
       <c r="K82" t="n">
-        <v>79.83</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>117.33</v>
+        <v>126.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>9.76</v>
+        <v>11.02</v>
       </c>
       <c r="K83" t="n">
-        <v>245.98</v>
+        <v>277.82</v>
       </c>
       <c r="L83" t="n">
-        <v>246.17</v>
+        <v>278.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-171.24</v>
+        <v>-189.32</v>
       </c>
       <c r="K84" t="n">
-        <v>-103.64</v>
+        <v>-114.58</v>
       </c>
       <c r="L84" t="n">
-        <v>200.16</v>
+        <v>221.29</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>66.68000000000001</v>
+        <v>76.17</v>
       </c>
       <c r="K85" t="n">
-        <v>-103.2</v>
+        <v>-117.9</v>
       </c>
       <c r="L85" t="n">
-        <v>122.87</v>
+        <v>140.36</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>35.33</v>
+        <v>40.33</v>
       </c>
       <c r="K86" t="n">
-        <v>284.53</v>
+        <v>324.84</v>
       </c>
       <c r="L86" t="n">
-        <v>286.72</v>
+        <v>327.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-335.01</v>
+        <v>-380.76</v>
       </c>
       <c r="K87" t="n">
-        <v>-25.9</v>
+        <v>-29.44</v>
       </c>
       <c r="L87" t="n">
-        <v>336.01</v>
+        <v>381.9</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-151.76</v>
+        <v>-174.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-92.12</v>
+        <v>-105.68</v>
       </c>
       <c r="L88" t="n">
-        <v>177.53</v>
+        <v>203.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-52.52</v>
+        <v>-37.96</v>
       </c>
       <c r="K14" t="n">
-        <v>15.1</v>
+        <v>10.91</v>
       </c>
       <c r="L14" t="n">
-        <v>54.65</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>18.05</v>
+        <v>13.53</v>
       </c>
       <c r="K15" t="n">
-        <v>77.84</v>
+        <v>58.38</v>
       </c>
       <c r="L15" t="n">
-        <v>79.90000000000001</v>
+        <v>59.93</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>71.91</v>
+        <v>46.42</v>
       </c>
       <c r="K16" t="n">
-        <v>37.26</v>
+        <v>24.06</v>
       </c>
       <c r="L16" t="n">
-        <v>80.98999999999999</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>56.4</v>
+        <v>42.3</v>
       </c>
       <c r="K17" t="n">
-        <v>63.73</v>
+        <v>47.8</v>
       </c>
       <c r="L17" t="n">
-        <v>85.11</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-21.83</v>
+        <v>-14.24</v>
       </c>
       <c r="K18" t="n">
-        <v>-100.06</v>
+        <v>-65.27</v>
       </c>
       <c r="L18" t="n">
-        <v>102.41</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-23.1</v>
+        <v>-17.33</v>
       </c>
       <c r="K19" t="n">
-        <v>55.82</v>
+        <v>41.86</v>
       </c>
       <c r="L19" t="n">
-        <v>60.41</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-38.28</v>
+        <v>-27.88</v>
       </c>
       <c r="K20" t="n">
-        <v>78.33</v>
+        <v>57.05</v>
       </c>
       <c r="L20" t="n">
-        <v>87.18000000000001</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-38.24</v>
+        <v>-25.94</v>
       </c>
       <c r="K21" t="n">
-        <v>81.67</v>
+        <v>55.4</v>
       </c>
       <c r="L21" t="n">
-        <v>90.18000000000001</v>
+        <v>61.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3</v>
+        <v>-0.22</v>
       </c>
       <c r="K22" t="n">
-        <v>-68.64</v>
+        <v>-50.17</v>
       </c>
       <c r="L22" t="n">
-        <v>68.64</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>182.65</v>
+        <v>136.99</v>
       </c>
       <c r="K23" t="n">
-        <v>-20.51</v>
+        <v>-15.38</v>
       </c>
       <c r="L23" t="n">
-        <v>183.8</v>
+        <v>137.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>134.31</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-135.69</v>
+        <v>-90.67</v>
       </c>
       <c r="L24" t="n">
-        <v>190.92</v>
+        <v>127.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>132.86</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-98.56</v>
+        <v>-70.05</v>
       </c>
       <c r="L25" t="n">
-        <v>165.42</v>
+        <v>117.58</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-136.13</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-59.32</v>
+        <v>-41.19</v>
       </c>
       <c r="L26" t="n">
-        <v>148.49</v>
+        <v>103.12</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>218.36</v>
+        <v>152.99</v>
       </c>
       <c r="K27" t="n">
-        <v>292.65</v>
+        <v>205.05</v>
       </c>
       <c r="L27" t="n">
-        <v>365.13</v>
+        <v>255.83</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>156.45</v>
+        <v>107.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.4</v>
+        <v>-3.71</v>
       </c>
       <c r="L28" t="n">
-        <v>156.55</v>
+        <v>107.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>78.61</v>
+        <v>57.64</v>
       </c>
       <c r="K29" t="n">
-        <v>3.31</v>
+        <v>2.43</v>
       </c>
       <c r="L29" t="n">
-        <v>78.68000000000001</v>
+        <v>57.69</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.07</v>
+        <v>-30.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.49</v>
+        <v>-2.43</v>
       </c>
       <c r="L30" t="n">
-        <v>44.21</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-98</v>
+        <v>-61.75</v>
       </c>
       <c r="K31" t="n">
-        <v>77.29000000000001</v>
+        <v>48.71</v>
       </c>
       <c r="L31" t="n">
-        <v>124.81</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-115.33</v>
+        <v>-74.84999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>102.66</v>
+        <v>66.63</v>
       </c>
       <c r="L32" t="n">
-        <v>154.4</v>
+        <v>100.21</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>6.95</v>
+        <v>4.57</v>
       </c>
       <c r="K33" t="n">
-        <v>-119.73</v>
+        <v>-78.7</v>
       </c>
       <c r="L33" t="n">
-        <v>119.93</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-57.56</v>
+        <v>-37.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-76.68000000000001</v>
+        <v>-50.15</v>
       </c>
       <c r="L34" t="n">
-        <v>95.88</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>72.77</v>
+        <v>45.94</v>
       </c>
       <c r="K35" t="n">
-        <v>131.16</v>
+        <v>82.8</v>
       </c>
       <c r="L35" t="n">
-        <v>150</v>
+        <v>94.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>17.42</v>
+        <v>12.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-120.84</v>
+        <v>-87.69</v>
       </c>
       <c r="L36" t="n">
-        <v>122.09</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-40.28</v>
+        <v>-30.21</v>
       </c>
       <c r="K37" t="n">
-        <v>129.6</v>
+        <v>97.2</v>
       </c>
       <c r="L37" t="n">
-        <v>135.71</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>81.75</v>
+        <v>57.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-54.13</v>
+        <v>-37.88</v>
       </c>
       <c r="L38" t="n">
-        <v>98.05</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-40.17</v>
+        <v>-25.54</v>
       </c>
       <c r="K39" t="n">
-        <v>-244.37</v>
+        <v>-155.34</v>
       </c>
       <c r="L39" t="n">
-        <v>247.65</v>
+        <v>157.43</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>60.42</v>
+        <v>42.37</v>
       </c>
       <c r="K40" t="n">
-        <v>-229.53</v>
+        <v>-160.95</v>
       </c>
       <c r="L40" t="n">
-        <v>237.35</v>
+        <v>166.43</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>148.92</v>
+        <v>111.69</v>
       </c>
       <c r="K41" t="n">
-        <v>52.85</v>
+        <v>39.64</v>
       </c>
       <c r="L41" t="n">
-        <v>158.01</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>242.26</v>
+        <v>174.45</v>
       </c>
       <c r="K42" t="n">
-        <v>144.66</v>
+        <v>104.17</v>
       </c>
       <c r="L42" t="n">
-        <v>282.17</v>
+        <v>203.19</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-207.56</v>
+        <v>-146.08</v>
       </c>
       <c r="K43" t="n">
-        <v>-212.75</v>
+        <v>-149.73</v>
       </c>
       <c r="L43" t="n">
-        <v>297.23</v>
+        <v>209.19</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.62</v>
+        <v>-11.27</v>
       </c>
       <c r="K44" t="n">
-        <v>51.85</v>
+        <v>35.14</v>
       </c>
       <c r="L44" t="n">
-        <v>54.45</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-51.13</v>
+        <v>-34.86</v>
       </c>
       <c r="K45" t="n">
-        <v>45.38</v>
+        <v>30.94</v>
       </c>
       <c r="L45" t="n">
-        <v>68.37</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>62.19</v>
+        <v>40.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.43</v>
+        <v>-4.19</v>
       </c>
       <c r="L46" t="n">
-        <v>62.52</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>181.91</v>
+        <v>112.56</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.17</v>
+        <v>-14.34</v>
       </c>
       <c r="L47" t="n">
-        <v>183.38</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-108.63</v>
+        <v>-73.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-49.99</v>
+        <v>-33.74</v>
       </c>
       <c r="L48" t="n">
-        <v>119.59</v>
+        <v>80.72</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>83.31999999999999</v>
+        <v>62.49</v>
       </c>
       <c r="K49" t="n">
-        <v>-18.02</v>
+        <v>-13.51</v>
       </c>
       <c r="L49" t="n">
-        <v>85.25</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-19.28</v>
+        <v>-13.56</v>
       </c>
       <c r="K50" t="n">
-        <v>-127.11</v>
+        <v>-89.41</v>
       </c>
       <c r="L50" t="n">
-        <v>128.57</v>
+        <v>90.43000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>130.86</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>111.34</v>
+        <v>71.72</v>
       </c>
       <c r="L51" t="n">
-        <v>171.82</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>61.4</v>
+        <v>39.43</v>
       </c>
       <c r="K52" t="n">
-        <v>138.44</v>
+        <v>88.91</v>
       </c>
       <c r="L52" t="n">
-        <v>151.45</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-121.74</v>
+        <v>-88.59</v>
       </c>
       <c r="K53" t="n">
-        <v>163.92</v>
+        <v>119.29</v>
       </c>
       <c r="L53" t="n">
-        <v>204.18</v>
+        <v>148.59</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-85.42</v>
+        <v>-53.66</v>
       </c>
       <c r="K54" t="n">
-        <v>241.56</v>
+        <v>151.73</v>
       </c>
       <c r="L54" t="n">
-        <v>256.21</v>
+        <v>160.94</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-36.25</v>
+        <v>-25.48</v>
       </c>
       <c r="K55" t="n">
-        <v>-86.33</v>
+        <v>-60.67</v>
       </c>
       <c r="L55" t="n">
-        <v>93.63</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>103.68</v>
+        <v>18.92</v>
       </c>
       <c r="K56" t="n">
-        <v>-52.91</v>
+        <v>-9.66</v>
       </c>
       <c r="L56" t="n">
-        <v>116.4</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-83.90000000000001</v>
+        <v>-56.29</v>
       </c>
       <c r="K57" t="n">
-        <v>118.24</v>
+        <v>79.33</v>
       </c>
       <c r="L57" t="n">
-        <v>144.98</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-168.59</v>
+        <v>-106.29</v>
       </c>
       <c r="K58" t="n">
-        <v>-68.47</v>
+        <v>-43.17</v>
       </c>
       <c r="L58" t="n">
-        <v>181.96</v>
+        <v>114.72</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.57</v>
+        <v>-29.64</v>
       </c>
       <c r="K59" t="n">
-        <v>86.36</v>
+        <v>53.8</v>
       </c>
       <c r="L59" t="n">
-        <v>98.59</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.12</v>
+        <v>-9.76</v>
       </c>
       <c r="K60" t="n">
-        <v>44.38</v>
+        <v>28.65</v>
       </c>
       <c r="L60" t="n">
-        <v>46.88</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>52.87</v>
+        <v>31.19</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.44</v>
+        <v>-39.19</v>
       </c>
       <c r="L61" t="n">
-        <v>84.91</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-45.95</v>
+        <v>-33.79</v>
       </c>
       <c r="K62" t="n">
-        <v>42.66</v>
+        <v>31.37</v>
       </c>
       <c r="L62" t="n">
-        <v>62.7</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>101.24</v>
+        <v>73.52</v>
       </c>
       <c r="K63" t="n">
-        <v>19.81</v>
+        <v>14.38</v>
       </c>
       <c r="L63" t="n">
-        <v>103.16</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>31.91</v>
+        <v>20.36</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.63</v>
+        <v>-60.37</v>
       </c>
       <c r="L64" t="n">
-        <v>99.86</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-119.19</v>
+        <v>-75.45999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>13.88</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>120</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-205.95</v>
+        <v>-144.85</v>
       </c>
       <c r="K66" t="n">
-        <v>-89.54000000000001</v>
+        <v>-62.98</v>
       </c>
       <c r="L66" t="n">
-        <v>224.57</v>
+        <v>157.95</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>74.91</v>
+        <v>46.26</v>
       </c>
       <c r="K67" t="n">
-        <v>-185</v>
+        <v>-114.24</v>
       </c>
       <c r="L67" t="n">
-        <v>199.59</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-184.47</v>
+        <v>-126.32</v>
       </c>
       <c r="K68" t="n">
-        <v>160.85</v>
+        <v>110.15</v>
       </c>
       <c r="L68" t="n">
-        <v>244.75</v>
+        <v>167.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>40.44</v>
+        <v>24.41</v>
       </c>
       <c r="K69" t="n">
-        <v>144.98</v>
+        <v>87.52</v>
       </c>
       <c r="L69" t="n">
-        <v>150.52</v>
+        <v>90.86</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>107.26</v>
+        <v>71.25</v>
       </c>
       <c r="K70" t="n">
-        <v>-205.54</v>
+        <v>-136.55</v>
       </c>
       <c r="L70" t="n">
-        <v>231.84</v>
+        <v>154.02</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>25.62</v>
+        <v>18.8</v>
       </c>
       <c r="K71" t="n">
-        <v>252.4</v>
+        <v>185.21</v>
       </c>
       <c r="L71" t="n">
-        <v>253.7</v>
+        <v>186.16</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>27.67</v>
+        <v>18.15</v>
       </c>
       <c r="K72" t="n">
-        <v>228.22</v>
+        <v>149.68</v>
       </c>
       <c r="L72" t="n">
-        <v>229.89</v>
+        <v>150.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>464.96</v>
+        <v>293.14</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>464.96</v>
+        <v>293.15</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-40.48</v>
+        <v>-26.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.8</v>
+        <v>-34.23</v>
       </c>
       <c r="L74" t="n">
-        <v>65.73999999999999</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-84.18000000000001</v>
+        <v>-50.13</v>
       </c>
       <c r="K75" t="n">
-        <v>-48.28</v>
+        <v>-28.75</v>
       </c>
       <c r="L75" t="n">
-        <v>97.04000000000001</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>28.78</v>
+        <v>19.98</v>
       </c>
       <c r="K76" t="n">
-        <v>32.59</v>
+        <v>22.63</v>
       </c>
       <c r="L76" t="n">
-        <v>43.48</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-68.34999999999999</v>
+        <v>-45.05</v>
       </c>
       <c r="K77" t="n">
-        <v>-50.12</v>
+        <v>-33.03</v>
       </c>
       <c r="L77" t="n">
-        <v>84.76000000000001</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.19</v>
+        <v>-22.61</v>
       </c>
       <c r="K78" t="n">
-        <v>-66.73999999999999</v>
+        <v>-46.87</v>
       </c>
       <c r="L78" t="n">
-        <v>74.09999999999999</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>87.77</v>
+        <v>54.68</v>
       </c>
       <c r="K79" t="n">
-        <v>28.91</v>
+        <v>18.01</v>
       </c>
       <c r="L79" t="n">
-        <v>92.41</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>176.83</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>63.17</v>
+        <v>34.56</v>
       </c>
       <c r="L80" t="n">
-        <v>187.77</v>
+        <v>102.73</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-97.89</v>
+        <v>-60.78</v>
       </c>
       <c r="K81" t="n">
-        <v>8.56</v>
+        <v>5.31</v>
       </c>
       <c r="L81" t="n">
-        <v>98.26000000000001</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-92.41</v>
+        <v>-57.53</v>
       </c>
       <c r="K82" t="n">
-        <v>85.79000000000001</v>
+        <v>53.41</v>
       </c>
       <c r="L82" t="n">
-        <v>126.09</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>11.02</v>
+        <v>7.4</v>
       </c>
       <c r="K83" t="n">
-        <v>277.82</v>
+        <v>186.39</v>
       </c>
       <c r="L83" t="n">
-        <v>278.04</v>
+        <v>186.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-189.32</v>
+        <v>-126.02</v>
       </c>
       <c r="K84" t="n">
-        <v>-114.58</v>
+        <v>-76.27</v>
       </c>
       <c r="L84" t="n">
-        <v>221.29</v>
+        <v>147.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>76.17</v>
+        <v>51</v>
       </c>
       <c r="K85" t="n">
-        <v>-117.9</v>
+        <v>-78.94</v>
       </c>
       <c r="L85" t="n">
-        <v>140.36</v>
+        <v>93.98</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>40.33</v>
+        <v>25.93</v>
       </c>
       <c r="K86" t="n">
-        <v>324.84</v>
+        <v>208.82</v>
       </c>
       <c r="L86" t="n">
-        <v>327.33</v>
+        <v>210.43</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-380.76</v>
+        <v>-261.54</v>
       </c>
       <c r="K87" t="n">
-        <v>-29.44</v>
+        <v>-20.22</v>
       </c>
       <c r="L87" t="n">
-        <v>381.9</v>
+        <v>262.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-174.11</v>
+        <v>-116.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-105.68</v>
+        <v>-70.61</v>
       </c>
       <c r="L88" t="n">
-        <v>203.67</v>
+        <v>136.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-37.96</v>
+        <v>-38.87</v>
       </c>
       <c r="K14" t="n">
-        <v>10.91</v>
+        <v>11.18</v>
       </c>
       <c r="L14" t="n">
-        <v>39.49</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>13.53</v>
+        <v>13.06</v>
       </c>
       <c r="K15" t="n">
-        <v>58.38</v>
+        <v>56.35</v>
       </c>
       <c r="L15" t="n">
-        <v>59.93</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>46.42</v>
+        <v>46.51</v>
       </c>
       <c r="K16" t="n">
-        <v>24.06</v>
+        <v>24.1</v>
       </c>
       <c r="L16" t="n">
-        <v>52.28</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>42.3</v>
+        <v>42.15</v>
       </c>
       <c r="K17" t="n">
-        <v>47.8</v>
+        <v>47.63</v>
       </c>
       <c r="L17" t="n">
-        <v>63.83</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.24</v>
+        <v>-14.26</v>
       </c>
       <c r="K18" t="n">
-        <v>-65.27</v>
+        <v>-65.38</v>
       </c>
       <c r="L18" t="n">
-        <v>66.81</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.33</v>
+        <v>-18.12</v>
       </c>
       <c r="K19" t="n">
-        <v>41.86</v>
+        <v>43.79</v>
       </c>
       <c r="L19" t="n">
-        <v>45.31</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-27.88</v>
+        <v>-29.61</v>
       </c>
       <c r="K20" t="n">
-        <v>57.05</v>
+        <v>60.59</v>
       </c>
       <c r="L20" t="n">
-        <v>63.49</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-25.94</v>
+        <v>-27.9</v>
       </c>
       <c r="K21" t="n">
-        <v>55.4</v>
+        <v>59.58</v>
       </c>
       <c r="L21" t="n">
-        <v>61.17</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="K22" t="n">
-        <v>-50.17</v>
+        <v>-54.98</v>
       </c>
       <c r="L22" t="n">
-        <v>50.17</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>136.99</v>
+        <v>135.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-15.38</v>
+        <v>-15.18</v>
       </c>
       <c r="L23" t="n">
-        <v>137.85</v>
+        <v>136.05</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>89.76000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="K24" t="n">
-        <v>-90.67</v>
+        <v>-91.45999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>127.58</v>
+        <v>128.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>94.43000000000001</v>
+        <v>94.61</v>
       </c>
       <c r="K25" t="n">
-        <v>-70.05</v>
+        <v>-70.18000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>117.58</v>
+        <v>117.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-94.54000000000001</v>
+        <v>-102.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-41.19</v>
+        <v>-44.59</v>
       </c>
       <c r="L26" t="n">
-        <v>103.12</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>152.99</v>
+        <v>147.53</v>
       </c>
       <c r="K27" t="n">
-        <v>205.05</v>
+        <v>197.72</v>
       </c>
       <c r="L27" t="n">
-        <v>255.83</v>
+        <v>246.69</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>107.47</v>
+        <v>116.85</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.71</v>
+        <v>-4.04</v>
       </c>
       <c r="L28" t="n">
-        <v>107.53</v>
+        <v>116.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>57.64</v>
+        <v>55.76</v>
       </c>
       <c r="K29" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="L29" t="n">
-        <v>57.69</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-30.7</v>
+        <v>-32.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.43</v>
+        <v>-2.56</v>
       </c>
       <c r="L30" t="n">
-        <v>30.8</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-61.75</v>
+        <v>-59.35</v>
       </c>
       <c r="K31" t="n">
-        <v>48.71</v>
+        <v>46.81</v>
       </c>
       <c r="L31" t="n">
-        <v>78.65000000000001</v>
+        <v>75.59</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-74.84999999999999</v>
+        <v>-72.01000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>66.63</v>
+        <v>64.11</v>
       </c>
       <c r="L32" t="n">
-        <v>100.21</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="K33" t="n">
-        <v>-78.7</v>
+        <v>-76.65000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>78.83</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-37.64</v>
+        <v>-38.02</v>
       </c>
       <c r="K34" t="n">
-        <v>-50.15</v>
+        <v>-50.66</v>
       </c>
       <c r="L34" t="n">
-        <v>62.7</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>45.94</v>
+        <v>45.62</v>
       </c>
       <c r="K35" t="n">
-        <v>82.8</v>
+        <v>82.23</v>
       </c>
       <c r="L35" t="n">
-        <v>94.69</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>12.64</v>
+        <v>12.58</v>
       </c>
       <c r="K36" t="n">
-        <v>-87.69</v>
+        <v>-87.26000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>88.59999999999999</v>
+        <v>88.16</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-30.21</v>
+        <v>-29.9</v>
       </c>
       <c r="K37" t="n">
-        <v>97.2</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>101.78</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>57.2</v>
+        <v>62.19</v>
       </c>
       <c r="K38" t="n">
-        <v>-37.88</v>
+        <v>-41.18</v>
       </c>
       <c r="L38" t="n">
-        <v>68.59999999999999</v>
+        <v>74.59</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-25.54</v>
+        <v>-25.16</v>
       </c>
       <c r="K39" t="n">
-        <v>-155.34</v>
+        <v>-153.06</v>
       </c>
       <c r="L39" t="n">
-        <v>157.43</v>
+        <v>155.12</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>42.37</v>
+        <v>41.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-160.95</v>
+        <v>-156.15</v>
       </c>
       <c r="L40" t="n">
-        <v>166.43</v>
+        <v>161.47</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>111.69</v>
+        <v>118.69</v>
       </c>
       <c r="K41" t="n">
-        <v>39.64</v>
+        <v>42.12</v>
       </c>
       <c r="L41" t="n">
-        <v>118.51</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>174.45</v>
+        <v>172.59</v>
       </c>
       <c r="K42" t="n">
-        <v>104.17</v>
+        <v>103.06</v>
       </c>
       <c r="L42" t="n">
-        <v>203.19</v>
+        <v>201.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-146.08</v>
+        <v>-143.29</v>
       </c>
       <c r="K43" t="n">
-        <v>-149.73</v>
+        <v>-146.87</v>
       </c>
       <c r="L43" t="n">
-        <v>209.19</v>
+        <v>205.18</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.27</v>
+        <v>-11.81</v>
       </c>
       <c r="K44" t="n">
-        <v>35.14</v>
+        <v>36.84</v>
       </c>
       <c r="L44" t="n">
-        <v>36.9</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.86</v>
+        <v>-35.03</v>
       </c>
       <c r="K45" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="L45" t="n">
-        <v>46.61</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>40.56</v>
+        <v>41.51</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.19</v>
+        <v>-4.29</v>
       </c>
       <c r="L46" t="n">
-        <v>40.77</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>112.56</v>
+        <v>106.76</v>
       </c>
       <c r="K47" t="n">
-        <v>-14.34</v>
+        <v>-13.6</v>
       </c>
       <c r="L47" t="n">
-        <v>113.47</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.33</v>
+        <v>-71.61</v>
       </c>
       <c r="K48" t="n">
-        <v>-33.74</v>
+        <v>-32.96</v>
       </c>
       <c r="L48" t="n">
-        <v>80.72</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>62.49</v>
+        <v>62.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.51</v>
+        <v>-13.47</v>
       </c>
       <c r="L49" t="n">
-        <v>63.93</v>
+        <v>63.74</v>
       </c>
     </row>
     <row r="50">
@@ -2155,10 +2155,10 @@
         <v>-13.56</v>
       </c>
       <c r="K50" t="n">
-        <v>-89.41</v>
+        <v>-89.34999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>90.43000000000001</v>
+        <v>90.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>84.29000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>71.72</v>
+        <v>70.92</v>
       </c>
       <c r="L51" t="n">
-        <v>110.67</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>39.43</v>
+        <v>39.51</v>
       </c>
       <c r="K52" t="n">
-        <v>88.91</v>
+        <v>89.09</v>
       </c>
       <c r="L52" t="n">
-        <v>97.27</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-88.59</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>119.29</v>
+        <v>116.8</v>
       </c>
       <c r="L53" t="n">
-        <v>148.59</v>
+        <v>145.49</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-53.66</v>
+        <v>-52.56</v>
       </c>
       <c r="K54" t="n">
-        <v>151.73</v>
+        <v>148.62</v>
       </c>
       <c r="L54" t="n">
-        <v>160.94</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-25.48</v>
+        <v>-27.77</v>
       </c>
       <c r="K55" t="n">
-        <v>-60.67</v>
+        <v>-66.12</v>
       </c>
       <c r="L55" t="n">
-        <v>65.8</v>
+        <v>71.70999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>18.92</v>
+        <v>18.62</v>
       </c>
       <c r="K56" t="n">
-        <v>-9.66</v>
+        <v>-9.5</v>
       </c>
       <c r="L56" t="n">
-        <v>21.25</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-56.29</v>
+        <v>-61.71</v>
       </c>
       <c r="K57" t="n">
-        <v>79.33</v>
+        <v>86.97</v>
       </c>
       <c r="L57" t="n">
-        <v>97.27</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-106.29</v>
+        <v>-113.57</v>
       </c>
       <c r="K58" t="n">
-        <v>-43.17</v>
+        <v>-46.12</v>
       </c>
       <c r="L58" t="n">
-        <v>114.72</v>
+        <v>122.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-29.64</v>
+        <v>-29.09</v>
       </c>
       <c r="K59" t="n">
-        <v>53.8</v>
+        <v>52.81</v>
       </c>
       <c r="L59" t="n">
-        <v>61.43</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.76</v>
+        <v>-10.65</v>
       </c>
       <c r="K60" t="n">
-        <v>28.65</v>
+        <v>31.24</v>
       </c>
       <c r="L60" t="n">
-        <v>30.26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>31.19</v>
+        <v>31.85</v>
       </c>
       <c r="K61" t="n">
-        <v>-39.19</v>
+        <v>-40.03</v>
       </c>
       <c r="L61" t="n">
-        <v>50.09</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-33.79</v>
+        <v>-35.59</v>
       </c>
       <c r="K62" t="n">
-        <v>31.37</v>
+        <v>33.04</v>
       </c>
       <c r="L62" t="n">
-        <v>46.11</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>73.52</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>14.38</v>
+        <v>14.1</v>
       </c>
       <c r="L63" t="n">
-        <v>74.91</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>20.36</v>
+        <v>20.45</v>
       </c>
       <c r="K64" t="n">
-        <v>-60.37</v>
+        <v>-60.65</v>
       </c>
       <c r="L64" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-75.45999999999999</v>
+        <v>-77.83</v>
       </c>
       <c r="K65" t="n">
-        <v>8.789999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="L65" t="n">
-        <v>75.97</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-144.85</v>
+        <v>-138.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-62.98</v>
+        <v>-60.04</v>
       </c>
       <c r="L66" t="n">
-        <v>157.95</v>
+        <v>150.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>46.26</v>
+        <v>45.45</v>
       </c>
       <c r="K67" t="n">
-        <v>-114.24</v>
+        <v>-112.25</v>
       </c>
       <c r="L67" t="n">
-        <v>123.25</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-126.32</v>
+        <v>-122.04</v>
       </c>
       <c r="K68" t="n">
-        <v>110.15</v>
+        <v>106.41</v>
       </c>
       <c r="L68" t="n">
-        <v>167.6</v>
+        <v>161.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>24.41</v>
+        <v>26.1</v>
       </c>
       <c r="K69" t="n">
-        <v>87.52</v>
+        <v>93.58</v>
       </c>
       <c r="L69" t="n">
-        <v>90.86</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>71.25</v>
+        <v>70.22</v>
       </c>
       <c r="K70" t="n">
-        <v>-136.55</v>
+        <v>-134.56</v>
       </c>
       <c r="L70" t="n">
-        <v>154.02</v>
+        <v>151.78</v>
       </c>
     </row>
     <row r="71">
@@ -3037,10 +3037,10 @@
         <v>18.8</v>
       </c>
       <c r="K71" t="n">
-        <v>185.21</v>
+        <v>185.19</v>
       </c>
       <c r="L71" t="n">
-        <v>186.16</v>
+        <v>186.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>18.15</v>
+        <v>18.78</v>
       </c>
       <c r="K72" t="n">
-        <v>149.68</v>
+        <v>154.9</v>
       </c>
       <c r="L72" t="n">
-        <v>150.78</v>
+        <v>156.03</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>293.14</v>
+        <v>281.77</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="L73" t="n">
-        <v>293.15</v>
+        <v>281.77</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-26.76</v>
+        <v>-27.09</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.23</v>
+        <v>-34.67</v>
       </c>
       <c r="L74" t="n">
-        <v>43.45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-50.13</v>
+        <v>-50.21</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.75</v>
+        <v>-28.79</v>
       </c>
       <c r="L75" t="n">
-        <v>57.79</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>19.98</v>
+        <v>21.46</v>
       </c>
       <c r="K76" t="n">
-        <v>22.63</v>
+        <v>24.3</v>
       </c>
       <c r="L76" t="n">
-        <v>30.19</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-45.05</v>
+        <v>-45.67</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.03</v>
+        <v>-33.49</v>
       </c>
       <c r="L77" t="n">
-        <v>55.86</v>
+        <v>56.63</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-22.61</v>
+        <v>-23.42</v>
       </c>
       <c r="K78" t="n">
-        <v>-46.87</v>
+        <v>-48.55</v>
       </c>
       <c r="L78" t="n">
-        <v>52.04</v>
+        <v>53.91</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>54.68</v>
+        <v>55.91</v>
       </c>
       <c r="K79" t="n">
-        <v>18.01</v>
+        <v>18.42</v>
       </c>
       <c r="L79" t="n">
-        <v>57.57</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>96.73999999999999</v>
+        <v>97.22</v>
       </c>
       <c r="K80" t="n">
-        <v>34.56</v>
+        <v>34.73</v>
       </c>
       <c r="L80" t="n">
-        <v>102.73</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-60.78</v>
+        <v>-65.73</v>
       </c>
       <c r="K81" t="n">
-        <v>5.31</v>
+        <v>5.75</v>
       </c>
       <c r="L81" t="n">
-        <v>61.01</v>
+        <v>65.98</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-57.53</v>
+        <v>-58.63</v>
       </c>
       <c r="K82" t="n">
-        <v>53.41</v>
+        <v>54.43</v>
       </c>
       <c r="L82" t="n">
-        <v>78.5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>7.4</v>
+        <v>7.11</v>
       </c>
       <c r="K83" t="n">
-        <v>186.39</v>
+        <v>179.26</v>
       </c>
       <c r="L83" t="n">
-        <v>186.54</v>
+        <v>179.41</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-126.02</v>
+        <v>-123.04</v>
       </c>
       <c r="K84" t="n">
-        <v>-76.27</v>
+        <v>-74.47</v>
       </c>
       <c r="L84" t="n">
-        <v>147.3</v>
+        <v>143.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>51</v>
+        <v>53.68</v>
       </c>
       <c r="K85" t="n">
-        <v>-78.94</v>
+        <v>-83.08</v>
       </c>
       <c r="L85" t="n">
-        <v>93.98</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>25.93</v>
+        <v>24.36</v>
       </c>
       <c r="K86" t="n">
-        <v>208.82</v>
+        <v>196.18</v>
       </c>
       <c r="L86" t="n">
-        <v>210.43</v>
+        <v>197.68</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-261.54</v>
+        <v>-251.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-20.22</v>
+        <v>-19.41</v>
       </c>
       <c r="L87" t="n">
-        <v>262.32</v>
+        <v>251.77</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-116.33</v>
+        <v>-121.23</v>
       </c>
       <c r="K88" t="n">
-        <v>-70.61</v>
+        <v>-73.58</v>
       </c>
       <c r="L88" t="n">
-        <v>136.08</v>
+        <v>141.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-38.87</v>
+        <v>-39.92</v>
       </c>
       <c r="K14" t="n">
-        <v>11.18</v>
+        <v>11.48</v>
       </c>
       <c r="L14" t="n">
-        <v>40.45</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>13.06</v>
+        <v>12.53</v>
       </c>
       <c r="K15" t="n">
-        <v>56.35</v>
+        <v>54.02</v>
       </c>
       <c r="L15" t="n">
-        <v>57.84</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>46.51</v>
+        <v>46.62</v>
       </c>
       <c r="K16" t="n">
-        <v>24.1</v>
+        <v>24.16</v>
       </c>
       <c r="L16" t="n">
-        <v>52.39</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>42.15</v>
+        <v>41.98</v>
       </c>
       <c r="K17" t="n">
-        <v>47.63</v>
+        <v>47.44</v>
       </c>
       <c r="L17" t="n">
-        <v>63.61</v>
+        <v>63.35</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.26</v>
+        <v>-14.29</v>
       </c>
       <c r="K18" t="n">
-        <v>-65.38</v>
+        <v>-65.5</v>
       </c>
       <c r="L18" t="n">
-        <v>66.92</v>
+        <v>67.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.12</v>
+        <v>-19.03</v>
       </c>
       <c r="K19" t="n">
-        <v>43.79</v>
+        <v>45.99</v>
       </c>
       <c r="L19" t="n">
-        <v>47.39</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-29.61</v>
+        <v>-31.58</v>
       </c>
       <c r="K20" t="n">
-        <v>60.59</v>
+        <v>64.63</v>
       </c>
       <c r="L20" t="n">
-        <v>67.43000000000001</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-27.9</v>
+        <v>-30.13</v>
       </c>
       <c r="K21" t="n">
-        <v>59.58</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>65.79000000000001</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="K22" t="n">
-        <v>-54.98</v>
+        <v>-60.47</v>
       </c>
       <c r="L22" t="n">
-        <v>54.98</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>135.2</v>
+        <v>133.16</v>
       </c>
       <c r="K23" t="n">
-        <v>-15.18</v>
+        <v>-14.95</v>
       </c>
       <c r="L23" t="n">
-        <v>136.05</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>90.53</v>
+        <v>91.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-91.45999999999999</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>128.69</v>
+        <v>129.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>94.61</v>
+        <v>94.81</v>
       </c>
       <c r="K25" t="n">
-        <v>-70.18000000000001</v>
+        <v>-70.33</v>
       </c>
       <c r="L25" t="n">
-        <v>117.8</v>
+        <v>118.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-102.34</v>
+        <v>-111.25</v>
       </c>
       <c r="K26" t="n">
-        <v>-44.59</v>
+        <v>-48.47</v>
       </c>
       <c r="L26" t="n">
-        <v>111.63</v>
+        <v>121.35</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>147.53</v>
+        <v>141.28</v>
       </c>
       <c r="K27" t="n">
-        <v>197.72</v>
+        <v>189.34</v>
       </c>
       <c r="L27" t="n">
-        <v>246.69</v>
+        <v>236.24</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>116.85</v>
+        <v>128.78</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.04</v>
+        <v>-4.45</v>
       </c>
       <c r="L28" t="n">
-        <v>116.92</v>
+        <v>128.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>55.76</v>
+        <v>53.62</v>
       </c>
       <c r="K29" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="L29" t="n">
-        <v>55.81</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.43</v>
+        <v>-34.4</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.56</v>
+        <v>-2.72</v>
       </c>
       <c r="L30" t="n">
-        <v>32.53</v>
+        <v>34.51</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-59.35</v>
+        <v>-56.59</v>
       </c>
       <c r="K31" t="n">
-        <v>46.81</v>
+        <v>44.64</v>
       </c>
       <c r="L31" t="n">
-        <v>75.59</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-72.01000000000001</v>
+        <v>-68.77</v>
       </c>
       <c r="K32" t="n">
-        <v>64.11</v>
+        <v>61.22</v>
       </c>
       <c r="L32" t="n">
-        <v>96.41</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="K33" t="n">
-        <v>-76.65000000000001</v>
+        <v>-74.31</v>
       </c>
       <c r="L33" t="n">
-        <v>76.78</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-38.02</v>
+        <v>-38.46</v>
       </c>
       <c r="K34" t="n">
-        <v>-50.66</v>
+        <v>-51.23</v>
       </c>
       <c r="L34" t="n">
-        <v>63.34</v>
+        <v>64.06</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>45.62</v>
+        <v>45.26</v>
       </c>
       <c r="K35" t="n">
-        <v>82.23</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>94.04000000000001</v>
+        <v>93.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>12.58</v>
+        <v>12.51</v>
       </c>
       <c r="K36" t="n">
-        <v>-87.26000000000001</v>
+        <v>-86.77</v>
       </c>
       <c r="L36" t="n">
-        <v>88.16</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.9</v>
+        <v>-29.55</v>
       </c>
       <c r="K37" t="n">
-        <v>96.20999999999999</v>
+        <v>95.09</v>
       </c>
       <c r="L37" t="n">
-        <v>100.75</v>
+        <v>99.56999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>62.19</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-41.18</v>
+        <v>-44.96</v>
       </c>
       <c r="L38" t="n">
-        <v>74.59</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-25.16</v>
+        <v>-24.73</v>
       </c>
       <c r="K39" t="n">
-        <v>-153.06</v>
+        <v>-150.46</v>
       </c>
       <c r="L39" t="n">
-        <v>155.12</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>41.1</v>
+        <v>39.66</v>
       </c>
       <c r="K40" t="n">
-        <v>-156.15</v>
+        <v>-150.66</v>
       </c>
       <c r="L40" t="n">
-        <v>161.47</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>118.69</v>
+        <v>126.69</v>
       </c>
       <c r="K41" t="n">
-        <v>42.12</v>
+        <v>44.96</v>
       </c>
       <c r="L41" t="n">
-        <v>125.94</v>
+        <v>134.44</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>172.59</v>
+        <v>170.46</v>
       </c>
       <c r="K42" t="n">
-        <v>103.06</v>
+        <v>101.79</v>
       </c>
       <c r="L42" t="n">
-        <v>201.02</v>
+        <v>198.54</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-143.29</v>
+        <v>-140.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-146.87</v>
+        <v>-143.59</v>
       </c>
       <c r="L43" t="n">
-        <v>205.18</v>
+        <v>200.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.81</v>
+        <v>-12.43</v>
       </c>
       <c r="K44" t="n">
-        <v>36.84</v>
+        <v>38.77</v>
       </c>
       <c r="L44" t="n">
-        <v>38.68</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.03</v>
+        <v>-35.23</v>
       </c>
       <c r="K45" t="n">
-        <v>31.09</v>
+        <v>31.26</v>
       </c>
       <c r="L45" t="n">
-        <v>46.84</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>41.51</v>
+        <v>42.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.29</v>
+        <v>-4.4</v>
       </c>
       <c r="L46" t="n">
-        <v>41.73</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>106.76</v>
+        <v>100.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.6</v>
+        <v>-12.76</v>
       </c>
       <c r="L47" t="n">
-        <v>107.62</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-71.61</v>
+        <v>-69.66</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.96</v>
+        <v>-32.05</v>
       </c>
       <c r="L48" t="n">
-        <v>78.83</v>
+        <v>76.68000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>62.3</v>
+        <v>62.09</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.47</v>
+        <v>-13.43</v>
       </c>
       <c r="L49" t="n">
-        <v>63.74</v>
+        <v>63.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.56</v>
+        <v>-13.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-89.34999999999999</v>
+        <v>-89.29000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>90.38</v>
+        <v>90.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>83.34999999999999</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>70.92</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>109.44</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>39.51</v>
+        <v>39.6</v>
       </c>
       <c r="K52" t="n">
-        <v>89.09</v>
+        <v>89.28</v>
       </c>
       <c r="L52" t="n">
-        <v>97.45999999999999</v>
+        <v>97.67</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-86.73999999999999</v>
+        <v>-84.63</v>
       </c>
       <c r="K53" t="n">
-        <v>116.8</v>
+        <v>113.95</v>
       </c>
       <c r="L53" t="n">
-        <v>145.49</v>
+        <v>141.94</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-52.56</v>
+        <v>-51.3</v>
       </c>
       <c r="K54" t="n">
-        <v>148.62</v>
+        <v>145.07</v>
       </c>
       <c r="L54" t="n">
-        <v>157.64</v>
+        <v>153.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-27.77</v>
+        <v>-30.38</v>
       </c>
       <c r="K55" t="n">
-        <v>-66.12</v>
+        <v>-72.34999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>71.70999999999999</v>
+        <v>78.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>18.62</v>
+        <v>19.82</v>
       </c>
       <c r="K56" t="n">
-        <v>-9.5</v>
+        <v>-10.11</v>
       </c>
       <c r="L56" t="n">
-        <v>20.9</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-61.71</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>86.97</v>
+        <v>95.7</v>
       </c>
       <c r="L57" t="n">
-        <v>106.64</v>
+        <v>117.34</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-113.57</v>
+        <v>-121.9</v>
       </c>
       <c r="K58" t="n">
-        <v>-46.12</v>
+        <v>-49.5</v>
       </c>
       <c r="L58" t="n">
-        <v>122.58</v>
+        <v>131.56</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-29.09</v>
+        <v>-28.47</v>
       </c>
       <c r="K59" t="n">
-        <v>52.81</v>
+        <v>51.68</v>
       </c>
       <c r="L59" t="n">
-        <v>60.3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.65</v>
+        <v>-11.66</v>
       </c>
       <c r="K60" t="n">
-        <v>31.24</v>
+        <v>34.2</v>
       </c>
       <c r="L60" t="n">
-        <v>33</v>
+        <v>36.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>31.85</v>
+        <v>32.61</v>
       </c>
       <c r="K61" t="n">
-        <v>-40.03</v>
+        <v>-40.98</v>
       </c>
       <c r="L61" t="n">
-        <v>51.16</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-35.59</v>
+        <v>-37.65</v>
       </c>
       <c r="K62" t="n">
-        <v>33.04</v>
+        <v>34.95</v>
       </c>
       <c r="L62" t="n">
-        <v>48.56</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>72.06999999999999</v>
+        <v>70.42</v>
       </c>
       <c r="K63" t="n">
-        <v>14.1</v>
+        <v>13.78</v>
       </c>
       <c r="L63" t="n">
-        <v>73.44</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>20.45</v>
+        <v>20.56</v>
       </c>
       <c r="K64" t="n">
-        <v>-60.65</v>
+        <v>-60.97</v>
       </c>
       <c r="L64" t="n">
-        <v>64</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-77.83</v>
+        <v>-80.53</v>
       </c>
       <c r="K65" t="n">
-        <v>9.06</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>78.34999999999999</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-138.09</v>
+        <v>-130.36</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.04</v>
+        <v>-56.68</v>
       </c>
       <c r="L66" t="n">
-        <v>150.58</v>
+        <v>142.15</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>45.45</v>
+        <v>44.53</v>
       </c>
       <c r="K67" t="n">
-        <v>-112.25</v>
+        <v>-109.97</v>
       </c>
       <c r="L67" t="n">
-        <v>121.1</v>
+        <v>118.65</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-122.04</v>
+        <v>-117.15</v>
       </c>
       <c r="K68" t="n">
-        <v>106.41</v>
+        <v>102.15</v>
       </c>
       <c r="L68" t="n">
-        <v>161.92</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>26.1</v>
+        <v>28.04</v>
       </c>
       <c r="K69" t="n">
-        <v>93.58</v>
+        <v>100.51</v>
       </c>
       <c r="L69" t="n">
-        <v>97.16</v>
+        <v>104.35</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>70.22</v>
+        <v>69.03</v>
       </c>
       <c r="K70" t="n">
-        <v>-134.56</v>
+        <v>-132.29</v>
       </c>
       <c r="L70" t="n">
-        <v>151.78</v>
+        <v>149.22</v>
       </c>
     </row>
     <row r="71">
@@ -3037,10 +3037,10 @@
         <v>18.8</v>
       </c>
       <c r="K71" t="n">
-        <v>185.19</v>
+        <v>185.17</v>
       </c>
       <c r="L71" t="n">
-        <v>186.14</v>
+        <v>186.12</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>18.78</v>
+        <v>19.5</v>
       </c>
       <c r="K72" t="n">
-        <v>154.9</v>
+        <v>160.86</v>
       </c>
       <c r="L72" t="n">
-        <v>156.03</v>
+        <v>162.04</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>281.77</v>
+        <v>268.78</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="L73" t="n">
-        <v>281.77</v>
+        <v>268.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.09</v>
+        <v>-27.48</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.67</v>
+        <v>-35.16</v>
       </c>
       <c r="L74" t="n">
-        <v>44</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-50.21</v>
+        <v>-50.3</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.79</v>
+        <v>-28.85</v>
       </c>
       <c r="L75" t="n">
-        <v>57.88</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>21.46</v>
+        <v>23.15</v>
       </c>
       <c r="K76" t="n">
-        <v>24.3</v>
+        <v>26.22</v>
       </c>
       <c r="L76" t="n">
-        <v>32.42</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-45.67</v>
+        <v>-46.38</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.49</v>
+        <v>-34.01</v>
       </c>
       <c r="L77" t="n">
-        <v>56.63</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.42</v>
+        <v>-24.35</v>
       </c>
       <c r="K78" t="n">
-        <v>-48.55</v>
+        <v>-50.47</v>
       </c>
       <c r="L78" t="n">
-        <v>53.91</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>55.91</v>
+        <v>57.32</v>
       </c>
       <c r="K79" t="n">
-        <v>18.42</v>
+        <v>18.88</v>
       </c>
       <c r="L79" t="n">
-        <v>58.87</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>97.22</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>34.73</v>
+        <v>34.92</v>
       </c>
       <c r="L80" t="n">
-        <v>103.23</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-65.73</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>5.75</v>
+        <v>6.24</v>
       </c>
       <c r="L81" t="n">
-        <v>65.98</v>
+        <v>71.67</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-58.63</v>
+        <v>-59.89</v>
       </c>
       <c r="K82" t="n">
-        <v>54.43</v>
+        <v>55.6</v>
       </c>
       <c r="L82" t="n">
-        <v>80</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>7.11</v>
+        <v>6.79</v>
       </c>
       <c r="K83" t="n">
-        <v>179.26</v>
+        <v>171.12</v>
       </c>
       <c r="L83" t="n">
-        <v>179.41</v>
+        <v>171.25</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-123.04</v>
+        <v>-119.64</v>
       </c>
       <c r="K84" t="n">
-        <v>-74.47</v>
+        <v>-72.41</v>
       </c>
       <c r="L84" t="n">
-        <v>143.82</v>
+        <v>139.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>53.68</v>
+        <v>56.73</v>
       </c>
       <c r="K85" t="n">
-        <v>-83.08</v>
+        <v>-87.81</v>
       </c>
       <c r="L85" t="n">
-        <v>98.91</v>
+        <v>104.55</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>24.36</v>
+        <v>24.54</v>
       </c>
       <c r="K86" t="n">
-        <v>196.18</v>
+        <v>197.63</v>
       </c>
       <c r="L86" t="n">
-        <v>197.68</v>
+        <v>199.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-251.02</v>
+        <v>-239</v>
       </c>
       <c r="K87" t="n">
-        <v>-19.41</v>
+        <v>-18.48</v>
       </c>
       <c r="L87" t="n">
-        <v>251.77</v>
+        <v>239.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-121.23</v>
+        <v>-126.83</v>
       </c>
       <c r="K88" t="n">
-        <v>-73.58</v>
+        <v>-76.98</v>
       </c>
       <c r="L88" t="n">
-        <v>141.81</v>
+        <v>148.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -628,25 +628,25 @@
         <v>1.95</v>
       </c>
       <c r="F14" t="n">
-        <v>8.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>313.7</v>
+        <v>304</v>
       </c>
       <c r="H14" t="n">
-        <v>83.7</v>
+        <v>88.7</v>
       </c>
       <c r="I14" t="n">
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-39.92</v>
+        <v>-52.64</v>
       </c>
       <c r="K14" t="n">
-        <v>11.48</v>
+        <v>15.2</v>
       </c>
       <c r="L14" t="n">
-        <v>41.54</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.71</v>
       </c>
       <c r="F15" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="G15" t="n">
-        <v>286.9</v>
+        <v>287.7</v>
       </c>
       <c r="H15" t="n">
-        <v>81.3</v>
+        <v>75.2</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>12.53</v>
+        <v>16.16</v>
       </c>
       <c r="K15" t="n">
-        <v>54.02</v>
+        <v>71.13</v>
       </c>
       <c r="L15" t="n">
-        <v>55.46</v>
+        <v>72.94</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>2.33</v>
       </c>
       <c r="F16" t="n">
-        <v>7.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>305.7</v>
+        <v>285.8</v>
       </c>
       <c r="H16" t="n">
-        <v>86.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>46.62</v>
+        <v>54.62</v>
       </c>
       <c r="K16" t="n">
-        <v>24.16</v>
+        <v>28.61</v>
       </c>
       <c r="L16" t="n">
-        <v>52.51</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.63</v>
       </c>
       <c r="F17" t="n">
-        <v>8.31</v>
+        <v>1.93</v>
       </c>
       <c r="G17" t="n">
-        <v>307.3</v>
+        <v>298.3</v>
       </c>
       <c r="H17" t="n">
-        <v>80</v>
+        <v>85.5</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>41.98</v>
+        <v>42.24</v>
       </c>
       <c r="K17" t="n">
-        <v>47.44</v>
+        <v>49.19</v>
       </c>
       <c r="L17" t="n">
-        <v>63.35</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.33</v>
       </c>
       <c r="F18" t="n">
-        <v>8.41</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>304.1</v>
+        <v>300.3</v>
       </c>
       <c r="H18" t="n">
-        <v>85.2</v>
+        <v>83.8</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.29</v>
+        <v>-20.31</v>
       </c>
       <c r="K18" t="n">
-        <v>-65.5</v>
+        <v>-83.56</v>
       </c>
       <c r="L18" t="n">
-        <v>67.04000000000001</v>
+        <v>85.98999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>1.73</v>
       </c>
       <c r="F19" t="n">
-        <v>8.699999999999999</v>
+        <v>6.69</v>
       </c>
       <c r="G19" t="n">
-        <v>297.9</v>
+        <v>306.2</v>
       </c>
       <c r="H19" t="n">
-        <v>86.7</v>
+        <v>80.7</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-19.03</v>
+        <v>-27.12</v>
       </c>
       <c r="K19" t="n">
-        <v>45.99</v>
+        <v>63.17</v>
       </c>
       <c r="L19" t="n">
-        <v>49.77</v>
+        <v>68.73999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>1.93</v>
       </c>
       <c r="F20" t="n">
-        <v>8.359999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="G20" t="n">
-        <v>288.7</v>
+        <v>299.5</v>
       </c>
       <c r="H20" t="n">
-        <v>83.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-31.58</v>
+        <v>-44.71</v>
       </c>
       <c r="K20" t="n">
-        <v>64.63</v>
+        <v>79.52</v>
       </c>
       <c r="L20" t="n">
-        <v>71.94</v>
+        <v>91.22</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>2.14</v>
       </c>
       <c r="F21" t="n">
-        <v>8.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>293.2</v>
+        <v>306.8</v>
       </c>
       <c r="H21" t="n">
-        <v>75.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.13</v>
+        <v>-44.05</v>
       </c>
       <c r="K21" t="n">
-        <v>64.34999999999999</v>
+        <v>82.08</v>
       </c>
       <c r="L21" t="n">
-        <v>71.06</v>
+        <v>93.15000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>1.92</v>
       </c>
       <c r="F22" t="n">
-        <v>8.56</v>
+        <v>6.72</v>
       </c>
       <c r="G22" t="n">
-        <v>298.3</v>
+        <v>303.5</v>
       </c>
       <c r="H22" t="n">
-        <v>80.7</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.27</v>
+        <v>-17.12</v>
       </c>
       <c r="K22" t="n">
-        <v>-60.47</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>60.47</v>
+        <v>74.67</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.59</v>
       </c>
       <c r="F23" t="n">
-        <v>7.68</v>
+        <v>9.27</v>
       </c>
       <c r="G23" t="n">
-        <v>287.6</v>
+        <v>285.9</v>
       </c>
       <c r="H23" t="n">
-        <v>82.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>133.16</v>
+        <v>178.42</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.95</v>
+        <v>-17.99</v>
       </c>
       <c r="L23" t="n">
-        <v>134</v>
+        <v>179.33</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>2.36</v>
       </c>
       <c r="F24" t="n">
-        <v>8.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>287.5</v>
+        <v>305.7</v>
       </c>
       <c r="H24" t="n">
-        <v>82.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>91.42</v>
+        <v>101.87</v>
       </c>
       <c r="K24" t="n">
-        <v>-92.34999999999999</v>
+        <v>-102.99</v>
       </c>
       <c r="L24" t="n">
-        <v>129.95</v>
+        <v>144.86</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.07</v>
       </c>
       <c r="F25" t="n">
-        <v>8.039999999999999</v>
+        <v>7.09</v>
       </c>
       <c r="G25" t="n">
-        <v>296.1</v>
+        <v>293</v>
       </c>
       <c r="H25" t="n">
-        <v>82.5</v>
+        <v>79.8</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>94.81</v>
+        <v>114.69</v>
       </c>
       <c r="K25" t="n">
-        <v>-70.33</v>
+        <v>-91.25</v>
       </c>
       <c r="L25" t="n">
-        <v>118.05</v>
+        <v>146.57</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.18</v>
       </c>
       <c r="F26" t="n">
-        <v>7.62</v>
+        <v>5.17</v>
       </c>
       <c r="G26" t="n">
-        <v>306.5</v>
+        <v>284.6</v>
       </c>
       <c r="H26" t="n">
-        <v>76.2</v>
+        <v>85</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-111.25</v>
+        <v>-155.23</v>
       </c>
       <c r="K26" t="n">
-        <v>-48.47</v>
+        <v>-34.79</v>
       </c>
       <c r="L26" t="n">
-        <v>121.35</v>
+        <v>159.08</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>2.14</v>
       </c>
       <c r="F27" t="n">
-        <v>7.8</v>
+        <v>5.84</v>
       </c>
       <c r="G27" t="n">
-        <v>299.1</v>
+        <v>288.2</v>
       </c>
       <c r="H27" t="n">
-        <v>83.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>141.28</v>
+        <v>133.2</v>
       </c>
       <c r="K27" t="n">
-        <v>189.34</v>
+        <v>220.66</v>
       </c>
       <c r="L27" t="n">
-        <v>236.24</v>
+        <v>257.75</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.23</v>
       </c>
       <c r="F28" t="n">
-        <v>8.59</v>
+        <v>9.17</v>
       </c>
       <c r="G28" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H28" t="n">
-        <v>82.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>128.78</v>
+        <v>38.42</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.45</v>
+        <v>53.86</v>
       </c>
       <c r="L28" t="n">
-        <v>128.86</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>1.91</v>
       </c>
       <c r="F29" t="n">
-        <v>7.76</v>
+        <v>7.74</v>
       </c>
       <c r="G29" t="n">
-        <v>302.7</v>
+        <v>287.5</v>
       </c>
       <c r="H29" t="n">
-        <v>81.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>53.62</v>
+        <v>69.95</v>
       </c>
       <c r="K29" t="n">
-        <v>2.26</v>
+        <v>2.96</v>
       </c>
       <c r="L29" t="n">
-        <v>53.67</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>2.06</v>
       </c>
       <c r="F30" t="n">
-        <v>8.380000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>290</v>
+        <v>299.8</v>
       </c>
       <c r="H30" t="n">
-        <v>89</v>
+        <v>76.8</v>
       </c>
       <c r="I30" t="n">
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-34.4</v>
+        <v>-46.22</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.72</v>
+        <v>-2.95</v>
       </c>
       <c r="L30" t="n">
-        <v>34.51</v>
+        <v>46.31</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>2.43</v>
       </c>
       <c r="F31" t="n">
-        <v>8.130000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>318.1</v>
+        <v>294.8</v>
       </c>
       <c r="H31" t="n">
-        <v>79.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-56.59</v>
+        <v>-64</v>
       </c>
       <c r="K31" t="n">
-        <v>44.64</v>
+        <v>50.01</v>
       </c>
       <c r="L31" t="n">
-        <v>72.08</v>
+        <v>81.22</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>2.35</v>
       </c>
       <c r="F32" t="n">
-        <v>8.33</v>
+        <v>5.47</v>
       </c>
       <c r="G32" t="n">
-        <v>309.9</v>
+        <v>298.8</v>
       </c>
       <c r="H32" t="n">
-        <v>75.3</v>
+        <v>86.7</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-68.77</v>
+        <v>-75.69</v>
       </c>
       <c r="K32" t="n">
-        <v>61.22</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>92.06999999999999</v>
+        <v>100.85</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>2.3</v>
       </c>
       <c r="F33" t="n">
-        <v>8.109999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>293.6</v>
+        <v>294.5</v>
       </c>
       <c r="H33" t="n">
-        <v>77.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="K33" t="n">
-        <v>-74.31</v>
+        <v>-102.2</v>
       </c>
       <c r="L33" t="n">
-        <v>74.44</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>2.32</v>
       </c>
       <c r="F34" t="n">
-        <v>8.19</v>
+        <v>6.94</v>
       </c>
       <c r="G34" t="n">
-        <v>301</v>
+        <v>296.1</v>
       </c>
       <c r="H34" t="n">
-        <v>78.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I34" t="n">
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-38.46</v>
+        <v>-46.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-51.23</v>
+        <v>-58.59</v>
       </c>
       <c r="L34" t="n">
-        <v>64.06</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>2.38</v>
       </c>
       <c r="F35" t="n">
-        <v>8.789999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>290.8</v>
+        <v>308</v>
       </c>
       <c r="H35" t="n">
-        <v>81.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>45.26</v>
+        <v>52.47</v>
       </c>
       <c r="K35" t="n">
-        <v>81.56999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="L35" t="n">
-        <v>93.28</v>
+        <v>121.78</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>1.94</v>
       </c>
       <c r="F36" t="n">
-        <v>8.19</v>
+        <v>6.78</v>
       </c>
       <c r="G36" t="n">
-        <v>287.9</v>
+        <v>296.1</v>
       </c>
       <c r="H36" t="n">
-        <v>80.2</v>
+        <v>75.7</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>12.51</v>
+        <v>10.52</v>
       </c>
       <c r="K36" t="n">
-        <v>-86.77</v>
+        <v>-104.55</v>
       </c>
       <c r="L36" t="n">
-        <v>87.66</v>
+        <v>105.08</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>1.7</v>
       </c>
       <c r="F37" t="n">
-        <v>7.71</v>
+        <v>6.09</v>
       </c>
       <c r="G37" t="n">
-        <v>296</v>
+        <v>286.4</v>
       </c>
       <c r="H37" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.55</v>
+        <v>-37.83</v>
       </c>
       <c r="K37" t="n">
-        <v>95.09</v>
+        <v>107.09</v>
       </c>
       <c r="L37" t="n">
-        <v>99.56999999999999</v>
+        <v>113.57</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>2.14</v>
       </c>
       <c r="F38" t="n">
-        <v>8.59</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H38" t="n">
-        <v>81.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>67.90000000000001</v>
+        <v>50.77</v>
       </c>
       <c r="K38" t="n">
-        <v>-44.96</v>
+        <v>-33.67</v>
       </c>
       <c r="L38" t="n">
-        <v>81.44</v>
+        <v>60.92</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>2.63</v>
       </c>
       <c r="F39" t="n">
-        <v>8.130000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>301.4</v>
+        <v>294.8</v>
       </c>
       <c r="H39" t="n">
-        <v>81</v>
+        <v>82.5</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>-24.73</v>
+        <v>-44.85</v>
       </c>
       <c r="K39" t="n">
-        <v>-150.46</v>
+        <v>-157.5</v>
       </c>
       <c r="L39" t="n">
-        <v>152.48</v>
+        <v>163.76</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.13</v>
       </c>
       <c r="F40" t="n">
-        <v>8.5</v>
+        <v>3.98</v>
       </c>
       <c r="G40" t="n">
-        <v>299.3</v>
+        <v>302.1</v>
       </c>
       <c r="H40" t="n">
-        <v>74</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>39.66</v>
+        <v>28.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-150.66</v>
+        <v>-136.86</v>
       </c>
       <c r="L40" t="n">
-        <v>155.8</v>
+        <v>139.82</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>1.78</v>
       </c>
       <c r="F41" t="n">
-        <v>8.33</v>
+        <v>4.26</v>
       </c>
       <c r="G41" t="n">
-        <v>292.7</v>
+        <v>298.8</v>
       </c>
       <c r="H41" t="n">
-        <v>83.3</v>
+        <v>78.2</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>126.69</v>
+        <v>106.03</v>
       </c>
       <c r="K41" t="n">
-        <v>44.96</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>134.44</v>
+        <v>137.13</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>2.02</v>
       </c>
       <c r="F42" t="n">
-        <v>8.470000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="G42" t="n">
-        <v>288.5</v>
+        <v>301.6</v>
       </c>
       <c r="H42" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>170.46</v>
+        <v>191.06</v>
       </c>
       <c r="K42" t="n">
-        <v>101.79</v>
+        <v>154.1</v>
       </c>
       <c r="L42" t="n">
-        <v>198.54</v>
+        <v>245.46</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>2.12</v>
       </c>
       <c r="F43" t="n">
-        <v>8.02</v>
+        <v>4.92</v>
       </c>
       <c r="G43" t="n">
-        <v>291.9</v>
+        <v>292.6</v>
       </c>
       <c r="H43" t="n">
-        <v>86</v>
+        <v>77.7</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-140.09</v>
+        <v>-171.78</v>
       </c>
       <c r="K43" t="n">
-        <v>-143.59</v>
+        <v>-139.5</v>
       </c>
       <c r="L43" t="n">
-        <v>200.61</v>
+        <v>221.28</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.15</v>
       </c>
       <c r="F44" t="n">
-        <v>8.51</v>
+        <v>6.39</v>
       </c>
       <c r="G44" t="n">
-        <v>292</v>
+        <v>302.4</v>
       </c>
       <c r="H44" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.43</v>
+        <v>-13.67</v>
       </c>
       <c r="K44" t="n">
-        <v>38.77</v>
+        <v>41.42</v>
       </c>
       <c r="L44" t="n">
-        <v>40.72</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.13</v>
       </c>
       <c r="F45" t="n">
-        <v>8.33</v>
+        <v>9.08</v>
       </c>
       <c r="G45" t="n">
-        <v>297</v>
+        <v>298.8</v>
       </c>
       <c r="H45" t="n">
-        <v>83.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.23</v>
+        <v>-44.2</v>
       </c>
       <c r="K45" t="n">
-        <v>31.26</v>
+        <v>39.09</v>
       </c>
       <c r="L45" t="n">
-        <v>47.1</v>
+        <v>59.01</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2.29</v>
       </c>
       <c r="F46" t="n">
-        <v>8.58</v>
+        <v>9.27</v>
       </c>
       <c r="G46" t="n">
-        <v>298.6</v>
+        <v>303.8</v>
       </c>
       <c r="H46" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>42.59</v>
+        <v>57.62</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.4</v>
+        <v>-5.48</v>
       </c>
       <c r="L46" t="n">
-        <v>42.82</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>2.55</v>
       </c>
       <c r="F47" t="n">
-        <v>8.01</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>300.2</v>
+        <v>292.3</v>
       </c>
       <c r="H47" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>100.14</v>
+        <v>124.36</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.76</v>
+        <v>-15.65</v>
       </c>
       <c r="L47" t="n">
-        <v>100.95</v>
+        <v>125.34</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>2.2</v>
       </c>
       <c r="F48" t="n">
-        <v>8.029999999999999</v>
+        <v>7.21</v>
       </c>
       <c r="G48" t="n">
-        <v>310.6</v>
+        <v>292.8</v>
       </c>
       <c r="H48" t="n">
-        <v>78.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.66</v>
+        <v>-84.06999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.05</v>
+        <v>-37.79</v>
       </c>
       <c r="L48" t="n">
-        <v>76.68000000000001</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>1.73</v>
       </c>
       <c r="F49" t="n">
-        <v>8.66</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>284.9</v>
+        <v>305.4</v>
       </c>
       <c r="H49" t="n">
-        <v>79.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>62.09</v>
+        <v>80.72</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.43</v>
+        <v>-16.41</v>
       </c>
       <c r="L49" t="n">
-        <v>63.52</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.03</v>
       </c>
       <c r="F50" t="n">
-        <v>8.1</v>
+        <v>9.44</v>
       </c>
       <c r="G50" t="n">
-        <v>296.4</v>
+        <v>294.2</v>
       </c>
       <c r="H50" t="n">
-        <v>83.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.55</v>
+        <v>-25.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-89.29000000000001</v>
+        <v>-119.87</v>
       </c>
       <c r="L50" t="n">
-        <v>90.31</v>
+        <v>122.54</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>2.31</v>
       </c>
       <c r="F51" t="n">
-        <v>8.539999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="G51" t="n">
-        <v>300.6</v>
+        <v>302.9</v>
       </c>
       <c r="H51" t="n">
-        <v>83.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>82.29000000000001</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>70.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>108.04</v>
+        <v>118.75</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>2.32</v>
       </c>
       <c r="F52" t="n">
-        <v>7.76</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>294.7</v>
+        <v>287.4</v>
       </c>
       <c r="H52" t="n">
-        <v>83.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>39.6</v>
+        <v>40.68</v>
       </c>
       <c r="K52" t="n">
-        <v>89.28</v>
+        <v>112.48</v>
       </c>
       <c r="L52" t="n">
-        <v>97.67</v>
+        <v>119.61</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>1.97</v>
       </c>
       <c r="F53" t="n">
-        <v>8.449999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="G53" t="n">
-        <v>283.1</v>
+        <v>301.2</v>
       </c>
       <c r="H53" t="n">
-        <v>80.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-84.63</v>
+        <v>-114.43</v>
       </c>
       <c r="K53" t="n">
-        <v>113.95</v>
+        <v>148.84</v>
       </c>
       <c r="L53" t="n">
-        <v>141.94</v>
+        <v>187.74</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>2.7</v>
       </c>
       <c r="F54" t="n">
-        <v>9.01</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>298.5</v>
+        <v>312.4</v>
       </c>
       <c r="H54" t="n">
-        <v>79.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.3</v>
+        <v>-72.94</v>
       </c>
       <c r="K54" t="n">
-        <v>145.07</v>
+        <v>185.19</v>
       </c>
       <c r="L54" t="n">
-        <v>153.88</v>
+        <v>199.03</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.12</v>
       </c>
       <c r="F55" t="n">
-        <v>7.88</v>
+        <v>4.74</v>
       </c>
       <c r="G55" t="n">
         <v>284.9</v>
       </c>
       <c r="H55" t="n">
-        <v>80.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-30.38</v>
+        <v>111.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-72.34999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="L55" t="n">
-        <v>78.47</v>
+        <v>111.21</v>
       </c>
     </row>
     <row r="56">
@@ -2389,10 +2389,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="F56" t="n">
-        <v>7.25</v>
+        <v>7.7</v>
       </c>
       <c r="G56" t="n">
         <v>306.1</v>
@@ -2401,16 +2401,16 @@
         <v>82.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>19.82</v>
+        <v>-187.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-10.11</v>
+        <v>60.09</v>
       </c>
       <c r="L56" t="n">
-        <v>22.25</v>
+        <v>197.08</v>
       </c>
     </row>
     <row r="57">
@@ -2431,10 +2431,10 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="F57" t="n">
-        <v>8.76</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G57" t="n">
         <v>296.2</v>
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-67.90000000000001</v>
+        <v>-152.35</v>
       </c>
       <c r="K57" t="n">
-        <v>95.7</v>
+        <v>-123.24</v>
       </c>
       <c r="L57" t="n">
-        <v>117.34</v>
+        <v>195.96</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="F58" t="n">
-        <v>8.27</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>308.1</v>
+        <v>305.9</v>
       </c>
       <c r="H58" t="n">
-        <v>84.7</v>
+        <v>79.7</v>
       </c>
       <c r="I58" t="n">
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-121.9</v>
+        <v>-160.66</v>
       </c>
       <c r="K58" t="n">
-        <v>-49.5</v>
+        <v>-6.44</v>
       </c>
       <c r="L58" t="n">
-        <v>131.56</v>
+        <v>160.79</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="F59" t="n">
-        <v>9.16</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>290.5</v>
+        <v>289.2</v>
       </c>
       <c r="H59" t="n">
-        <v>76.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-28.47</v>
+        <v>82.97</v>
       </c>
       <c r="K59" t="n">
-        <v>51.68</v>
+        <v>-6.61</v>
       </c>
       <c r="L59" t="n">
-        <v>59</v>
+        <v>83.23</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="F60" t="n">
-        <v>8.23</v>
+        <v>8.57</v>
       </c>
       <c r="G60" t="n">
-        <v>295.7</v>
+        <v>297.1</v>
       </c>
       <c r="H60" t="n">
-        <v>80.3</v>
+        <v>83.2</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.66</v>
+        <v>-8.74</v>
       </c>
       <c r="K60" t="n">
-        <v>34.2</v>
+        <v>-62.08</v>
       </c>
       <c r="L60" t="n">
-        <v>36.13</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="61">
@@ -2599,10 +2599,10 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="F61" t="n">
-        <v>8.65</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G61" t="n">
         <v>320.1</v>
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>32.61</v>
+        <v>-56.04</v>
       </c>
       <c r="K61" t="n">
-        <v>-40.98</v>
+        <v>41.66</v>
       </c>
       <c r="L61" t="n">
-        <v>52.37</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="62">
@@ -2641,10 +2641,10 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="F62" t="n">
-        <v>7.84</v>
+        <v>7.24</v>
       </c>
       <c r="G62" t="n">
         <v>283.2</v>
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-37.65</v>
+        <v>-6.09</v>
       </c>
       <c r="K62" t="n">
-        <v>34.95</v>
+        <v>-60.33</v>
       </c>
       <c r="L62" t="n">
-        <v>51.37</v>
+        <v>60.64</v>
       </c>
     </row>
     <row r="63">
@@ -2683,10 +2683,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="F63" t="n">
-        <v>7.86</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>284.5</v>
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>70.42</v>
+        <v>19.88</v>
       </c>
       <c r="K63" t="n">
-        <v>13.78</v>
+        <v>92.8</v>
       </c>
       <c r="L63" t="n">
-        <v>71.76000000000001</v>
+        <v>94.91</v>
       </c>
     </row>
     <row r="64">
@@ -2725,10 +2725,10 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="F64" t="n">
-        <v>7.82</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G64" t="n">
         <v>294.3</v>
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>20.56</v>
+        <v>-80.84999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-60.97</v>
+        <v>25.85</v>
       </c>
       <c r="L64" t="n">
-        <v>64.34999999999999</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="65">
@@ -2767,10 +2767,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="F65" t="n">
-        <v>8.43</v>
+        <v>4.8</v>
       </c>
       <c r="G65" t="n">
         <v>309.5</v>
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-80.53</v>
+        <v>87.73</v>
       </c>
       <c r="K65" t="n">
-        <v>9.380000000000001</v>
+        <v>-52.1</v>
       </c>
       <c r="L65" t="n">
-        <v>81.06999999999999</v>
+        <v>102.03</v>
       </c>
     </row>
     <row r="66">
@@ -2809,10 +2809,10 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="F66" t="n">
-        <v>7.81</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>292.4</v>
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-130.36</v>
+        <v>-97.81</v>
       </c>
       <c r="K66" t="n">
-        <v>-56.68</v>
+        <v>-144.76</v>
       </c>
       <c r="L66" t="n">
-        <v>142.15</v>
+        <v>174.71</v>
       </c>
     </row>
     <row r="67">
@@ -2851,10 +2851,10 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.46</v>
+        <v>2.01</v>
       </c>
       <c r="F67" t="n">
-        <v>8.43</v>
+        <v>4.22</v>
       </c>
       <c r="G67" t="n">
         <v>293.1</v>
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>44.53</v>
+        <v>56.79</v>
       </c>
       <c r="K67" t="n">
-        <v>-109.97</v>
+        <v>76.41</v>
       </c>
       <c r="L67" t="n">
-        <v>118.65</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="F68" t="n">
-        <v>7.88</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>285.4</v>
+        <v>289.8</v>
       </c>
       <c r="H68" t="n">
-        <v>90.7</v>
+        <v>74.5</v>
       </c>
       <c r="I68" t="n">
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-117.15</v>
+        <v>-150.75</v>
       </c>
       <c r="K68" t="n">
-        <v>102.15</v>
+        <v>125.46</v>
       </c>
       <c r="L68" t="n">
-        <v>155.43</v>
+        <v>196.12</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>2.95</v>
       </c>
       <c r="F69" t="n">
-        <v>8.17</v>
+        <v>8.57</v>
       </c>
       <c r="G69" t="n">
-        <v>296.2</v>
+        <v>295.7</v>
       </c>
       <c r="H69" t="n">
-        <v>72</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>28.04</v>
+        <v>-14.36</v>
       </c>
       <c r="K69" t="n">
-        <v>100.51</v>
+        <v>136.22</v>
       </c>
       <c r="L69" t="n">
-        <v>104.35</v>
+        <v>136.98</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>2.39</v>
       </c>
       <c r="F70" t="n">
-        <v>8.31</v>
+        <v>6.88</v>
       </c>
       <c r="G70" t="n">
-        <v>303.5</v>
+        <v>298.3</v>
       </c>
       <c r="H70" t="n">
-        <v>76.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>69.03</v>
+        <v>63.06</v>
       </c>
       <c r="K70" t="n">
-        <v>-132.29</v>
+        <v>-144.04</v>
       </c>
       <c r="L70" t="n">
-        <v>149.22</v>
+        <v>157.24</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>1.94</v>
       </c>
       <c r="F71" t="n">
-        <v>8.74</v>
+        <v>5.24</v>
       </c>
       <c r="G71" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H71" t="n">
-        <v>83.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I71" t="n">
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>18.8</v>
+        <v>-4.09</v>
       </c>
       <c r="K71" t="n">
-        <v>185.17</v>
+        <v>215.43</v>
       </c>
       <c r="L71" t="n">
-        <v>186.12</v>
+        <v>215.47</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>2.45</v>
       </c>
       <c r="F72" t="n">
-        <v>8.18</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>299.1</v>
+        <v>295.8</v>
       </c>
       <c r="H72" t="n">
-        <v>86.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>19.5</v>
+        <v>-30.3</v>
       </c>
       <c r="K72" t="n">
-        <v>160.86</v>
+        <v>191.95</v>
       </c>
       <c r="L72" t="n">
-        <v>162.04</v>
+        <v>194.33</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>2.65</v>
       </c>
       <c r="F73" t="n">
-        <v>8.279999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>297.8</v>
+        <v>297.9</v>
       </c>
       <c r="H73" t="n">
-        <v>73</v>
+        <v>80.7</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>268.78</v>
+        <v>265.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.63</v>
+        <v>15.83</v>
       </c>
       <c r="L73" t="n">
-        <v>268.78</v>
+        <v>266.21</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>2.24</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>282.2</v>
+        <v>292.1</v>
       </c>
       <c r="H74" t="n">
-        <v>84.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.48</v>
+        <v>-36.9</v>
       </c>
       <c r="K74" t="n">
-        <v>-35.16</v>
+        <v>-46.03</v>
       </c>
       <c r="L74" t="n">
-        <v>44.63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>2.7</v>
       </c>
       <c r="F75" t="n">
-        <v>7.98</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>296.3</v>
+        <v>291.8</v>
       </c>
       <c r="H75" t="n">
-        <v>79.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-50.3</v>
+        <v>-59.93</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.85</v>
+        <v>-33.68</v>
       </c>
       <c r="L75" t="n">
-        <v>57.99</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>2.07</v>
       </c>
       <c r="F76" t="n">
-        <v>8.98</v>
+        <v>8.73</v>
       </c>
       <c r="G76" t="n">
-        <v>300.1</v>
+        <v>311.8</v>
       </c>
       <c r="H76" t="n">
         <v>81.8</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>23.15</v>
+        <v>27.43</v>
       </c>
       <c r="K76" t="n">
-        <v>26.22</v>
+        <v>32.81</v>
       </c>
       <c r="L76" t="n">
-        <v>34.97</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>2.29</v>
       </c>
       <c r="F77" t="n">
-        <v>8.16</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>296.2</v>
+        <v>295.3</v>
       </c>
       <c r="H77" t="n">
-        <v>82.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-46.38</v>
+        <v>-68.5</v>
       </c>
       <c r="K77" t="n">
-        <v>-34.01</v>
+        <v>-47.72</v>
       </c>
       <c r="L77" t="n">
-        <v>57.52</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>2.06</v>
       </c>
       <c r="F78" t="n">
-        <v>8.41</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>290.9</v>
+        <v>300.5</v>
       </c>
       <c r="H78" t="n">
-        <v>85.7</v>
+        <v>77.3</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-24.35</v>
+        <v>-35.29</v>
       </c>
       <c r="K78" t="n">
-        <v>-50.47</v>
+        <v>-67.11</v>
       </c>
       <c r="L78" t="n">
-        <v>56.04</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>2.52</v>
       </c>
       <c r="F79" t="n">
-        <v>7.8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>293</v>
+        <v>288.2</v>
       </c>
       <c r="H79" t="n">
-        <v>79.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>57.32</v>
+        <v>67.33</v>
       </c>
       <c r="K79" t="n">
-        <v>18.88</v>
+        <v>23.61</v>
       </c>
       <c r="L79" t="n">
-        <v>60.35</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>2.96</v>
       </c>
       <c r="F80" t="n">
-        <v>8.49</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>295.7</v>
+        <v>302</v>
       </c>
       <c r="H80" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>97.76000000000001</v>
+        <v>98.56</v>
       </c>
       <c r="K80" t="n">
-        <v>34.92</v>
+        <v>44.63</v>
       </c>
       <c r="L80" t="n">
-        <v>103.81</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>2.44</v>
       </c>
       <c r="F81" t="n">
-        <v>8.9</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>297.3</v>
+        <v>310.3</v>
       </c>
       <c r="H81" t="n">
-        <v>81.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-71.40000000000001</v>
+        <v>-86</v>
       </c>
       <c r="K81" t="n">
-        <v>6.24</v>
+        <v>20.2</v>
       </c>
       <c r="L81" t="n">
-        <v>71.67</v>
+        <v>88.34</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>2.43</v>
       </c>
       <c r="F82" t="n">
-        <v>7.95</v>
+        <v>6.64</v>
       </c>
       <c r="G82" t="n">
-        <v>285.9</v>
+        <v>291.1</v>
       </c>
       <c r="H82" t="n">
-        <v>75.5</v>
+        <v>74.7</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-59.89</v>
+        <v>-70.16</v>
       </c>
       <c r="K82" t="n">
-        <v>55.6</v>
+        <v>61.67</v>
       </c>
       <c r="L82" t="n">
-        <v>81.72</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>2.34</v>
       </c>
       <c r="F83" t="n">
-        <v>8.539999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="G83" t="n">
-        <v>302.9</v>
+        <v>303</v>
       </c>
       <c r="H83" t="n">
-        <v>79.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>6.79</v>
+        <v>-3.4</v>
       </c>
       <c r="K83" t="n">
-        <v>171.12</v>
+        <v>184.95</v>
       </c>
       <c r="L83" t="n">
-        <v>171.25</v>
+        <v>184.98</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>2.38</v>
       </c>
       <c r="F84" t="n">
-        <v>8.24</v>
+        <v>9.17</v>
       </c>
       <c r="G84" t="n">
-        <v>298.9</v>
+        <v>297</v>
       </c>
       <c r="H84" t="n">
-        <v>80.2</v>
+        <v>81.3</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-119.64</v>
+        <v>-172.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-72.41</v>
+        <v>-87.88</v>
       </c>
       <c r="L84" t="n">
-        <v>139.84</v>
+        <v>193.24</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>2.35</v>
       </c>
       <c r="F85" t="n">
-        <v>8.66</v>
+        <v>8.16</v>
       </c>
       <c r="G85" t="n">
-        <v>298.7</v>
+        <v>305.3</v>
       </c>
       <c r="H85" t="n">
-        <v>80.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>56.73</v>
+        <v>49.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-87.81</v>
+        <v>-98.91</v>
       </c>
       <c r="L85" t="n">
-        <v>104.55</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>2.55</v>
       </c>
       <c r="F86" t="n">
-        <v>8.539999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>303.9</v>
+        <v>302.9</v>
       </c>
       <c r="H86" t="n">
-        <v>84.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>24.54</v>
+        <v>-16.86</v>
       </c>
       <c r="K86" t="n">
-        <v>197.63</v>
+        <v>270.08</v>
       </c>
       <c r="L86" t="n">
-        <v>199.15</v>
+        <v>270.61</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>2.23</v>
       </c>
       <c r="F87" t="n">
-        <v>8.27</v>
+        <v>9.41</v>
       </c>
       <c r="G87" t="n">
-        <v>291.6</v>
+        <v>297.6</v>
       </c>
       <c r="H87" t="n">
-        <v>82.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I87" t="n">
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-239</v>
+        <v>-305.84</v>
       </c>
       <c r="K87" t="n">
-        <v>-18.48</v>
+        <v>-7.67</v>
       </c>
       <c r="L87" t="n">
-        <v>239.71</v>
+        <v>305.93</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>2.36</v>
       </c>
       <c r="F88" t="n">
-        <v>7.97</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>288.5</v>
+        <v>291.6</v>
       </c>
       <c r="H88" t="n">
-        <v>86.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-126.83</v>
+        <v>-197.62</v>
       </c>
       <c r="K88" t="n">
-        <v>-76.98</v>
+        <v>-64.14</v>
       </c>
       <c r="L88" t="n">
-        <v>148.37</v>
+        <v>207.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-52.64</v>
+        <v>-50.45</v>
       </c>
       <c r="K14" t="n">
-        <v>15.2</v>
+        <v>14.57</v>
       </c>
       <c r="L14" t="n">
-        <v>54.79</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>16.16</v>
+        <v>15.49</v>
       </c>
       <c r="K15" t="n">
-        <v>71.13</v>
+        <v>68.16</v>
       </c>
       <c r="L15" t="n">
-        <v>72.94</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>54.62</v>
+        <v>48.55</v>
       </c>
       <c r="K16" t="n">
-        <v>28.61</v>
+        <v>25.43</v>
       </c>
       <c r="L16" t="n">
-        <v>61.66</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>42.24</v>
+        <v>41.37</v>
       </c>
       <c r="K17" t="n">
-        <v>49.19</v>
+        <v>48.19</v>
       </c>
       <c r="L17" t="n">
-        <v>64.84</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.31</v>
+        <v>-19.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-83.56</v>
+        <v>-80.08</v>
       </c>
       <c r="L18" t="n">
-        <v>85.98999999999999</v>
+        <v>82.41</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.12</v>
+        <v>-27.66</v>
       </c>
       <c r="K19" t="n">
-        <v>63.17</v>
+        <v>64.41</v>
       </c>
       <c r="L19" t="n">
-        <v>68.73999999999999</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-44.71</v>
+        <v>-40.82</v>
       </c>
       <c r="K20" t="n">
-        <v>79.52</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>91.22</v>
+        <v>83.29000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-44.05</v>
+        <v>-42.21</v>
       </c>
       <c r="K21" t="n">
-        <v>82.08</v>
+        <v>78.66</v>
       </c>
       <c r="L21" t="n">
-        <v>93.15000000000001</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.12</v>
+        <v>-17.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-72.68000000000001</v>
+        <v>-74.11</v>
       </c>
       <c r="L22" t="n">
-        <v>74.67</v>
+        <v>76.13</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>178.42</v>
+        <v>174.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-17.99</v>
+        <v>-17.62</v>
       </c>
       <c r="L23" t="n">
-        <v>179.33</v>
+        <v>175.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>101.87</v>
+        <v>95.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-102.99</v>
+        <v>-96.42</v>
       </c>
       <c r="L24" t="n">
-        <v>144.86</v>
+        <v>135.62</v>
       </c>
     </row>
     <row r="25">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-155.23</v>
+        <v>-145.32</v>
       </c>
       <c r="K26" t="n">
-        <v>-34.79</v>
+        <v>-32.57</v>
       </c>
       <c r="L26" t="n">
-        <v>159.08</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>133.2</v>
+        <v>127.65</v>
       </c>
       <c r="K27" t="n">
-        <v>220.66</v>
+        <v>211.46</v>
       </c>
       <c r="L27" t="n">
-        <v>257.75</v>
+        <v>247.01</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>38.42</v>
+        <v>39.17</v>
       </c>
       <c r="K28" t="n">
-        <v>53.86</v>
+        <v>54.91</v>
       </c>
       <c r="L28" t="n">
-        <v>66.15000000000001</v>
+        <v>67.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>69.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="L29" t="n">
-        <v>70.01000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-46.22</v>
+        <v>-41.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.95</v>
+        <v>-2.62</v>
       </c>
       <c r="L30" t="n">
-        <v>46.31</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-64</v>
+        <v>-56.89</v>
       </c>
       <c r="K31" t="n">
-        <v>50.01</v>
+        <v>44.45</v>
       </c>
       <c r="L31" t="n">
-        <v>81.22</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-75.69</v>
+        <v>-77.17</v>
       </c>
       <c r="K32" t="n">
-        <v>66.65000000000001</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>100.85</v>
+        <v>102.83</v>
       </c>
     </row>
     <row r="33">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-46.41</v>
+        <v>-45.47</v>
       </c>
       <c r="K34" t="n">
-        <v>-58.59</v>
+        <v>-57.39</v>
       </c>
       <c r="L34" t="n">
-        <v>74.75</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>52.47</v>
+        <v>49.12</v>
       </c>
       <c r="K35" t="n">
-        <v>109.9</v>
+        <v>102.89</v>
       </c>
       <c r="L35" t="n">
-        <v>121.78</v>
+        <v>114.01</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>10.52</v>
+        <v>9.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.55</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>105.08</v>
+        <v>95.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-37.83</v>
+        <v>-36.25</v>
       </c>
       <c r="K37" t="n">
-        <v>107.09</v>
+        <v>102.63</v>
       </c>
       <c r="L37" t="n">
-        <v>113.57</v>
+        <v>108.84</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>50.77</v>
+        <v>45.13</v>
       </c>
       <c r="K38" t="n">
-        <v>-33.67</v>
+        <v>-29.93</v>
       </c>
       <c r="L38" t="n">
-        <v>60.92</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>-44.85</v>
+        <v>-39.87</v>
       </c>
       <c r="K39" t="n">
-        <v>-157.5</v>
+        <v>-140</v>
       </c>
       <c r="L39" t="n">
-        <v>163.76</v>
+        <v>145.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>28.59</v>
+        <v>25.41</v>
       </c>
       <c r="K40" t="n">
-        <v>-136.86</v>
+        <v>-121.66</v>
       </c>
       <c r="L40" t="n">
-        <v>139.82</v>
+        <v>124.28</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>106.03</v>
+        <v>96.81</v>
       </c>
       <c r="K41" t="n">
-        <v>86.95999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>137.13</v>
+        <v>125.21</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>191.06</v>
+        <v>194.81</v>
       </c>
       <c r="K42" t="n">
-        <v>154.1</v>
+        <v>157.12</v>
       </c>
       <c r="L42" t="n">
-        <v>245.46</v>
+        <v>250.27</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-171.78</v>
+        <v>-164.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-139.5</v>
+        <v>-133.69</v>
       </c>
       <c r="L43" t="n">
-        <v>221.28</v>
+        <v>212.06</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-13.67</v>
+        <v>-12.48</v>
       </c>
       <c r="K44" t="n">
-        <v>41.42</v>
+        <v>37.82</v>
       </c>
       <c r="L44" t="n">
-        <v>43.62</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-44.2</v>
+        <v>-41.38</v>
       </c>
       <c r="K45" t="n">
-        <v>39.09</v>
+        <v>36.59</v>
       </c>
       <c r="L45" t="n">
-        <v>59.01</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>57.62</v>
+        <v>56.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.48</v>
+        <v>-5.37</v>
       </c>
       <c r="L46" t="n">
-        <v>57.88</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>124.36</v>
+        <v>121.82</v>
       </c>
       <c r="K47" t="n">
-        <v>-15.65</v>
+        <v>-15.33</v>
       </c>
       <c r="L47" t="n">
-        <v>125.34</v>
+        <v>122.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-84.06999999999999</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-37.79</v>
+        <v>-37.01</v>
       </c>
       <c r="L48" t="n">
-        <v>92.17</v>
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>80.72</v>
+        <v>73.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-16.41</v>
+        <v>-14.98</v>
       </c>
       <c r="L49" t="n">
-        <v>82.37</v>
+        <v>75.20999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-25.41</v>
+        <v>-24.89</v>
       </c>
       <c r="K50" t="n">
-        <v>-119.87</v>
+        <v>-117.43</v>
       </c>
       <c r="L50" t="n">
-        <v>122.54</v>
+        <v>120.04</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>85.93000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>81.95999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="L51" t="n">
-        <v>118.75</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>40.68</v>
+        <v>39.85</v>
       </c>
       <c r="K52" t="n">
-        <v>112.48</v>
+        <v>110.19</v>
       </c>
       <c r="L52" t="n">
-        <v>119.61</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-114.43</v>
+        <v>-116.67</v>
       </c>
       <c r="K53" t="n">
-        <v>148.84</v>
+        <v>151.76</v>
       </c>
       <c r="L53" t="n">
-        <v>187.74</v>
+        <v>191.42</v>
       </c>
     </row>
     <row r="54">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-187.7</v>
+        <v>-166.84</v>
       </c>
       <c r="K56" t="n">
-        <v>60.09</v>
+        <v>53.41</v>
       </c>
       <c r="L56" t="n">
-        <v>197.08</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-152.35</v>
+        <v>-139.1</v>
       </c>
       <c r="K57" t="n">
-        <v>-123.24</v>
+        <v>-112.53</v>
       </c>
       <c r="L57" t="n">
-        <v>195.96</v>
+        <v>178.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-160.66</v>
+        <v>-146.69</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.44</v>
+        <v>-5.88</v>
       </c>
       <c r="L58" t="n">
-        <v>160.79</v>
+        <v>146.8</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>82.97</v>
+        <v>81.28</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.61</v>
+        <v>-6.47</v>
       </c>
       <c r="L59" t="n">
-        <v>83.23</v>
+        <v>81.53</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.74</v>
+        <v>-8.19</v>
       </c>
       <c r="K60" t="n">
-        <v>-62.08</v>
+        <v>-58.12</v>
       </c>
       <c r="L60" t="n">
-        <v>62.69</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-56.04</v>
+        <v>-53.71</v>
       </c>
       <c r="K61" t="n">
-        <v>41.66</v>
+        <v>39.93</v>
       </c>
       <c r="L61" t="n">
-        <v>69.83</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-6.09</v>
+        <v>-5.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-60.33</v>
+        <v>-59.1</v>
       </c>
       <c r="L62" t="n">
-        <v>60.64</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>19.88</v>
+        <v>18.16</v>
       </c>
       <c r="K63" t="n">
-        <v>92.8</v>
+        <v>84.73</v>
       </c>
       <c r="L63" t="n">
-        <v>94.91</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-80.84999999999999</v>
+        <v>-73.81999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="L64" t="n">
-        <v>84.88</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>87.73</v>
+        <v>82.13</v>
       </c>
       <c r="K65" t="n">
-        <v>-52.1</v>
+        <v>-48.77</v>
       </c>
       <c r="L65" t="n">
-        <v>102.03</v>
+        <v>95.52</v>
       </c>
     </row>
     <row r="66">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>56.79</v>
+        <v>57.91</v>
       </c>
       <c r="K67" t="n">
-        <v>76.41</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>95.2</v>
+        <v>97.06999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-150.75</v>
+        <v>-134</v>
       </c>
       <c r="K68" t="n">
-        <v>125.46</v>
+        <v>111.52</v>
       </c>
       <c r="L68" t="n">
-        <v>196.12</v>
+        <v>174.33</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-14.36</v>
+        <v>-14.65</v>
       </c>
       <c r="K69" t="n">
-        <v>136.22</v>
+        <v>138.89</v>
       </c>
       <c r="L69" t="n">
-        <v>136.98</v>
+        <v>139.66</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>63.06</v>
+        <v>60.43</v>
       </c>
       <c r="K70" t="n">
-        <v>-144.04</v>
+        <v>-138.04</v>
       </c>
       <c r="L70" t="n">
-        <v>157.24</v>
+        <v>150.69</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.09</v>
+        <v>-4</v>
       </c>
       <c r="K71" t="n">
-        <v>215.43</v>
+        <v>211.04</v>
       </c>
       <c r="L71" t="n">
-        <v>215.47</v>
+        <v>211.07</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-30.3</v>
+        <v>-26.94</v>
       </c>
       <c r="K72" t="n">
-        <v>191.95</v>
+        <v>170.62</v>
       </c>
       <c r="L72" t="n">
-        <v>194.33</v>
+        <v>172.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>265.74</v>
+        <v>236.21</v>
       </c>
       <c r="K73" t="n">
-        <v>15.83</v>
+        <v>14.07</v>
       </c>
       <c r="L73" t="n">
-        <v>266.21</v>
+        <v>236.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-36.9</v>
+        <v>-35.36</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.03</v>
+        <v>-44.12</v>
       </c>
       <c r="L74" t="n">
-        <v>59</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-59.93</v>
+        <v>-58.71</v>
       </c>
       <c r="K75" t="n">
-        <v>-33.68</v>
+        <v>-33</v>
       </c>
       <c r="L75" t="n">
-        <v>68.75</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>27.43</v>
+        <v>24.38</v>
       </c>
       <c r="K76" t="n">
-        <v>32.81</v>
+        <v>29.16</v>
       </c>
       <c r="L76" t="n">
-        <v>42.76</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-68.5</v>
+        <v>-69.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.72</v>
+        <v>-48.66</v>
       </c>
       <c r="L77" t="n">
-        <v>83.48</v>
+        <v>85.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.29</v>
+        <v>-35.98</v>
       </c>
       <c r="K78" t="n">
-        <v>-67.11</v>
+        <v>-68.43000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>75.83</v>
+        <v>77.31</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>67.33</v>
+        <v>61.47</v>
       </c>
       <c r="K79" t="n">
-        <v>23.61</v>
+        <v>21.56</v>
       </c>
       <c r="L79" t="n">
-        <v>71.34999999999999</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>98.56</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>44.63</v>
+        <v>40.75</v>
       </c>
       <c r="L80" t="n">
-        <v>108.2</v>
+        <v>98.79000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-86</v>
+        <v>-80.51000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>20.2</v>
+        <v>18.91</v>
       </c>
       <c r="L81" t="n">
-        <v>88.34</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-70.16</v>
+        <v>-62.36</v>
       </c>
       <c r="K82" t="n">
-        <v>61.67</v>
+        <v>54.81</v>
       </c>
       <c r="L82" t="n">
-        <v>93.40000000000001</v>
+        <v>83.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.4</v>
+        <v>-3.19</v>
       </c>
       <c r="K83" t="n">
-        <v>184.95</v>
+        <v>173.15</v>
       </c>
       <c r="L83" t="n">
-        <v>184.98</v>
+        <v>173.18</v>
       </c>
     </row>
     <row r="84">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>49.24</v>
+        <v>44.96</v>
       </c>
       <c r="K85" t="n">
-        <v>-98.91</v>
+        <v>-90.31</v>
       </c>
       <c r="L85" t="n">
-        <v>110.49</v>
+        <v>100.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.86</v>
+        <v>-17.19</v>
       </c>
       <c r="K86" t="n">
-        <v>270.08</v>
+        <v>275.38</v>
       </c>
       <c r="L86" t="n">
-        <v>270.61</v>
+        <v>275.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-305.84</v>
+        <v>-286.31</v>
       </c>
       <c r="K87" t="n">
-        <v>-7.67</v>
+        <v>-7.18</v>
       </c>
       <c r="L87" t="n">
-        <v>305.93</v>
+        <v>286.4</v>
       </c>
     </row>
     <row r="88">

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="F14" t="n">
-        <v>8.470000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="G14" t="n">
-        <v>304</v>
+        <v>294.6</v>
       </c>
       <c r="H14" t="n">
-        <v>88.7</v>
+        <v>50.5</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-50.45</v>
+        <v>-19.29</v>
       </c>
       <c r="K14" t="n">
-        <v>14.57</v>
+        <v>21.44</v>
       </c>
       <c r="L14" t="n">
-        <v>52.51</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:15:05</t>
+          <t>06:15:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.71</v>
+        <v>2.22</v>
       </c>
       <c r="F15" t="n">
-        <v>7.79</v>
+        <v>7.43</v>
       </c>
       <c r="G15" t="n">
-        <v>287.7</v>
+        <v>285.8</v>
       </c>
       <c r="H15" t="n">
-        <v>75.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>15.49</v>
+        <v>-6.33</v>
       </c>
       <c r="K15" t="n">
-        <v>68.16</v>
+        <v>39.75</v>
       </c>
       <c r="L15" t="n">
-        <v>69.90000000000001</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:16:54</t>
+          <t>06:16:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="F16" t="n">
-        <v>9.539999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="G16" t="n">
-        <v>285.8</v>
+        <v>292.7</v>
       </c>
       <c r="H16" t="n">
-        <v>84.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>48.55</v>
+        <v>-25.44</v>
       </c>
       <c r="K16" t="n">
-        <v>25.43</v>
+        <v>3.32</v>
       </c>
       <c r="L16" t="n">
-        <v>54.81</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:20:07</t>
+          <t>06:21:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="F17" t="n">
-        <v>1.93</v>
+        <v>3.35</v>
       </c>
       <c r="G17" t="n">
-        <v>298.3</v>
+        <v>294.5</v>
       </c>
       <c r="H17" t="n">
-        <v>85.5</v>
+        <v>59</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>41.37</v>
+        <v>-34.48</v>
       </c>
       <c r="K17" t="n">
-        <v>48.19</v>
+        <v>-23.36</v>
       </c>
       <c r="L17" t="n">
-        <v>63.51</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:21:08</t>
+          <t>06:23:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="F18" t="n">
-        <v>9.539999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="G18" t="n">
-        <v>300.3</v>
+        <v>297.8</v>
       </c>
       <c r="H18" t="n">
-        <v>83.8</v>
+        <v>62.6</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>-19.46</v>
+        <v>0.08</v>
       </c>
       <c r="K18" t="n">
-        <v>-80.08</v>
+        <v>45.45</v>
       </c>
       <c r="L18" t="n">
-        <v>82.41</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:22:48</t>
+          <t>06:25:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="F19" t="n">
-        <v>6.69</v>
+        <v>6.97</v>
       </c>
       <c r="G19" t="n">
-        <v>306.2</v>
+        <v>307.5</v>
       </c>
       <c r="H19" t="n">
-        <v>80.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.66</v>
+        <v>-12.79</v>
       </c>
       <c r="K19" t="n">
-        <v>64.41</v>
+        <v>36.43</v>
       </c>
       <c r="L19" t="n">
-        <v>70.09</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:27:41</t>
+          <t>06:29:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="F20" t="n">
-        <v>8.32</v>
+        <v>2.42</v>
       </c>
       <c r="G20" t="n">
-        <v>299.5</v>
+        <v>285</v>
       </c>
       <c r="H20" t="n">
-        <v>76.09999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-40.82</v>
+        <v>-50.37</v>
       </c>
       <c r="K20" t="n">
-        <v>72.59999999999999</v>
+        <v>-40.74</v>
       </c>
       <c r="L20" t="n">
-        <v>83.29000000000001</v>
+        <v>64.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:29:27</t>
+          <t>06:32:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="F21" t="n">
-        <v>8.800000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="G21" t="n">
-        <v>306.8</v>
+        <v>297.9</v>
       </c>
       <c r="H21" t="n">
-        <v>78.40000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-42.21</v>
+        <v>44.07</v>
       </c>
       <c r="K21" t="n">
-        <v>78.66</v>
+        <v>45.08</v>
       </c>
       <c r="L21" t="n">
-        <v>89.27</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:31:00</t>
+          <t>06:34:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="F22" t="n">
-        <v>6.72</v>
+        <v>6.64</v>
       </c>
       <c r="G22" t="n">
-        <v>303.5</v>
+        <v>301.4</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>30.8</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.45</v>
+        <v>-63.86</v>
       </c>
       <c r="K22" t="n">
-        <v>-74.11</v>
+        <v>-7.24</v>
       </c>
       <c r="L22" t="n">
-        <v>76.13</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:35:20</t>
+          <t>06:37:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="F23" t="n">
-        <v>9.27</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>285.9</v>
+        <v>302.5</v>
       </c>
       <c r="H23" t="n">
-        <v>75.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>174.78</v>
+        <v>146.5</v>
       </c>
       <c r="K23" t="n">
-        <v>-17.62</v>
+        <v>10.1</v>
       </c>
       <c r="L23" t="n">
-        <v>175.67</v>
+        <v>146.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:37:28</t>
+          <t>06:39:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="F24" t="n">
-        <v>9.539999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="G24" t="n">
-        <v>305.7</v>
+        <v>300.3</v>
       </c>
       <c r="H24" t="n">
-        <v>75.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>95.37</v>
+        <v>109.35</v>
       </c>
       <c r="K24" t="n">
-        <v>-96.42</v>
+        <v>54.56</v>
       </c>
       <c r="L24" t="n">
-        <v>135.62</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:38:26</t>
+          <t>06:41:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="F25" t="n">
-        <v>7.09</v>
+        <v>6.07</v>
       </c>
       <c r="G25" t="n">
-        <v>293</v>
+        <v>301.6</v>
       </c>
       <c r="H25" t="n">
-        <v>79.8</v>
+        <v>36.7</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>114.69</v>
+        <v>-91.81999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-91.25</v>
+        <v>11.47</v>
       </c>
       <c r="L25" t="n">
-        <v>146.57</v>
+        <v>92.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:43:02</t>
+          <t>06:46:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="F26" t="n">
-        <v>5.17</v>
+        <v>1.97</v>
       </c>
       <c r="G26" t="n">
-        <v>284.6</v>
+        <v>294.2</v>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>62.5</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-145.32</v>
+        <v>-83.22</v>
       </c>
       <c r="K26" t="n">
-        <v>-32.57</v>
+        <v>67.91</v>
       </c>
       <c r="L26" t="n">
-        <v>148.93</v>
+        <v>107.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:43:58</t>
+          <t>06:47:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="F27" t="n">
-        <v>5.84</v>
+        <v>6.02</v>
       </c>
       <c r="G27" t="n">
-        <v>288.2</v>
+        <v>296.8</v>
       </c>
       <c r="H27" t="n">
-        <v>81.40000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>127.65</v>
+        <v>-84.98999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>211.46</v>
+        <v>123.24</v>
       </c>
       <c r="L27" t="n">
-        <v>247.01</v>
+        <v>149.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:45:15</t>
+          <t>06:50:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="F28" t="n">
-        <v>9.17</v>
+        <v>4.74</v>
       </c>
       <c r="G28" t="n">
-        <v>304</v>
+        <v>297.1</v>
       </c>
       <c r="H28" t="n">
-        <v>84.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>39.17</v>
+        <v>-113.96</v>
       </c>
       <c r="K28" t="n">
-        <v>54.91</v>
+        <v>-21.17</v>
       </c>
       <c r="L28" t="n">
-        <v>67.45</v>
+        <v>115.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:58:27</t>
+          <t>06:59:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="F29" t="n">
-        <v>7.74</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>287.5</v>
+        <v>298.1</v>
       </c>
       <c r="H29" t="n">
-        <v>83.09999999999999</v>
+        <v>27.7</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>67.04000000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="K29" t="n">
-        <v>2.83</v>
+        <v>-24.14</v>
       </c>
       <c r="L29" t="n">
-        <v>67.09999999999999</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:01:03</t>
+          <t>07:01:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="F30" t="n">
-        <v>9.539999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>299.8</v>
+        <v>290.5</v>
       </c>
       <c r="H30" t="n">
-        <v>76.8</v>
+        <v>20.7</v>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.08</v>
+        <v>11.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.62</v>
+        <v>-14.67</v>
       </c>
       <c r="L30" t="n">
-        <v>41.17</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:02:27</t>
+          <t>07:03:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="F31" t="n">
-        <v>9.539999999999999</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>294.8</v>
+        <v>311.2</v>
       </c>
       <c r="H31" t="n">
-        <v>90.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I31" t="n">
         <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-56.89</v>
+        <v>-35.34</v>
       </c>
       <c r="K31" t="n">
-        <v>44.45</v>
+        <v>-2.93</v>
       </c>
       <c r="L31" t="n">
-        <v>72.2</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:07:53</t>
+          <t>07:07:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="F32" t="n">
-        <v>5.47</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>298.8</v>
+        <v>302.2</v>
       </c>
       <c r="H32" t="n">
-        <v>86.7</v>
+        <v>53.2</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-77.17</v>
+        <v>-37.67</v>
       </c>
       <c r="K32" t="n">
-        <v>67.95999999999999</v>
+        <v>34.3</v>
       </c>
       <c r="L32" t="n">
-        <v>102.83</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:09:07</t>
+          <t>07:10:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="F33" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>294.5</v>
+        <v>300.7</v>
       </c>
       <c r="H33" t="n">
-        <v>78.59999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
+        <v>7.15</v>
       </c>
       <c r="K33" t="n">
-        <v>-102.2</v>
+        <v>50.97</v>
       </c>
       <c r="L33" t="n">
-        <v>102.3</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:10:24</t>
+          <t>07:12:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="F34" t="n">
-        <v>6.94</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>296.1</v>
+        <v>308.5</v>
       </c>
       <c r="H34" t="n">
-        <v>82.3</v>
+        <v>60.7</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>-45.47</v>
+        <v>-49.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-57.39</v>
+        <v>-21.74</v>
       </c>
       <c r="L34" t="n">
-        <v>73.22</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:14:56</t>
+          <t>07:17:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="F35" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>308</v>
+        <v>304.3</v>
       </c>
       <c r="H35" t="n">
-        <v>77.2</v>
+        <v>51.9</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>49.12</v>
+        <v>-35.89</v>
       </c>
       <c r="K35" t="n">
-        <v>102.89</v>
+        <v>63.52</v>
       </c>
       <c r="L35" t="n">
-        <v>114.01</v>
+        <v>72.95999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:16:58</t>
+          <t>07:18:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="F36" t="n">
-        <v>6.78</v>
+        <v>9.15</v>
       </c>
       <c r="G36" t="n">
-        <v>296.1</v>
+        <v>299.7</v>
       </c>
       <c r="H36" t="n">
-        <v>75.7</v>
+        <v>55.4</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>9.6</v>
+        <v>-80.61</v>
       </c>
       <c r="K36" t="n">
-        <v>-95.45999999999999</v>
+        <v>-15.26</v>
       </c>
       <c r="L36" t="n">
-        <v>95.94</v>
+        <v>82.04000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:18:18</t>
+          <t>07:20:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="F37" t="n">
-        <v>6.09</v>
+        <v>6.97</v>
       </c>
       <c r="G37" t="n">
-        <v>286.4</v>
+        <v>311.5</v>
       </c>
       <c r="H37" t="n">
-        <v>79.8</v>
+        <v>46.7</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-36.25</v>
+        <v>-42.03</v>
       </c>
       <c r="K37" t="n">
-        <v>102.63</v>
+        <v>-90.98999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>108.84</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:22:25</t>
+          <t>07:24:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="F38" t="n">
-        <v>8.529999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>304</v>
+        <v>293.9</v>
       </c>
       <c r="H38" t="n">
-        <v>84.3</v>
+        <v>65.5</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>45.13</v>
+        <v>-111.55</v>
       </c>
       <c r="K38" t="n">
-        <v>-29.93</v>
+        <v>-135.78</v>
       </c>
       <c r="L38" t="n">
-        <v>54.15</v>
+        <v>175.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:24:10</t>
+          <t>07:26:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.63</v>
+        <v>1.72</v>
       </c>
       <c r="F39" t="n">
-        <v>9.539999999999999</v>
+        <v>3.73</v>
       </c>
       <c r="G39" t="n">
-        <v>294.8</v>
+        <v>273.1</v>
       </c>
       <c r="H39" t="n">
-        <v>82.5</v>
+        <v>33.7</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-39.87</v>
+        <v>87.39</v>
       </c>
       <c r="K39" t="n">
-        <v>-140</v>
+        <v>-0.99</v>
       </c>
       <c r="L39" t="n">
-        <v>145.56</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:26:25</t>
+          <t>07:29:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1720,31 +1720,31 @@
         <v>2.13</v>
       </c>
       <c r="F40" t="n">
-        <v>3.98</v>
+        <v>6.04</v>
       </c>
       <c r="G40" t="n">
-        <v>302.1</v>
+        <v>292.1</v>
       </c>
       <c r="H40" t="n">
-        <v>81.40000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="I40" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>25.41</v>
+        <v>-56.38</v>
       </c>
       <c r="K40" t="n">
-        <v>-121.66</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>124.28</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:30:27</t>
+          <t>07:34:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.78</v>
+        <v>3.03</v>
       </c>
       <c r="F41" t="n">
-        <v>4.26</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>298.8</v>
+        <v>285.2</v>
       </c>
       <c r="H41" t="n">
-        <v>78.2</v>
+        <v>38.8</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>96.81</v>
+        <v>18.05</v>
       </c>
       <c r="K41" t="n">
-        <v>79.40000000000001</v>
+        <v>148.78</v>
       </c>
       <c r="L41" t="n">
-        <v>125.21</v>
+        <v>149.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:31:32</t>
+          <t>07:35:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="F42" t="n">
-        <v>8.15</v>
+        <v>7.03</v>
       </c>
       <c r="G42" t="n">
-        <v>301.6</v>
+        <v>302.7</v>
       </c>
       <c r="H42" t="n">
-        <v>76</v>
+        <v>48.8</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>194.81</v>
+        <v>-159.12</v>
       </c>
       <c r="K42" t="n">
-        <v>157.12</v>
+        <v>-32.87</v>
       </c>
       <c r="L42" t="n">
-        <v>250.27</v>
+        <v>162.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:32:31</t>
+          <t>07:37:31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="F43" t="n">
-        <v>4.92</v>
+        <v>7.2</v>
       </c>
       <c r="G43" t="n">
-        <v>292.6</v>
+        <v>293</v>
       </c>
       <c r="H43" t="n">
-        <v>77.7</v>
+        <v>45.3</v>
       </c>
       <c r="I43" t="n">
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-164.62</v>
+        <v>-83.51000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-133.69</v>
+        <v>-61.33</v>
       </c>
       <c r="L43" t="n">
-        <v>212.06</v>
+        <v>103.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:40:31</t>
+          <t>07:46:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="F44" t="n">
-        <v>6.39</v>
+        <v>6.8</v>
       </c>
       <c r="G44" t="n">
-        <v>302.4</v>
+        <v>301.1</v>
       </c>
       <c r="H44" t="n">
-        <v>77.8</v>
+        <v>55.3</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.48</v>
+        <v>18.47</v>
       </c>
       <c r="K44" t="n">
-        <v>37.82</v>
+        <v>4.41</v>
       </c>
       <c r="L44" t="n">
-        <v>39.83</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:42:22</t>
+          <t>07:48:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="F45" t="n">
-        <v>9.08</v>
+        <v>4.91</v>
       </c>
       <c r="G45" t="n">
-        <v>298.8</v>
+        <v>302.8</v>
       </c>
       <c r="H45" t="n">
-        <v>80.3</v>
+        <v>72.2</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.38</v>
+        <v>-0.17</v>
       </c>
       <c r="K45" t="n">
-        <v>36.59</v>
+        <v>26.93</v>
       </c>
       <c r="L45" t="n">
-        <v>55.24</v>
+        <v>26.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:45:02</t>
+          <t>07:51:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="F46" t="n">
-        <v>9.27</v>
+        <v>8.06</v>
       </c>
       <c r="G46" t="n">
-        <v>303.8</v>
+        <v>305.1</v>
       </c>
       <c r="H46" t="n">
-        <v>81.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>56.44</v>
+        <v>-3.93</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.37</v>
+        <v>-63.13</v>
       </c>
       <c r="L46" t="n">
-        <v>56.7</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:49:31</t>
+          <t>07:56:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="F47" t="n">
-        <v>9.539999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="G47" t="n">
-        <v>292.3</v>
+        <v>295.6</v>
       </c>
       <c r="H47" t="n">
-        <v>81.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>121.82</v>
+        <v>-40.26</v>
       </c>
       <c r="K47" t="n">
-        <v>-15.33</v>
+        <v>4.93</v>
       </c>
       <c r="L47" t="n">
-        <v>122.78</v>
+        <v>40.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:50:40</t>
+          <t>07:57:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="F48" t="n">
-        <v>7.21</v>
+        <v>6.07</v>
       </c>
       <c r="G48" t="n">
-        <v>292.8</v>
+        <v>305.4</v>
       </c>
       <c r="H48" t="n">
-        <v>87.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-82.34999999999999</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-37.01</v>
+        <v>34.76</v>
       </c>
       <c r="L48" t="n">
-        <v>90.29000000000001</v>
+        <v>35.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:51:50</t>
+          <t>07:58:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="F49" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>305.4</v>
+        <v>284.2</v>
       </c>
       <c r="H49" t="n">
-        <v>74.2</v>
+        <v>36.7</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>73.7</v>
+        <v>-33.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.98</v>
+        <v>36.07</v>
       </c>
       <c r="L49" t="n">
-        <v>75.20999999999999</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:57:41</t>
+          <t>08:03:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="F50" t="n">
-        <v>9.44</v>
+        <v>6.38</v>
       </c>
       <c r="G50" t="n">
-        <v>294.2</v>
+        <v>299.6</v>
       </c>
       <c r="H50" t="n">
-        <v>80</v>
+        <v>46.8</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-24.89</v>
+        <v>43.28</v>
       </c>
       <c r="K50" t="n">
-        <v>-117.43</v>
+        <v>75.52</v>
       </c>
       <c r="L50" t="n">
-        <v>120.04</v>
+        <v>87.04000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:59:39</t>
+          <t>08:05:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="F51" t="n">
-        <v>7.78</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>302.9</v>
+        <v>295.5</v>
       </c>
       <c r="H51" t="n">
-        <v>82.09999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>82.34999999999999</v>
+        <v>3.49</v>
       </c>
       <c r="K51" t="n">
-        <v>78.55</v>
+        <v>82.63</v>
       </c>
       <c r="L51" t="n">
-        <v>113.8</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:00:27</t>
+          <t>08:06:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="F52" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>287.4</v>
+        <v>300.7</v>
       </c>
       <c r="H52" t="n">
-        <v>79.09999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>39.85</v>
+        <v>55.8</v>
       </c>
       <c r="K52" t="n">
-        <v>110.19</v>
+        <v>-1.08</v>
       </c>
       <c r="L52" t="n">
-        <v>117.17</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:05:00</t>
+          <t>08:12:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="F53" t="n">
-        <v>8.57</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>301.2</v>
+        <v>291.2</v>
       </c>
       <c r="H53" t="n">
-        <v>73.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-116.67</v>
+        <v>76.13</v>
       </c>
       <c r="K53" t="n">
-        <v>151.76</v>
+        <v>-63.25</v>
       </c>
       <c r="L53" t="n">
-        <v>191.42</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>08:13:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="F54" t="n">
-        <v>9.539999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>312.4</v>
+        <v>294.5</v>
       </c>
       <c r="H54" t="n">
-        <v>81.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I54" t="n">
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-72.94</v>
+        <v>-43.21</v>
       </c>
       <c r="K54" t="n">
-        <v>185.19</v>
+        <v>83.62</v>
       </c>
       <c r="L54" t="n">
-        <v>199.03</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:07:03</t>
+          <t>08:15:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="F55" t="n">
-        <v>4.74</v>
+        <v>8.09</v>
       </c>
       <c r="G55" t="n">
-        <v>284.9</v>
+        <v>313.2</v>
       </c>
       <c r="H55" t="n">
-        <v>83.40000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>111.2</v>
+        <v>-50.47</v>
       </c>
       <c r="K55" t="n">
-        <v>1.23</v>
+        <v>60.72</v>
       </c>
       <c r="L55" t="n">
-        <v>111.21</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:11:02</t>
+          <t>08:19:29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="F56" t="n">
-        <v>7.7</v>
+        <v>6.57</v>
       </c>
       <c r="G56" t="n">
-        <v>306.1</v>
+        <v>296.2</v>
       </c>
       <c r="H56" t="n">
-        <v>82.09999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-166.84</v>
+        <v>-106.03</v>
       </c>
       <c r="K56" t="n">
-        <v>53.41</v>
+        <v>-11.36</v>
       </c>
       <c r="L56" t="n">
-        <v>175.18</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:12:19</t>
+          <t>08:21:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="F57" t="n">
-        <v>9.039999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="G57" t="n">
-        <v>296.2</v>
+        <v>301.4</v>
       </c>
       <c r="H57" t="n">
-        <v>78.8</v>
+        <v>81.7</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-139.1</v>
+        <v>-97.47</v>
       </c>
       <c r="K57" t="n">
-        <v>-112.53</v>
+        <v>-2.88</v>
       </c>
       <c r="L57" t="n">
-        <v>178.92</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:14:14</t>
+          <t>08:23:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.22</v>
+        <v>3.55</v>
       </c>
       <c r="F58" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>305.9</v>
+        <v>296.6</v>
       </c>
       <c r="H58" t="n">
-        <v>79.7</v>
+        <v>51.3</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-146.69</v>
+        <v>-16.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.88</v>
+        <v>182.13</v>
       </c>
       <c r="L58" t="n">
-        <v>146.8</v>
+        <v>182.83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:25:36</t>
+          <t>08:34:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="F59" t="n">
-        <v>9.539999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="G59" t="n">
-        <v>289.2</v>
+        <v>302.3</v>
       </c>
       <c r="H59" t="n">
-        <v>81.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>81.28</v>
+        <v>16.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.47</v>
+        <v>-20.74</v>
       </c>
       <c r="L59" t="n">
-        <v>81.53</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:27:00</t>
+          <t>08:36:44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="F60" t="n">
-        <v>8.57</v>
+        <v>4.55</v>
       </c>
       <c r="G60" t="n">
-        <v>297.1</v>
+        <v>289.9</v>
       </c>
       <c r="H60" t="n">
-        <v>83.2</v>
+        <v>33.7</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.19</v>
+        <v>13.22</v>
       </c>
       <c r="K60" t="n">
-        <v>-58.12</v>
+        <v>28.7</v>
       </c>
       <c r="L60" t="n">
-        <v>58.69</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:29:06</t>
+          <t>08:38:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="F61" t="n">
-        <v>9.539999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G61" t="n">
-        <v>320.1</v>
+        <v>300</v>
       </c>
       <c r="H61" t="n">
-        <v>80.5</v>
+        <v>50.7</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-53.71</v>
+        <v>10.84</v>
       </c>
       <c r="K61" t="n">
-        <v>39.93</v>
+        <v>36.33</v>
       </c>
       <c r="L61" t="n">
-        <v>66.92</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:33:25</t>
+          <t>08:44:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2644,31 +2644,31 @@
         <v>2.07</v>
       </c>
       <c r="F62" t="n">
-        <v>7.24</v>
+        <v>7.88</v>
       </c>
       <c r="G62" t="n">
-        <v>283.2</v>
+        <v>308.2</v>
       </c>
       <c r="H62" t="n">
-        <v>81.3</v>
+        <v>70</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.97</v>
+        <v>32.07</v>
       </c>
       <c r="K62" t="n">
-        <v>-59.1</v>
+        <v>-5.14</v>
       </c>
       <c r="L62" t="n">
-        <v>59.4</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:45:18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="F63" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>284.5</v>
+        <v>297.4</v>
       </c>
       <c r="H63" t="n">
-        <v>87.5</v>
+        <v>47.5</v>
       </c>
       <c r="I63" t="n">
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>18.16</v>
+        <v>-1.56</v>
       </c>
       <c r="K63" t="n">
-        <v>84.73</v>
+        <v>-42.73</v>
       </c>
       <c r="L63" t="n">
-        <v>86.66</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:35:35</t>
+          <t>08:46:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="F64" t="n">
-        <v>9.210000000000001</v>
+        <v>6.28</v>
       </c>
       <c r="G64" t="n">
-        <v>294.3</v>
+        <v>300.4</v>
       </c>
       <c r="H64" t="n">
-        <v>76.8</v>
+        <v>56.7</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-73.81999999999999</v>
+        <v>-7.13</v>
       </c>
       <c r="K64" t="n">
-        <v>23.6</v>
+        <v>62.61</v>
       </c>
       <c r="L64" t="n">
-        <v>77.5</v>
+        <v>63.02</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:41:25</t>
+          <t>08:52:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,13 +2767,13 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="F65" t="n">
-        <v>4.8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>309.5</v>
+        <v>303.7</v>
       </c>
       <c r="H65" t="n">
         <v>78.90000000000001</v>
@@ -2782,19 +2782,19 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>82.13</v>
+        <v>-31.31</v>
       </c>
       <c r="K65" t="n">
-        <v>-48.77</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>95.52</v>
+        <v>87.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:42:36</t>
+          <t>08:53:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="F66" t="n">
-        <v>8.039999999999999</v>
+        <v>5.13</v>
       </c>
       <c r="G66" t="n">
-        <v>292.4</v>
+        <v>294</v>
       </c>
       <c r="H66" t="n">
-        <v>79.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J66" t="n">
-        <v>-97.81</v>
+        <v>-18.75</v>
       </c>
       <c r="K66" t="n">
-        <v>-144.76</v>
+        <v>-62.07</v>
       </c>
       <c r="L66" t="n">
-        <v>174.71</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:45:07</t>
+          <t>08:54:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="F67" t="n">
-        <v>4.22</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>293.1</v>
+        <v>283.6</v>
       </c>
       <c r="H67" t="n">
-        <v>88.09999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>57.91</v>
+        <v>-63.2</v>
       </c>
       <c r="K67" t="n">
-        <v>77.90000000000001</v>
+        <v>-42.59</v>
       </c>
       <c r="L67" t="n">
-        <v>97.06999999999999</v>
+        <v>76.20999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:49:47</t>
+          <t>08:59:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="F68" t="n">
-        <v>9.539999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="G68" t="n">
-        <v>289.8</v>
+        <v>293</v>
       </c>
       <c r="H68" t="n">
-        <v>74.5</v>
+        <v>48</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-134</v>
+        <v>-40.59</v>
       </c>
       <c r="K68" t="n">
-        <v>111.52</v>
+        <v>78.41</v>
       </c>
       <c r="L68" t="n">
-        <v>174.33</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:51:33</t>
+          <t>09:01:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="F69" t="n">
-        <v>8.57</v>
+        <v>2.25</v>
       </c>
       <c r="G69" t="n">
-        <v>295.7</v>
+        <v>299.4</v>
       </c>
       <c r="H69" t="n">
-        <v>79.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-14.65</v>
+        <v>-30.37</v>
       </c>
       <c r="K69" t="n">
-        <v>138.89</v>
+        <v>85.97</v>
       </c>
       <c r="L69" t="n">
-        <v>139.66</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:54:00</t>
+          <t>09:02:42</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.39</v>
+        <v>2.83</v>
       </c>
       <c r="F70" t="n">
-        <v>6.88</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>298.3</v>
+        <v>300.4</v>
       </c>
       <c r="H70" t="n">
-        <v>83.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="I70" t="n">
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>60.43</v>
+        <v>-4.53</v>
       </c>
       <c r="K70" t="n">
-        <v>-138.04</v>
+        <v>-95.11</v>
       </c>
       <c r="L70" t="n">
-        <v>150.69</v>
+        <v>95.22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:59:17</t>
+          <t>09:08:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="F71" t="n">
-        <v>5.24</v>
+        <v>8.91</v>
       </c>
       <c r="G71" t="n">
-        <v>307</v>
+        <v>291.1</v>
       </c>
       <c r="H71" t="n">
-        <v>82.3</v>
+        <v>58.7</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>-4</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>211.04</v>
+        <v>-114.4</v>
       </c>
       <c r="L71" t="n">
-        <v>211.07</v>
+        <v>134.15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:01:29</t>
+          <t>09:10:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="F72" t="n">
-        <v>9.539999999999999</v>
+        <v>5.67</v>
       </c>
       <c r="G72" t="n">
-        <v>295.8</v>
+        <v>304.4</v>
       </c>
       <c r="H72" t="n">
-        <v>81.40000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-26.94</v>
+        <v>-152.41</v>
       </c>
       <c r="K72" t="n">
-        <v>170.62</v>
+        <v>77.12</v>
       </c>
       <c r="L72" t="n">
-        <v>172.74</v>
+        <v>170.81</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:03:11</t>
+          <t>09:11:54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="F73" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>297.9</v>
+        <v>295</v>
       </c>
       <c r="H73" t="n">
-        <v>80.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>236.21</v>
+        <v>87.17</v>
       </c>
       <c r="K73" t="n">
-        <v>14.07</v>
+        <v>1.39</v>
       </c>
       <c r="L73" t="n">
-        <v>236.63</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:15:12</t>
+          <t>09:21:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="F74" t="n">
-        <v>9.539999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="G74" t="n">
-        <v>292.1</v>
+        <v>297.8</v>
       </c>
       <c r="H74" t="n">
-        <v>72.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-35.36</v>
+        <v>21.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.12</v>
+        <v>-19.36</v>
       </c>
       <c r="L74" t="n">
-        <v>56.54</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:17:03</t>
+          <t>09:22:31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="F75" t="n">
-        <v>9.539999999999999</v>
+        <v>4.96</v>
       </c>
       <c r="G75" t="n">
-        <v>291.8</v>
+        <v>289.8</v>
       </c>
       <c r="H75" t="n">
-        <v>79.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-58.71</v>
+        <v>-32.57</v>
       </c>
       <c r="K75" t="n">
-        <v>-33</v>
+        <v>-1.49</v>
       </c>
       <c r="L75" t="n">
-        <v>67.34999999999999</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:18:01</t>
+          <t>09:23:36</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="F76" t="n">
-        <v>8.73</v>
+        <v>8.82</v>
       </c>
       <c r="G76" t="n">
-        <v>311.8</v>
+        <v>298.8</v>
       </c>
       <c r="H76" t="n">
-        <v>81.8</v>
+        <v>49.9</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>24.38</v>
+        <v>46.9</v>
       </c>
       <c r="K76" t="n">
-        <v>29.16</v>
+        <v>3.71</v>
       </c>
       <c r="L76" t="n">
-        <v>38.01</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:22:06</t>
+          <t>09:27:21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="F77" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>295.3</v>
+        <v>294.4</v>
       </c>
       <c r="H77" t="n">
-        <v>79.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-69.84</v>
+        <v>-15.99</v>
       </c>
       <c r="K77" t="n">
-        <v>-48.66</v>
+        <v>44.75</v>
       </c>
       <c r="L77" t="n">
-        <v>85.12</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:24:06</t>
+          <t>09:28:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.06</v>
+        <v>2.39</v>
       </c>
       <c r="F78" t="n">
-        <v>9.539999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G78" t="n">
-        <v>300.5</v>
+        <v>293.1</v>
       </c>
       <c r="H78" t="n">
-        <v>77.3</v>
+        <v>38</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.98</v>
+        <v>14.41</v>
       </c>
       <c r="K78" t="n">
-        <v>-68.43000000000001</v>
+        <v>56.12</v>
       </c>
       <c r="L78" t="n">
-        <v>77.31</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:25:39</t>
+          <t>09:29:49</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="F79" t="n">
-        <v>9.539999999999999</v>
+        <v>5.17</v>
       </c>
       <c r="G79" t="n">
-        <v>288.2</v>
+        <v>302</v>
       </c>
       <c r="H79" t="n">
-        <v>78.3</v>
+        <v>63.8</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>61.47</v>
+        <v>-47.27</v>
       </c>
       <c r="K79" t="n">
-        <v>21.56</v>
+        <v>-6.74</v>
       </c>
       <c r="L79" t="n">
-        <v>65.15000000000001</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:29:53</t>
+          <t>09:33:16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.96</v>
+        <v>2.12</v>
       </c>
       <c r="F80" t="n">
-        <v>9.539999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="G80" t="n">
-        <v>302</v>
+        <v>306.5</v>
       </c>
       <c r="H80" t="n">
-        <v>79.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>89.98999999999999</v>
+        <v>-57.16</v>
       </c>
       <c r="K80" t="n">
-        <v>40.75</v>
+        <v>57.45</v>
       </c>
       <c r="L80" t="n">
-        <v>98.79000000000001</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:32:09</t>
+          <t>09:35:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="F81" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>310.3</v>
+        <v>298.3</v>
       </c>
       <c r="H81" t="n">
-        <v>80.40000000000001</v>
+        <v>53</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-80.51000000000001</v>
+        <v>-43.59</v>
       </c>
       <c r="K81" t="n">
-        <v>18.91</v>
+        <v>-61.64</v>
       </c>
       <c r="L81" t="n">
-        <v>82.7</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:33:49</t>
+          <t>09:37:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="F82" t="n">
-        <v>6.64</v>
+        <v>6.99</v>
       </c>
       <c r="G82" t="n">
-        <v>291.1</v>
+        <v>297.5</v>
       </c>
       <c r="H82" t="n">
-        <v>74.7</v>
+        <v>51.2</v>
       </c>
       <c r="I82" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-62.36</v>
+        <v>-62.16</v>
       </c>
       <c r="K82" t="n">
-        <v>54.81</v>
+        <v>-50.03</v>
       </c>
       <c r="L82" t="n">
-        <v>83.03</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:39:15</t>
+          <t>09:42:10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="F83" t="n">
-        <v>6.61</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>303</v>
+        <v>295.6</v>
       </c>
       <c r="H83" t="n">
-        <v>83.2</v>
+        <v>46.9</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.19</v>
+        <v>-89.23999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>173.15</v>
+        <v>7.73</v>
       </c>
       <c r="L83" t="n">
-        <v>173.18</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:41:54</t>
+          <t>09:43:08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="F84" t="n">
-        <v>9.17</v>
+        <v>5.26</v>
       </c>
       <c r="G84" t="n">
-        <v>297</v>
+        <v>310.9</v>
       </c>
       <c r="H84" t="n">
-        <v>81.3</v>
+        <v>60</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-172.1</v>
+        <v>80.22</v>
       </c>
       <c r="K84" t="n">
-        <v>-87.88</v>
+        <v>-9.1</v>
       </c>
       <c r="L84" t="n">
-        <v>193.24</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:44:31</t>
+          <t>09:44:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="F85" t="n">
-        <v>8.16</v>
+        <v>9.07</v>
       </c>
       <c r="G85" t="n">
-        <v>305.3</v>
+        <v>293.2</v>
       </c>
       <c r="H85" t="n">
-        <v>81.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>44.96</v>
+        <v>-69.86</v>
       </c>
       <c r="K85" t="n">
-        <v>-90.31</v>
+        <v>52.72</v>
       </c>
       <c r="L85" t="n">
-        <v>100.88</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:50:12</t>
+          <t>09:49:53</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="F86" t="n">
-        <v>9.539999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="G86" t="n">
-        <v>302.9</v>
+        <v>316.1</v>
       </c>
       <c r="H86" t="n">
-        <v>83.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.19</v>
+        <v>83.13</v>
       </c>
       <c r="K86" t="n">
-        <v>275.38</v>
+        <v>-93.06</v>
       </c>
       <c r="L86" t="n">
-        <v>275.91</v>
+        <v>124.78</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:51:17</t>
+          <t>09:50:40</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.23</v>
+        <v>2.96</v>
       </c>
       <c r="F87" t="n">
-        <v>9.41</v>
+        <v>7.97</v>
       </c>
       <c r="G87" t="n">
         <v>297.6</v>
       </c>
       <c r="H87" t="n">
-        <v>77.59999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-286.31</v>
+        <v>-163.07</v>
       </c>
       <c r="K87" t="n">
-        <v>-7.18</v>
+        <v>14.98</v>
       </c>
       <c r="L87" t="n">
-        <v>286.4</v>
+        <v>163.76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:53:23</t>
+          <t>09:52:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="F88" t="n">
-        <v>9.539999999999999</v>
+        <v>7.31</v>
       </c>
       <c r="G88" t="n">
-        <v>291.6</v>
+        <v>302.3</v>
       </c>
       <c r="H88" t="n">
-        <v>76</v>
+        <v>59.9</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-197.62</v>
+        <v>-121.25</v>
       </c>
       <c r="K88" t="n">
-        <v>-64.14</v>
+        <v>114.63</v>
       </c>
       <c r="L88" t="n">
-        <v>207.77</v>
+        <v>166.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="n">
-        <v>7.87</v>
+        <v>6.34</v>
       </c>
       <c r="G14" t="n">
-        <v>294.6</v>
+        <v>314.9</v>
       </c>
       <c r="H14" t="n">
-        <v>50.5</v>
+        <v>62.9</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.29</v>
+        <v>-2.04</v>
       </c>
       <c r="K14" t="n">
-        <v>21.44</v>
+        <v>36.43</v>
       </c>
       <c r="L14" t="n">
-        <v>28.84</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:15:22</t>
+          <t>06:13:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="F15" t="n">
-        <v>7.43</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>285.8</v>
+        <v>322.4</v>
       </c>
       <c r="H15" t="n">
-        <v>72.40000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.33</v>
+        <v>-33.89</v>
       </c>
       <c r="K15" t="n">
-        <v>39.75</v>
+        <v>20.76</v>
       </c>
       <c r="L15" t="n">
-        <v>40.26</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:16:08</t>
+          <t>06:15:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="F16" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>292.7</v>
+        <v>312.9</v>
       </c>
       <c r="H16" t="n">
-        <v>67.2</v>
+        <v>22.3</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-25.44</v>
+        <v>-45.09</v>
       </c>
       <c r="K16" t="n">
-        <v>3.32</v>
+        <v>-3.51</v>
       </c>
       <c r="L16" t="n">
-        <v>25.65</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:21:29</t>
+          <t>06:20:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>5.99</v>
       </c>
       <c r="G17" t="n">
-        <v>294.5</v>
+        <v>297.6</v>
       </c>
       <c r="H17" t="n">
-        <v>59</v>
+        <v>80.2</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-34.48</v>
+        <v>57.65</v>
       </c>
       <c r="K17" t="n">
-        <v>-23.36</v>
+        <v>4.06</v>
       </c>
       <c r="L17" t="n">
-        <v>41.65</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:23:21</t>
+          <t>06:21:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="F18" t="n">
-        <v>5.75</v>
+        <v>4.91</v>
       </c>
       <c r="G18" t="n">
-        <v>297.8</v>
+        <v>286.5</v>
       </c>
       <c r="H18" t="n">
-        <v>62.6</v>
+        <v>59.5</v>
       </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08</v>
+        <v>-6.95</v>
       </c>
       <c r="K18" t="n">
-        <v>45.45</v>
+        <v>67.98</v>
       </c>
       <c r="L18" t="n">
-        <v>45.45</v>
+        <v>68.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:25:04</t>
+          <t>06:23:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="F19" t="n">
-        <v>6.97</v>
+        <v>6.55</v>
       </c>
       <c r="G19" t="n">
-        <v>307.5</v>
+        <v>305.9</v>
       </c>
       <c r="H19" t="n">
-        <v>84.90000000000001</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.79</v>
+        <v>-42.66</v>
       </c>
       <c r="K19" t="n">
-        <v>36.43</v>
+        <v>38.85</v>
       </c>
       <c r="L19" t="n">
-        <v>38.61</v>
+        <v>57.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:29:41</t>
+          <t>06:27:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="F20" t="n">
-        <v>2.42</v>
+        <v>8.01</v>
       </c>
       <c r="G20" t="n">
-        <v>285</v>
+        <v>286.1</v>
       </c>
       <c r="H20" t="n">
-        <v>56.7</v>
+        <v>13.7</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-50.37</v>
+        <v>61.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-40.74</v>
+        <v>11.83</v>
       </c>
       <c r="L20" t="n">
-        <v>64.78</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:32:04</t>
+          <t>06:27:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="F21" t="n">
-        <v>5.75</v>
+        <v>5.59</v>
       </c>
       <c r="G21" t="n">
-        <v>297.9</v>
+        <v>285.2</v>
       </c>
       <c r="H21" t="n">
-        <v>14.6</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>44.07</v>
+        <v>8.73</v>
       </c>
       <c r="K21" t="n">
-        <v>45.08</v>
+        <v>97.37</v>
       </c>
       <c r="L21" t="n">
-        <v>63.04</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:34:45</t>
+          <t>06:29:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.01</v>
+        <v>2.92</v>
       </c>
       <c r="F22" t="n">
-        <v>6.64</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>301.4</v>
+        <v>297.8</v>
       </c>
       <c r="H22" t="n">
-        <v>30.8</v>
+        <v>32.4</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-63.86</v>
+        <v>122.57</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.24</v>
+        <v>53.29</v>
       </c>
       <c r="L22" t="n">
-        <v>64.27</v>
+        <v>133.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:37:35</t>
+          <t>06:34:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="F23" t="n">
-        <v>9.539999999999999</v>
+        <v>3.59</v>
       </c>
       <c r="G23" t="n">
-        <v>302.5</v>
+        <v>304.2</v>
       </c>
       <c r="H23" t="n">
-        <v>77.40000000000001</v>
+        <v>55</v>
       </c>
       <c r="I23" t="n">
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>146.5</v>
+        <v>-80.13</v>
       </c>
       <c r="K23" t="n">
-        <v>10.1</v>
+        <v>87.95</v>
       </c>
       <c r="L23" t="n">
-        <v>146.84</v>
+        <v>118.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:39:46</t>
+          <t>06:36:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="F24" t="n">
-        <v>7.45</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>300.3</v>
+        <v>292.6</v>
       </c>
       <c r="H24" t="n">
-        <v>68</v>
+        <v>29.3</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>109.35</v>
+        <v>-134.34</v>
       </c>
       <c r="K24" t="n">
-        <v>54.56</v>
+        <v>-70.87</v>
       </c>
       <c r="L24" t="n">
-        <v>122.21</v>
+        <v>151.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:41:06</t>
+          <t>06:38:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="F25" t="n">
-        <v>6.07</v>
+        <v>8.43</v>
       </c>
       <c r="G25" t="n">
-        <v>301.6</v>
+        <v>313.5</v>
       </c>
       <c r="H25" t="n">
-        <v>36.7</v>
+        <v>61.3</v>
       </c>
       <c r="I25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-91.81999999999999</v>
+        <v>78.12</v>
       </c>
       <c r="K25" t="n">
-        <v>11.47</v>
+        <v>-140.77</v>
       </c>
       <c r="L25" t="n">
-        <v>92.53</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:46:06</t>
+          <t>06:43:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="F26" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>294.2</v>
+        <v>290</v>
       </c>
       <c r="H26" t="n">
-        <v>62.5</v>
+        <v>57</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>-83.22</v>
+        <v>66.94</v>
       </c>
       <c r="K26" t="n">
-        <v>67.91</v>
+        <v>11.83</v>
       </c>
       <c r="L26" t="n">
-        <v>107.42</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:47:44</t>
+          <t>06:44:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="F27" t="n">
-        <v>6.02</v>
+        <v>6.95</v>
       </c>
       <c r="G27" t="n">
-        <v>296.8</v>
+        <v>301.4</v>
       </c>
       <c r="H27" t="n">
-        <v>52.5</v>
+        <v>30.8</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>-84.98999999999999</v>
+        <v>-172.63</v>
       </c>
       <c r="K27" t="n">
-        <v>123.24</v>
+        <v>-36.41</v>
       </c>
       <c r="L27" t="n">
-        <v>149.7</v>
+        <v>176.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:50:03</t>
+          <t>06:45:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="F28" t="n">
-        <v>4.74</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>297.1</v>
+        <v>306.1</v>
       </c>
       <c r="H28" t="n">
-        <v>64.09999999999999</v>
+        <v>45.4</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-113.96</v>
+        <v>-161.66</v>
       </c>
       <c r="K28" t="n">
-        <v>-21.17</v>
+        <v>-68.15000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>115.91</v>
+        <v>175.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:59:04</t>
+          <t>06:57:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="F29" t="n">
-        <v>9.539999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>298.1</v>
+        <v>300.3</v>
       </c>
       <c r="H29" t="n">
-        <v>27.7</v>
+        <v>68</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.83</v>
+        <v>33.51</v>
       </c>
       <c r="K29" t="n">
-        <v>-24.14</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>24.16</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:01:36</t>
+          <t>06:58:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="F30" t="n">
-        <v>8.880000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="G30" t="n">
-        <v>290.5</v>
+        <v>289.8</v>
       </c>
       <c r="H30" t="n">
-        <v>20.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>11.28</v>
+        <v>-28.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-14.67</v>
+        <v>-35.48</v>
       </c>
       <c r="L30" t="n">
-        <v>18.51</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:03:23</t>
+          <t>07:00:42</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="G31" t="n">
-        <v>311.2</v>
+        <v>294.2</v>
       </c>
       <c r="H31" t="n">
-        <v>93.3</v>
+        <v>62.5</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.34</v>
+        <v>-21.64</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.93</v>
+        <v>18.83</v>
       </c>
       <c r="L31" t="n">
-        <v>35.46</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:07:54</t>
+          <t>07:06:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="F32" t="n">
-        <v>9.029999999999999</v>
+        <v>6.32</v>
       </c>
       <c r="G32" t="n">
-        <v>302.2</v>
+        <v>296.1</v>
       </c>
       <c r="H32" t="n">
-        <v>53.2</v>
+        <v>69.8</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>-37.67</v>
+        <v>18.23</v>
       </c>
       <c r="K32" t="n">
-        <v>34.3</v>
+        <v>49.2</v>
       </c>
       <c r="L32" t="n">
-        <v>50.94</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:10:14</t>
+          <t>07:09:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="F33" t="n">
-        <v>9.539999999999999</v>
+        <v>3.58</v>
       </c>
       <c r="G33" t="n">
-        <v>300.7</v>
+        <v>289.8</v>
       </c>
       <c r="H33" t="n">
-        <v>30.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>7.15</v>
+        <v>-32.69</v>
       </c>
       <c r="K33" t="n">
-        <v>50.97</v>
+        <v>-44.55</v>
       </c>
       <c r="L33" t="n">
-        <v>51.47</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:12:20</t>
+          <t>07:10:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="F34" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>308.5</v>
+        <v>300.5</v>
       </c>
       <c r="H34" t="n">
-        <v>60.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.5</v>
+        <v>-38.25</v>
       </c>
       <c r="K34" t="n">
-        <v>-21.74</v>
+        <v>-41.55</v>
       </c>
       <c r="L34" t="n">
-        <v>54.06</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:17:20</t>
+          <t>07:16:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="F35" t="n">
-        <v>9.539999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>304.3</v>
+        <v>290.5</v>
       </c>
       <c r="H35" t="n">
-        <v>51.9</v>
+        <v>20.7</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-35.89</v>
+        <v>31.09</v>
       </c>
       <c r="K35" t="n">
-        <v>63.52</v>
+        <v>-32.81</v>
       </c>
       <c r="L35" t="n">
-        <v>72.95999999999999</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:18:57</t>
+          <t>07:19:09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="F36" t="n">
-        <v>9.15</v>
+        <v>7.25</v>
       </c>
       <c r="G36" t="n">
-        <v>299.7</v>
+        <v>312.4</v>
       </c>
       <c r="H36" t="n">
-        <v>55.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-80.61</v>
+        <v>95.5</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.26</v>
+        <v>-5.75</v>
       </c>
       <c r="L36" t="n">
-        <v>82.04000000000001</v>
+        <v>95.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:20:22</t>
+          <t>07:21:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="F37" t="n">
-        <v>6.97</v>
+        <v>5.9</v>
       </c>
       <c r="G37" t="n">
-        <v>311.5</v>
+        <v>302.2</v>
       </c>
       <c r="H37" t="n">
-        <v>46.7</v>
+        <v>53.2</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-42.03</v>
+        <v>-59.55</v>
       </c>
       <c r="K37" t="n">
-        <v>-90.98999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="L37" t="n">
-        <v>100.23</v>
+        <v>83.54000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:24:55</t>
+          <t>07:24:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="F38" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>293.9</v>
+        <v>301.7</v>
       </c>
       <c r="H38" t="n">
-        <v>65.5</v>
+        <v>64</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-111.55</v>
+        <v>-38.73</v>
       </c>
       <c r="K38" t="n">
-        <v>-135.78</v>
+        <v>109.63</v>
       </c>
       <c r="L38" t="n">
-        <v>175.73</v>
+        <v>116.27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:26:55</t>
+          <t>07:26:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="F39" t="n">
-        <v>3.73</v>
+        <v>7.93</v>
       </c>
       <c r="G39" t="n">
-        <v>273.1</v>
+        <v>301.9</v>
       </c>
       <c r="H39" t="n">
-        <v>33.7</v>
+        <v>51.8</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>87.39</v>
+        <v>-82.3</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.99</v>
+        <v>-45.53</v>
       </c>
       <c r="L39" t="n">
-        <v>87.40000000000001</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:29:18</t>
+          <t>07:28:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="F40" t="n">
-        <v>6.04</v>
+        <v>8.84</v>
       </c>
       <c r="G40" t="n">
-        <v>292.1</v>
+        <v>305.1</v>
       </c>
       <c r="H40" t="n">
-        <v>56.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-56.38</v>
+        <v>-1.06</v>
       </c>
       <c r="K40" t="n">
-        <v>69.51000000000001</v>
+        <v>168.08</v>
       </c>
       <c r="L40" t="n">
-        <v>89.48999999999999</v>
+        <v>168.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:34:36</t>
+          <t>07:33:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.03</v>
+        <v>2.13</v>
       </c>
       <c r="F41" t="n">
-        <v>9.539999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="G41" t="n">
-        <v>285.2</v>
+        <v>308.6</v>
       </c>
       <c r="H41" t="n">
-        <v>38.8</v>
+        <v>36.6</v>
       </c>
       <c r="I41" t="n">
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>18.05</v>
+        <v>-78.04000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>148.78</v>
+        <v>-154.32</v>
       </c>
       <c r="L41" t="n">
-        <v>149.87</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:35:27</t>
+          <t>07:35:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>7.03</v>
+        <v>2.3</v>
       </c>
       <c r="G42" t="n">
-        <v>302.7</v>
+        <v>320.1</v>
       </c>
       <c r="H42" t="n">
-        <v>48.8</v>
+        <v>37.7</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-159.12</v>
+        <v>-39.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-32.87</v>
+        <v>53.24</v>
       </c>
       <c r="L42" t="n">
-        <v>162.48</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:37:31</t>
+          <t>07:38:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="F43" t="n">
-        <v>7.2</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>293</v>
+        <v>292.6</v>
       </c>
       <c r="H43" t="n">
-        <v>45.3</v>
+        <v>73.5</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-83.51000000000001</v>
+        <v>-106.1</v>
       </c>
       <c r="K43" t="n">
-        <v>-61.33</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>103.61</v>
+        <v>138.32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:46:31</t>
+          <t>07:47:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="F44" t="n">
-        <v>6.8</v>
+        <v>4.65</v>
       </c>
       <c r="G44" t="n">
-        <v>301.1</v>
+        <v>293.4</v>
       </c>
       <c r="H44" t="n">
-        <v>55.3</v>
+        <v>48.3</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>18.47</v>
+        <v>20.15</v>
       </c>
       <c r="K44" t="n">
-        <v>4.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>18.99</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:48:56</t>
+          <t>07:48:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="F45" t="n">
-        <v>4.91</v>
+        <v>8.06</v>
       </c>
       <c r="G45" t="n">
-        <v>302.8</v>
+        <v>296.3</v>
       </c>
       <c r="H45" t="n">
-        <v>72.2</v>
+        <v>61.1</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.17</v>
+        <v>-4.85</v>
       </c>
       <c r="K45" t="n">
-        <v>26.93</v>
+        <v>-37.57</v>
       </c>
       <c r="L45" t="n">
-        <v>26.93</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:51:00</t>
+          <t>07:50:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="F46" t="n">
-        <v>8.06</v>
+        <v>6.7</v>
       </c>
       <c r="G46" t="n">
-        <v>305.1</v>
+        <v>295.3</v>
       </c>
       <c r="H46" t="n">
-        <v>90.5</v>
+        <v>25.3</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.93</v>
+        <v>50.18</v>
       </c>
       <c r="K46" t="n">
-        <v>-63.13</v>
+        <v>-7.02</v>
       </c>
       <c r="L46" t="n">
-        <v>63.25</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:56:01</t>
+          <t>07:55:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.95</v>
+        <v>2.69</v>
       </c>
       <c r="F47" t="n">
-        <v>6.59</v>
+        <v>4.38</v>
       </c>
       <c r="G47" t="n">
-        <v>295.6</v>
+        <v>299.4</v>
       </c>
       <c r="H47" t="n">
-        <v>80.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.26</v>
+        <v>-70.63</v>
       </c>
       <c r="K47" t="n">
-        <v>4.93</v>
+        <v>1.77</v>
       </c>
       <c r="L47" t="n">
-        <v>40.56</v>
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:57:12</t>
+          <t>07:57:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="F48" t="n">
-        <v>6.07</v>
+        <v>8.57</v>
       </c>
       <c r="G48" t="n">
-        <v>305.4</v>
+        <v>293</v>
       </c>
       <c r="H48" t="n">
-        <v>42.1</v>
+        <v>45.3</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.710000000000001</v>
+        <v>-37.27</v>
       </c>
       <c r="K48" t="n">
-        <v>34.76</v>
+        <v>-33.59</v>
       </c>
       <c r="L48" t="n">
-        <v>35.83</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:58:14</t>
+          <t>07:59:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="F49" t="n">
-        <v>9.539999999999999</v>
+        <v>6.99</v>
       </c>
       <c r="G49" t="n">
-        <v>284.2</v>
+        <v>303.9</v>
       </c>
       <c r="H49" t="n">
-        <v>36.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J49" t="n">
-        <v>-33.39</v>
+        <v>32.01</v>
       </c>
       <c r="K49" t="n">
-        <v>36.07</v>
+        <v>48.76</v>
       </c>
       <c r="L49" t="n">
-        <v>49.15</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:03:50</t>
+          <t>08:02:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="F50" t="n">
-        <v>6.38</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>299.6</v>
+        <v>295.4</v>
       </c>
       <c r="H50" t="n">
-        <v>46.8</v>
+        <v>66.2</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>43.28</v>
+        <v>65.8</v>
       </c>
       <c r="K50" t="n">
-        <v>75.52</v>
+        <v>-63.94</v>
       </c>
       <c r="L50" t="n">
-        <v>87.04000000000001</v>
+        <v>91.73999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:05:42</t>
+          <t>08:04:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="F51" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>295.5</v>
+        <v>299.4</v>
       </c>
       <c r="H51" t="n">
-        <v>4.7</v>
+        <v>63.5</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>3.49</v>
+        <v>-61.44</v>
       </c>
       <c r="K51" t="n">
-        <v>82.63</v>
+        <v>-51.97</v>
       </c>
       <c r="L51" t="n">
-        <v>82.7</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:06:50</t>
+          <t>08:07:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="F52" t="n">
-        <v>9.539999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>300.7</v>
+        <v>297</v>
       </c>
       <c r="H52" t="n">
-        <v>40.7</v>
+        <v>51.2</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>55.8</v>
+        <v>21.87</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.08</v>
+        <v>-50.26</v>
       </c>
       <c r="L52" t="n">
-        <v>55.81</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:12:50</t>
+          <t>08:12:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.77</v>
+        <v>2.47</v>
       </c>
       <c r="F53" t="n">
-        <v>8.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>291.2</v>
+        <v>297.4</v>
       </c>
       <c r="H53" t="n">
-        <v>80.59999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>76.13</v>
+        <v>-14.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-63.25</v>
+        <v>-142.81</v>
       </c>
       <c r="L53" t="n">
-        <v>98.98</v>
+        <v>143.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:13:43</t>
+          <t>08:14:23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="F54" t="n">
-        <v>8.949999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="G54" t="n">
-        <v>294.5</v>
+        <v>286.8</v>
       </c>
       <c r="H54" t="n">
-        <v>77.2</v>
+        <v>67.8</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-43.21</v>
+        <v>42</v>
       </c>
       <c r="K54" t="n">
-        <v>83.62</v>
+        <v>112.65</v>
       </c>
       <c r="L54" t="n">
-        <v>94.12</v>
+        <v>120.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:15:22</t>
+          <t>08:16:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="F55" t="n">
-        <v>8.09</v>
+        <v>9.49</v>
       </c>
       <c r="G55" t="n">
-        <v>313.2</v>
+        <v>301.1</v>
       </c>
       <c r="H55" t="n">
-        <v>10.6</v>
+        <v>81.8</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J55" t="n">
-        <v>-50.47</v>
+        <v>88.81</v>
       </c>
       <c r="K55" t="n">
-        <v>60.72</v>
+        <v>52.45</v>
       </c>
       <c r="L55" t="n">
-        <v>78.95</v>
+        <v>103.14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:19:29</t>
+          <t>08:22:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.09</v>
+        <v>2.74</v>
       </c>
       <c r="F56" t="n">
-        <v>6.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>296.2</v>
+        <v>303.9</v>
       </c>
       <c r="H56" t="n">
-        <v>48.7</v>
+        <v>53</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-106.03</v>
+        <v>102.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-11.36</v>
+        <v>-160.51</v>
       </c>
       <c r="L56" t="n">
-        <v>106.64</v>
+        <v>190.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:21:11</t>
+          <t>08:24:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="F57" t="n">
-        <v>2.43</v>
+        <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>301.4</v>
+        <v>298.3</v>
       </c>
       <c r="H57" t="n">
-        <v>81.7</v>
+        <v>31.3</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-97.47</v>
+        <v>-121.72</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.88</v>
+        <v>19.43</v>
       </c>
       <c r="L57" t="n">
-        <v>97.52</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:23:01</t>
+          <t>08:26:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="F58" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>296.6</v>
+        <v>294.6</v>
       </c>
       <c r="H58" t="n">
-        <v>51.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-16.03</v>
+        <v>-186.7</v>
       </c>
       <c r="K58" t="n">
-        <v>182.13</v>
+        <v>-62.87</v>
       </c>
       <c r="L58" t="n">
-        <v>182.83</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:34:53</t>
+          <t>08:34:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="F59" t="n">
-        <v>4.65</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>302.3</v>
+        <v>297.7</v>
       </c>
       <c r="H59" t="n">
-        <v>71.09999999999999</v>
+        <v>46.4</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>16.23</v>
+        <v>-7.21</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.74</v>
+        <v>-36.57</v>
       </c>
       <c r="L59" t="n">
-        <v>26.34</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:36:44</t>
+          <t>08:36:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="F60" t="n">
-        <v>4.55</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>289.9</v>
+        <v>294.4</v>
       </c>
       <c r="H60" t="n">
-        <v>33.7</v>
+        <v>30.2</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>13.22</v>
+        <v>40.26</v>
       </c>
       <c r="K60" t="n">
-        <v>28.7</v>
+        <v>12.7</v>
       </c>
       <c r="L60" t="n">
-        <v>31.6</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:38:01</t>
+          <t>08:37:45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="F61" t="n">
-        <v>8.51</v>
+        <v>4.3</v>
       </c>
       <c r="G61" t="n">
-        <v>300</v>
+        <v>289.5</v>
       </c>
       <c r="H61" t="n">
-        <v>50.7</v>
+        <v>18.8</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>10.84</v>
+        <v>-17.8</v>
       </c>
       <c r="K61" t="n">
-        <v>36.33</v>
+        <v>28.67</v>
       </c>
       <c r="L61" t="n">
-        <v>37.92</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:44:00</t>
+          <t>08:41:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.07</v>
+        <v>2.39</v>
       </c>
       <c r="F62" t="n">
-        <v>7.88</v>
+        <v>7.04</v>
       </c>
       <c r="G62" t="n">
-        <v>308.2</v>
+        <v>289.1</v>
       </c>
       <c r="H62" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>32.07</v>
+        <v>-66.19</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.14</v>
+        <v>29.4</v>
       </c>
       <c r="L62" t="n">
-        <v>32.48</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:45:18</t>
+          <t>08:42:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="F63" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>297.4</v>
+        <v>307.9</v>
       </c>
       <c r="H63" t="n">
-        <v>47.5</v>
+        <v>53</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.56</v>
+        <v>30.85</v>
       </c>
       <c r="K63" t="n">
-        <v>-42.73</v>
+        <v>-46.16</v>
       </c>
       <c r="L63" t="n">
-        <v>42.76</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:46:51</t>
+          <t>08:43:16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="F64" t="n">
-        <v>6.28</v>
+        <v>7.66</v>
       </c>
       <c r="G64" t="n">
-        <v>300.4</v>
+        <v>291</v>
       </c>
       <c r="H64" t="n">
-        <v>56.7</v>
+        <v>59.5</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.13</v>
+        <v>41.79</v>
       </c>
       <c r="K64" t="n">
-        <v>62.61</v>
+        <v>-51.88</v>
       </c>
       <c r="L64" t="n">
-        <v>63.02</v>
+        <v>66.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:52:12</t>
+          <t>08:47:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="F65" t="n">
-        <v>9.539999999999999</v>
+        <v>6.74</v>
       </c>
       <c r="G65" t="n">
-        <v>303.7</v>
+        <v>302.4</v>
       </c>
       <c r="H65" t="n">
-        <v>78.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>-31.31</v>
+        <v>-87.39</v>
       </c>
       <c r="K65" t="n">
-        <v>82.01000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>87.78</v>
+        <v>87.81999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:53:32</t>
+          <t>08:49:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="F66" t="n">
-        <v>5.13</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>294</v>
+        <v>307.6</v>
       </c>
       <c r="H66" t="n">
-        <v>65.09999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="I66" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.75</v>
+        <v>-27.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-62.07</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>64.84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:54:50</t>
+          <t>08:51:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="F67" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>283.6</v>
+        <v>298.8</v>
       </c>
       <c r="H67" t="n">
-        <v>56.2</v>
+        <v>16.1</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-63.2</v>
+        <v>19.34</v>
       </c>
       <c r="K67" t="n">
-        <v>-42.59</v>
+        <v>124.45</v>
       </c>
       <c r="L67" t="n">
-        <v>76.20999999999999</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:59:30</t>
+          <t>08:57:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.14</v>
+        <v>3.51</v>
       </c>
       <c r="F68" t="n">
-        <v>9.01</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>293</v>
+        <v>289.5</v>
       </c>
       <c r="H68" t="n">
-        <v>48</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-40.59</v>
+        <v>108.91</v>
       </c>
       <c r="K68" t="n">
-        <v>78.41</v>
+        <v>-108.89</v>
       </c>
       <c r="L68" t="n">
-        <v>88.29000000000001</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:01:11</t>
+          <t>08:59:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="F69" t="n">
-        <v>2.25</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>299.4</v>
+        <v>307.2</v>
       </c>
       <c r="H69" t="n">
-        <v>45.3</v>
+        <v>29.4</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-30.37</v>
+        <v>-49.54</v>
       </c>
       <c r="K69" t="n">
-        <v>85.97</v>
+        <v>162.01</v>
       </c>
       <c r="L69" t="n">
-        <v>91.18000000000001</v>
+        <v>169.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:02:42</t>
+          <t>09:00:38</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="F70" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>300.4</v>
+        <v>300.3</v>
       </c>
       <c r="H70" t="n">
-        <v>65.5</v>
+        <v>44.4</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.53</v>
+        <v>-142.39</v>
       </c>
       <c r="K70" t="n">
-        <v>-95.11</v>
+        <v>59.08</v>
       </c>
       <c r="L70" t="n">
-        <v>95.22</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:08:19</t>
+          <t>09:05:22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="F71" t="n">
-        <v>8.91</v>
+        <v>6.93</v>
       </c>
       <c r="G71" t="n">
-        <v>291.1</v>
+        <v>309.3</v>
       </c>
       <c r="H71" t="n">
-        <v>58.7</v>
+        <v>95.5</v>
       </c>
       <c r="I71" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-70.06999999999999</v>
+        <v>16.79</v>
       </c>
       <c r="K71" t="n">
-        <v>-114.4</v>
+        <v>206.54</v>
       </c>
       <c r="L71" t="n">
-        <v>134.15</v>
+        <v>207.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:10:30</t>
+          <t>09:07:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="F72" t="n">
-        <v>5.67</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>304.4</v>
+        <v>281.2</v>
       </c>
       <c r="H72" t="n">
-        <v>63.8</v>
+        <v>59.3</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-152.41</v>
+        <v>-26.27</v>
       </c>
       <c r="K72" t="n">
-        <v>77.12</v>
+        <v>149.9</v>
       </c>
       <c r="L72" t="n">
-        <v>170.81</v>
+        <v>152.18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:11:54</t>
+          <t>09:09:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="F73" t="n">
-        <v>9.539999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="G73" t="n">
-        <v>295</v>
+        <v>300.9</v>
       </c>
       <c r="H73" t="n">
-        <v>79.59999999999999</v>
+        <v>51.1</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>87.17</v>
+        <v>180.29</v>
       </c>
       <c r="K73" t="n">
-        <v>1.39</v>
+        <v>-103.41</v>
       </c>
       <c r="L73" t="n">
-        <v>87.18000000000001</v>
+        <v>207.85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:21:10</t>
+          <t>09:20:18</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="F74" t="n">
-        <v>9.23</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>297.8</v>
+        <v>302.9</v>
       </c>
       <c r="H74" t="n">
-        <v>82.8</v>
+        <v>43.5</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>21.47</v>
+        <v>-36.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.36</v>
+        <v>-30.55</v>
       </c>
       <c r="L74" t="n">
-        <v>28.91</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:22:31</t>
+          <t>09:21:57</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="F75" t="n">
-        <v>4.96</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>289.8</v>
+        <v>293.7</v>
       </c>
       <c r="H75" t="n">
-        <v>75.8</v>
+        <v>56.4</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-32.57</v>
+        <v>39.54</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.49</v>
+        <v>17.82</v>
       </c>
       <c r="L75" t="n">
-        <v>32.6</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:23:36</t>
+          <t>09:23:48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="F76" t="n">
-        <v>8.82</v>
+        <v>7.77</v>
       </c>
       <c r="G76" t="n">
-        <v>298.8</v>
+        <v>301.6</v>
       </c>
       <c r="H76" t="n">
-        <v>49.9</v>
+        <v>43.8</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>46.9</v>
+        <v>17.12</v>
       </c>
       <c r="K76" t="n">
-        <v>3.71</v>
+        <v>-19.44</v>
       </c>
       <c r="L76" t="n">
-        <v>47.05</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:27:21</t>
+          <t>09:27:36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="F77" t="n">
-        <v>9.539999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="G77" t="n">
-        <v>294.4</v>
+        <v>301</v>
       </c>
       <c r="H77" t="n">
-        <v>82.09999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-15.99</v>
+        <v>-17.58</v>
       </c>
       <c r="K77" t="n">
-        <v>44.75</v>
+        <v>-55.34</v>
       </c>
       <c r="L77" t="n">
-        <v>47.53</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:28:33</t>
+          <t>09:28:44</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="F78" t="n">
-        <v>7.99</v>
+        <v>8.25</v>
       </c>
       <c r="G78" t="n">
-        <v>293.1</v>
+        <v>277.2</v>
       </c>
       <c r="H78" t="n">
-        <v>38</v>
+        <v>49.2</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J78" t="n">
-        <v>14.41</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>56.12</v>
+        <v>-7.98</v>
       </c>
       <c r="L78" t="n">
-        <v>57.94</v>
+        <v>72.65000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:29:49</t>
+          <t>09:29:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.11</v>
+        <v>3.4</v>
       </c>
       <c r="F79" t="n">
-        <v>5.17</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="H79" t="n">
-        <v>63.8</v>
+        <v>42.3</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-47.27</v>
+        <v>1.16</v>
       </c>
       <c r="K79" t="n">
-        <v>-6.74</v>
+        <v>-69.73</v>
       </c>
       <c r="L79" t="n">
-        <v>47.75</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:33:16</t>
+          <t>09:34:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="F80" t="n">
-        <v>6.49</v>
+        <v>8.68</v>
       </c>
       <c r="G80" t="n">
-        <v>306.5</v>
+        <v>298.2</v>
       </c>
       <c r="H80" t="n">
-        <v>89.8</v>
+        <v>36.7</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-57.16</v>
+        <v>-0.03</v>
       </c>
       <c r="K80" t="n">
-        <v>57.45</v>
+        <v>88.97</v>
       </c>
       <c r="L80" t="n">
-        <v>81.04000000000001</v>
+        <v>88.97</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:35:03</t>
+          <t>09:36:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="F81" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>298.3</v>
+        <v>298.5</v>
       </c>
       <c r="H81" t="n">
-        <v>53</v>
+        <v>59.2</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-43.59</v>
+        <v>-93.7</v>
       </c>
       <c r="K81" t="n">
-        <v>-61.64</v>
+        <v>-10.42</v>
       </c>
       <c r="L81" t="n">
-        <v>75.5</v>
+        <v>94.28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:37:01</t>
+          <t>09:38:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="F82" t="n">
-        <v>6.99</v>
+        <v>4.41</v>
       </c>
       <c r="G82" t="n">
-        <v>297.5</v>
+        <v>292.8</v>
       </c>
       <c r="H82" t="n">
-        <v>51.2</v>
+        <v>75.5</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-62.16</v>
+        <v>75.11</v>
       </c>
       <c r="K82" t="n">
-        <v>-50.03</v>
+        <v>-40.17</v>
       </c>
       <c r="L82" t="n">
-        <v>79.8</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:42:10</t>
+          <t>09:42:46</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="F83" t="n">
-        <v>8.630000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>295.6</v>
+        <v>290.3</v>
       </c>
       <c r="H83" t="n">
-        <v>46.9</v>
+        <v>44</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-89.23999999999999</v>
+        <v>-38.5</v>
       </c>
       <c r="K83" t="n">
-        <v>7.73</v>
+        <v>81.58</v>
       </c>
       <c r="L83" t="n">
-        <v>89.56999999999999</v>
+        <v>90.20999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:43:08</t>
+          <t>09:44:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="F84" t="n">
-        <v>5.26</v>
+        <v>9.35</v>
       </c>
       <c r="G84" t="n">
-        <v>310.9</v>
+        <v>314.4</v>
       </c>
       <c r="H84" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>80.22</v>
+        <v>-114.97</v>
       </c>
       <c r="K84" t="n">
-        <v>-9.1</v>
+        <v>-30.07</v>
       </c>
       <c r="L84" t="n">
-        <v>80.73999999999999</v>
+        <v>118.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:44:20</t>
+          <t>09:46:09</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="F85" t="n">
-        <v>9.07</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>293.2</v>
+        <v>311</v>
       </c>
       <c r="H85" t="n">
-        <v>67.59999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J85" t="n">
-        <v>-69.86</v>
+        <v>-48.05</v>
       </c>
       <c r="K85" t="n">
-        <v>52.72</v>
+        <v>137.88</v>
       </c>
       <c r="L85" t="n">
-        <v>87.52</v>
+        <v>146.02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:49:53</t>
+          <t>09:50:22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="F86" t="n">
-        <v>6.41</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>316.1</v>
+        <v>298.3</v>
       </c>
       <c r="H86" t="n">
-        <v>78.09999999999999</v>
+        <v>53</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>83.13</v>
+        <v>-79.87</v>
       </c>
       <c r="K86" t="n">
-        <v>-93.06</v>
+        <v>-173.99</v>
       </c>
       <c r="L86" t="n">
-        <v>124.78</v>
+        <v>191.45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:50:40</t>
+          <t>09:52:01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.96</v>
+        <v>2.57</v>
       </c>
       <c r="F87" t="n">
-        <v>7.97</v>
+        <v>7.13</v>
       </c>
       <c r="G87" t="n">
-        <v>297.6</v>
+        <v>294.1</v>
       </c>
       <c r="H87" t="n">
-        <v>44.3</v>
+        <v>56.1</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>-163.07</v>
+        <v>-184.03</v>
       </c>
       <c r="K87" t="n">
-        <v>14.98</v>
+        <v>122.64</v>
       </c>
       <c r="L87" t="n">
-        <v>163.76</v>
+        <v>221.15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:52:10</t>
+          <t>09:53:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="F88" t="n">
-        <v>7.31</v>
+        <v>6.62</v>
       </c>
       <c r="G88" t="n">
-        <v>302.3</v>
+        <v>295.6</v>
       </c>
       <c r="H88" t="n">
-        <v>59.9</v>
+        <v>46.9</v>
       </c>
       <c r="I88" t="n">
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-121.25</v>
+        <v>-161.69</v>
       </c>
       <c r="K88" t="n">
-        <v>114.63</v>
+        <v>3.94</v>
       </c>
       <c r="L88" t="n">
-        <v>166.86</v>
+        <v>161.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-13.xlsx
+++ b/output/2024-04-13.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-39.92</v>
+        <v>-43.59</v>
       </c>
       <c r="K14" t="n">
-        <v>11.48</v>
+        <v>12.53</v>
       </c>
       <c r="L14" t="n">
-        <v>41.54</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>12.53</v>
+        <v>12.6</v>
       </c>
       <c r="K15" t="n">
-        <v>54.02</v>
+        <v>54.36</v>
       </c>
       <c r="L15" t="n">
-        <v>55.46</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>46.62</v>
+        <v>49.76</v>
       </c>
       <c r="K16" t="n">
-        <v>24.16</v>
+        <v>25.79</v>
       </c>
       <c r="L16" t="n">
-        <v>52.51</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>41.98</v>
+        <v>44.62</v>
       </c>
       <c r="K17" t="n">
-        <v>47.44</v>
+        <v>50.42</v>
       </c>
       <c r="L17" t="n">
-        <v>63.35</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.29</v>
+        <v>-15.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-65.5</v>
+        <v>-72.05</v>
       </c>
       <c r="L18" t="n">
-        <v>67.04000000000001</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-19.03</v>
+        <v>-21.73</v>
       </c>
       <c r="K19" t="n">
-        <v>45.99</v>
+        <v>52.5</v>
       </c>
       <c r="L19" t="n">
-        <v>49.77</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-31.58</v>
+        <v>-38.79</v>
       </c>
       <c r="K20" t="n">
-        <v>64.63</v>
+        <v>79.38</v>
       </c>
       <c r="L20" t="n">
-        <v>71.94</v>
+        <v>88.34999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.13</v>
+        <v>-37.48</v>
       </c>
       <c r="K21" t="n">
-        <v>64.34999999999999</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>71.06</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.27</v>
+        <v>-0.33</v>
       </c>
       <c r="K22" t="n">
-        <v>-60.47</v>
+        <v>-75.94</v>
       </c>
       <c r="L22" t="n">
-        <v>60.47</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>133.16</v>
+        <v>155.36</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.95</v>
+        <v>-17.44</v>
       </c>
       <c r="L23" t="n">
-        <v>134</v>
+        <v>156.33</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>91.42</v>
+        <v>109.16</v>
       </c>
       <c r="K24" t="n">
-        <v>-92.34999999999999</v>
+        <v>-110.28</v>
       </c>
       <c r="L24" t="n">
-        <v>129.95</v>
+        <v>155.17</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>94.81</v>
+        <v>109.91</v>
       </c>
       <c r="K25" t="n">
-        <v>-70.33</v>
+        <v>-81.53</v>
       </c>
       <c r="L25" t="n">
-        <v>118.05</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-111.25</v>
+        <v>-147.99</v>
       </c>
       <c r="K26" t="n">
-        <v>-48.47</v>
+        <v>-64.48</v>
       </c>
       <c r="L26" t="n">
-        <v>121.35</v>
+        <v>161.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>141.28</v>
+        <v>163.38</v>
       </c>
       <c r="K27" t="n">
-        <v>189.34</v>
+        <v>218.96</v>
       </c>
       <c r="L27" t="n">
-        <v>236.24</v>
+        <v>273.2</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>128.78</v>
+        <v>177.13</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.45</v>
+        <v>-6.12</v>
       </c>
       <c r="L28" t="n">
-        <v>128.86</v>
+        <v>177.23</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>53.62</v>
+        <v>53.71</v>
       </c>
       <c r="K29" t="n">
         <v>2.26</v>
       </c>
       <c r="L29" t="n">
-        <v>53.67</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-34.4</v>
+        <v>-38.39</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.72</v>
+        <v>-3.04</v>
       </c>
       <c r="L30" t="n">
-        <v>34.51</v>
+        <v>38.51</v>
       </c>
     </row>
     <row r="31">
@@ -1357,10 +1357,10 @@
         <v>-56.59</v>
       </c>
       <c r="K31" t="n">
-        <v>44.64</v>
+        <v>44.63</v>
       </c>
       <c r="L31" t="n">
-        <v>72.08</v>
+        <v>72.06999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-68.77</v>
+        <v>-70.75</v>
       </c>
       <c r="K32" t="n">
-        <v>61.22</v>
+        <v>62.98</v>
       </c>
       <c r="L32" t="n">
-        <v>92.06999999999999</v>
+        <v>94.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>4.31</v>
+        <v>4.49</v>
       </c>
       <c r="K33" t="n">
-        <v>-74.31</v>
+        <v>-77.3</v>
       </c>
       <c r="L33" t="n">
-        <v>74.44</v>
+        <v>77.43000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-38.46</v>
+        <v>-42.65</v>
       </c>
       <c r="K34" t="n">
-        <v>-51.23</v>
+        <v>-56.82</v>
       </c>
       <c r="L34" t="n">
-        <v>64.06</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>45.26</v>
+        <v>50.98</v>
       </c>
       <c r="K35" t="n">
-        <v>81.56999999999999</v>
+        <v>91.89</v>
       </c>
       <c r="L35" t="n">
-        <v>93.28</v>
+        <v>105.08</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>12.51</v>
+        <v>13.97</v>
       </c>
       <c r="K36" t="n">
-        <v>-86.77</v>
+        <v>-96.94</v>
       </c>
       <c r="L36" t="n">
-        <v>87.66</v>
+        <v>97.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.55</v>
+        <v>-32.89</v>
       </c>
       <c r="K37" t="n">
-        <v>95.09</v>
+        <v>105.85</v>
       </c>
       <c r="L37" t="n">
-        <v>99.56999999999999</v>
+        <v>110.84</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>67.90000000000001</v>
+        <v>86.94</v>
       </c>
       <c r="K38" t="n">
-        <v>-44.96</v>
+        <v>-57.57</v>
       </c>
       <c r="L38" t="n">
-        <v>81.44</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-24.73</v>
+        <v>-28.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-150.46</v>
+        <v>-175</v>
       </c>
       <c r="L39" t="n">
-        <v>152.48</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>39.66</v>
+        <v>43.85</v>
       </c>
       <c r="K40" t="n">
-        <v>-150.66</v>
+        <v>-166.58</v>
       </c>
       <c r="L40" t="n">
-        <v>155.8</v>
+        <v>172.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>126.69</v>
+        <v>166.91</v>
       </c>
       <c r="K41" t="n">
-        <v>44.96</v>
+        <v>59.23</v>
       </c>
       <c r="L41" t="n">
-        <v>134.44</v>
+        <v>177.11</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>170.46</v>
+        <v>205.89</v>
       </c>
       <c r="K42" t="n">
-        <v>101.79</v>
+        <v>122.94</v>
       </c>
       <c r="L42" t="n">
-        <v>198.54</v>
+        <v>239.81</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-140.09</v>
+        <v>-166.92</v>
       </c>
       <c r="K43" t="n">
-        <v>-143.59</v>
+        <v>-171.09</v>
       </c>
       <c r="L43" t="n">
-        <v>200.61</v>
+        <v>239.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.43</v>
+        <v>-13.86</v>
       </c>
       <c r="K44" t="n">
-        <v>38.77</v>
+        <v>43.22</v>
       </c>
       <c r="L44" t="n">
-        <v>40.72</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.23</v>
+        <v>-37.16</v>
       </c>
       <c r="K45" t="n">
-        <v>31.26</v>
+        <v>32.98</v>
       </c>
       <c r="L45" t="n">
-        <v>47.1</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>42.59</v>
+        <v>46.23</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.4</v>
+        <v>-4.78</v>
       </c>
       <c r="L46" t="n">
-        <v>42.82</v>
+        <v>46.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>100.14</v>
+        <v>100.75</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.76</v>
+        <v>-12.84</v>
       </c>
       <c r="L47" t="n">
-        <v>100.95</v>
+        <v>101.57</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.66</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.05</v>
+        <v>-33.68</v>
       </c>
       <c r="L48" t="n">
-        <v>76.68000000000001</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>62.09</v>
+        <v>66.36</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.43</v>
+        <v>-14.35</v>
       </c>
       <c r="L49" t="n">
-        <v>63.52</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.55</v>
+        <v>-15.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-89.29000000000001</v>
+        <v>-101.6</v>
       </c>
       <c r="L50" t="n">
-        <v>90.31</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>82.29000000000001</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>70.01000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="L51" t="n">
-        <v>108.04</v>
+        <v>122.75</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>39.6</v>
+        <v>45.78</v>
       </c>
       <c r="K52" t="n">
-        <v>89.28</v>
+        <v>103.22</v>
       </c>
       <c r="L52" t="n">
-        <v>97.67</v>
+        <v>112.92</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-84.63</v>
+        <v>-96.19</v>
       </c>
       <c r="K53" t="n">
-        <v>113.95</v>
+        <v>129.52</v>
       </c>
       <c r="L53" t="n">
-        <v>141.94</v>
+        <v>161.33</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.3</v>
+        <v>-58.93</v>
       </c>
       <c r="K54" t="n">
-        <v>145.07</v>
+        <v>166.65</v>
       </c>
       <c r="L54" t="n">
-        <v>153.88</v>
+        <v>176.77</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-30.38</v>
+        <v>-38.8</v>
       </c>
       <c r="K55" t="n">
-        <v>-72.34999999999999</v>
+        <v>-92.38</v>
       </c>
       <c r="L55" t="n">
-        <v>78.47</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>19.82</v>
+        <v>26.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-10.11</v>
+        <v>-13.3</v>
       </c>
       <c r="L56" t="n">
-        <v>22.25</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-67.90000000000001</v>
+        <v>-92.2</v>
       </c>
       <c r="K57" t="n">
-        <v>95.7</v>
+        <v>129.95</v>
       </c>
       <c r="L57" t="n">
-        <v>117.34</v>
+        <v>159.33</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-121.9</v>
+        <v>-163.14</v>
       </c>
       <c r="K58" t="n">
-        <v>-49.5</v>
+        <v>-66.25</v>
       </c>
       <c r="L58" t="n">
-        <v>131.56</v>
+        <v>176.08</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-28.47</v>
+        <v>-29.27</v>
       </c>
       <c r="K59" t="n">
-        <v>51.68</v>
+        <v>53.13</v>
       </c>
       <c r="L59" t="n">
-        <v>59</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.66</v>
+        <v>-13.66</v>
       </c>
       <c r="K60" t="n">
-        <v>34.2</v>
+        <v>40.07</v>
       </c>
       <c r="L60" t="n">
-        <v>36.13</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>32.61</v>
+        <v>36.28</v>
       </c>
       <c r="K61" t="n">
-        <v>-40.98</v>
+        <v>-45.59</v>
       </c>
       <c r="L61" t="n">
-        <v>52.37</v>
+        <v>58.26</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-37.65</v>
+        <v>-43.55</v>
       </c>
       <c r="K62" t="n">
-        <v>34.95</v>
+        <v>40.43</v>
       </c>
       <c r="L62" t="n">
-        <v>51.37</v>
+        <v>59.43</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>70.42</v>
+        <v>74.16</v>
       </c>
       <c r="K63" t="n">
-        <v>13.78</v>
+        <v>14.51</v>
       </c>
       <c r="L63" t="n">
-        <v>71.76000000000001</v>
+        <v>75.56999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>20.56</v>
+        <v>22.5</v>
       </c>
       <c r="K64" t="n">
-        <v>-60.97</v>
+        <v>-66.73999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>64.34999999999999</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-80.53</v>
+        <v>-95.7</v>
       </c>
       <c r="K65" t="n">
-        <v>9.380000000000001</v>
+        <v>11.15</v>
       </c>
       <c r="L65" t="n">
-        <v>81.06999999999999</v>
+        <v>96.34</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-130.36</v>
+        <v>-137.74</v>
       </c>
       <c r="K66" t="n">
-        <v>-56.68</v>
+        <v>-59.88</v>
       </c>
       <c r="L66" t="n">
-        <v>142.15</v>
+        <v>150.2</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>44.53</v>
+        <v>50.47</v>
       </c>
       <c r="K67" t="n">
-        <v>-109.97</v>
+        <v>-124.63</v>
       </c>
       <c r="L67" t="n">
-        <v>118.65</v>
+        <v>134.46</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-117.15</v>
+        <v>-130.03</v>
       </c>
       <c r="K68" t="n">
-        <v>102.15</v>
+        <v>113.38</v>
       </c>
       <c r="L68" t="n">
-        <v>155.43</v>
+        <v>172.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>28.04</v>
+        <v>36.08</v>
       </c>
       <c r="K69" t="n">
-        <v>100.51</v>
+        <v>129.36</v>
       </c>
       <c r="L69" t="n">
-        <v>104.35</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>69.03</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-132.29</v>
+        <v>-151.86</v>
       </c>
       <c r="L70" t="n">
-        <v>149.22</v>
+        <v>171.29</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>18.8</v>
+        <v>23.03</v>
       </c>
       <c r="K71" t="n">
-        <v>185.17</v>
+        <v>226.84</v>
       </c>
       <c r="L71" t="n">
-        <v>186.12</v>
+        <v>228.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>19.5</v>
+        <v>25.3</v>
       </c>
       <c r="K72" t="n">
-        <v>160.86</v>
+        <v>208.71</v>
       </c>
       <c r="L72" t="n">
-        <v>162.04</v>
+        <v>210.23</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>268.78</v>
+        <v>310.79</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.63</v>
+        <v>-0.73</v>
       </c>
       <c r="L73" t="n">
-        <v>268.78</v>
+        <v>310.79</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.48</v>
+        <v>-29.42</v>
       </c>
       <c r="K74" t="n">
-        <v>-35.16</v>
+        <v>-37.64</v>
       </c>
       <c r="L74" t="n">
-        <v>44.63</v>
+        <v>47.77</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-50.3</v>
+        <v>-54.52</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.85</v>
+        <v>-31.27</v>
       </c>
       <c r="L75" t="n">
-        <v>57.99</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>23.15</v>
+        <v>26.36</v>
       </c>
       <c r="K76" t="n">
-        <v>26.22</v>
+        <v>29.85</v>
       </c>
       <c r="L76" t="n">
-        <v>34.97</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-46.38</v>
+        <v>-51.41</v>
       </c>
       <c r="K77" t="n">
-        <v>-34.01</v>
+        <v>-37.7</v>
       </c>
       <c r="L77" t="n">
-        <v>57.52</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-24.35</v>
+        <v>-27.99</v>
       </c>
       <c r="K78" t="n">
-        <v>-50.47</v>
+        <v>-58.03</v>
       </c>
       <c r="L78" t="n">
-        <v>56.04</v>
+        <v>64.43000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>57.32</v>
+        <v>64.91</v>
       </c>
       <c r="K79" t="n">
-        <v>18.88</v>
+        <v>21.38</v>
       </c>
       <c r="L79" t="n">
-        <v>60.35</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>97.76000000000001</v>
+        <v>114.5</v>
       </c>
       <c r="K80" t="n">
-        <v>34.92</v>
+        <v>40.9</v>
       </c>
       <c r="L80" t="n">
-        <v>103.81</v>
+        <v>121.59</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-71.40000000000001</v>
+        <v>-90.64</v>
       </c>
       <c r="K81" t="n">
-        <v>6.24</v>
+        <v>7.93</v>
       </c>
       <c r="L81" t="n">
-        <v>71.67</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-59.89</v>
+        <v>-69.75</v>
       </c>
       <c r="K82" t="n">
-        <v>55.6</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>81.72</v>
+        <v>95.18000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>6.79</v>
+        <v>7.48</v>
       </c>
       <c r="K83" t="n">
-        <v>171.12</v>
+        <v>188.59</v>
       </c>
       <c r="L83" t="n">
-        <v>171.25</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-119.64</v>
+        <v>-134.34</v>
       </c>
       <c r="K84" t="n">
-        <v>-72.41</v>
+        <v>-81.3</v>
       </c>
       <c r="L84" t="n">
-        <v>139.84</v>
+        <v>157.02</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>56.73</v>
+        <v>71.36</v>
       </c>
       <c r="K85" t="n">
-        <v>-87.81</v>
+        <v>-110.45</v>
       </c>
       <c r="L85" t="n">
-        <v>104.55</v>
+        <v>131.49</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>24.54</v>
+        <v>30.62</v>
       </c>
       <c r="K86" t="n">
-        <v>197.63</v>
+        <v>246.58</v>
       </c>
       <c r="L86" t="n">
-        <v>199.15</v>
+        <v>248.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-239</v>
+        <v>-274.24</v>
       </c>
       <c r="K87" t="n">
-        <v>-18.48</v>
+        <v>-21.2</v>
       </c>
       <c r="L87" t="n">
-        <v>239.71</v>
+        <v>275.06</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-126.83</v>
+        <v>-165.31</v>
       </c>
       <c r="K88" t="n">
-        <v>-76.98</v>
+        <v>-100.34</v>
       </c>
       <c r="L88" t="n">
-        <v>148.37</v>
+        <v>193.38</v>
       </c>
     </row>
   </sheetData>
